--- a/public/synthetic_12_data.xlsx
+++ b/public/synthetic_12_data.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S241"/>
+  <dimension ref="A1:S281"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7541,16 +7541,16 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>robin1</v>
+        <v>plant1</v>
       </c>
       <c r="B122">
-        <v>0.7682151683012921</v>
+        <v>0.07821516830129209</v>
       </c>
       <c r="C122">
-        <v>0.29098477493135516</v>
+        <v>0.07098477493135516</v>
       </c>
       <c r="D122">
-        <v>0.2502057169497341</v>
+        <v>0.11020571694973409</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -7562,28 +7562,28 @@
         <v>0</v>
       </c>
       <c r="H122">
-        <v>0.613492166934819</v>
+        <v>0.36349216693481906</v>
       </c>
       <c r="I122">
-        <v>0.1975830261702534</v>
+        <v>0.5975830261702534</v>
       </c>
       <c r="J122">
-        <v>0.988293580972487</v>
+        <v>0.788293580972487</v>
       </c>
       <c r="K122">
-        <v>0.5229600909385751</v>
+        <v>0.02296009093857508</v>
       </c>
       <c r="L122">
-        <v>0.7649452170854608</v>
+        <v>0</v>
       </c>
       <c r="M122">
         <v>0.009312421271618132</v>
       </c>
       <c r="N122">
-        <v>0</v>
+        <v>0.38231214544887854</v>
       </c>
       <c r="O122">
-        <v>0</v>
+        <v>0.2774196921735451</v>
       </c>
       <c r="P122">
         <v>0</v>
@@ -7600,52 +7600,52 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>robin2</v>
+        <v>plant2</v>
       </c>
       <c r="B123">
-        <v>0.7523235097323362</v>
+        <v>0.06232350973233624</v>
       </c>
       <c r="C123">
-        <v>0.33235767694185075</v>
+        <v>0.11235767694185078</v>
       </c>
       <c r="D123">
-        <v>0.2050431576630566</v>
+        <v>0.0650431576630566</v>
       </c>
       <c r="E123">
-        <v>0.3362522603101173</v>
+        <v>1</v>
       </c>
       <c r="F123">
         <v>0</v>
       </c>
       <c r="G123">
-        <v>0.6637477396898827</v>
+        <v>0</v>
       </c>
       <c r="H123">
-        <v>0.60650618888495</v>
+        <v>0.35650618888495006</v>
       </c>
       <c r="I123">
-        <v>0.24671094461054802</v>
+        <v>0.646710944610548</v>
       </c>
       <c r="J123">
-        <v>0.939015697656029</v>
+        <v>0.739015697656029</v>
       </c>
       <c r="K123">
-        <v>0.5165730933421129</v>
+        <v>0.016573093342112894</v>
       </c>
       <c r="L123">
-        <v>0.8049017382569897</v>
+        <v>0.00490173825698972</v>
       </c>
       <c r="M123">
         <v>0</v>
       </c>
       <c r="N123">
-        <v>0</v>
+        <v>0.3541055341661902</v>
       </c>
       <c r="O123">
-        <v>0</v>
+        <v>0.280358320524927</v>
       </c>
       <c r="P123">
-        <v>0.2592298434512274</v>
+        <v>0.3542221036957685</v>
       </c>
       <c r="Q123">
         <v>0</v>
@@ -7654,57 +7654,57 @@
         <v>0.3974276840576861</v>
       </c>
       <c r="S123">
-        <v>0.34334247249108646</v>
+        <v>0.24835021224654535</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>robin3</v>
+        <v>plant3</v>
       </c>
       <c r="B124">
-        <v>0.7116863725155096</v>
+        <v>0.021686372515509575</v>
       </c>
       <c r="C124">
-        <v>0.3532687477796716</v>
+        <v>0.13326874777967163</v>
       </c>
       <c r="D124">
-        <v>0.2220191605565174</v>
+        <v>0.0820191605565174</v>
       </c>
       <c r="E124">
-        <v>0.28376175477885285</v>
+        <v>0.9893368893127936</v>
       </c>
       <c r="F124">
-        <v>0.01088239592947704</v>
+        <v>0.010663110687206363</v>
       </c>
       <c r="G124">
-        <v>0.7053558492916701</v>
+        <v>0</v>
       </c>
       <c r="H124">
-        <v>0.5952936894858517</v>
+        <v>0.34529368948585176</v>
       </c>
       <c r="I124">
-        <v>0.22861861261974498</v>
+        <v>0.6286186126197449</v>
       </c>
       <c r="J124">
-        <v>0.984159782780272</v>
+        <v>0.7841597827802721</v>
       </c>
       <c r="K124">
-        <v>0.46539560564886767</v>
+        <v>0</v>
       </c>
       <c r="L124">
-        <v>0.796736176934073</v>
+        <v>0</v>
       </c>
       <c r="M124">
         <v>0</v>
       </c>
       <c r="N124">
-        <v>0.030701676125442074</v>
+        <v>0.4307016761254421</v>
       </c>
       <c r="O124">
-        <v>0</v>
+        <v>0.2941232934187716</v>
       </c>
       <c r="P124">
-        <v>0.24526112807365597</v>
+        <v>0.3398958387221994</v>
       </c>
       <c r="Q124">
         <v>0.015464896231436586</v>
@@ -7713,57 +7713,57 @@
         <v>0.3907855479000344</v>
       </c>
       <c r="S124">
-        <v>0.348488427794873</v>
+        <v>0.25385371714632954</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>robin4</v>
+        <v>plant4</v>
       </c>
       <c r="B125">
-        <v>0.7422014165328822</v>
+        <v>0.052201416532882225</v>
       </c>
       <c r="C125">
-        <v>0.3068849135152916</v>
+        <v>0.08688491351529165</v>
       </c>
       <c r="D125">
-        <v>0.23762106510975878</v>
+        <v>0.09762106510975876</v>
       </c>
       <c r="E125">
-        <v>0.267412192683072</v>
+        <v>0.9769511219552235</v>
       </c>
       <c r="F125">
-        <v>0.023429585795794322</v>
+        <v>0.023048878044776497</v>
       </c>
       <c r="G125">
-        <v>0.7091582215211336</v>
+        <v>0</v>
       </c>
       <c r="H125">
-        <v>0.559954831013738</v>
+        <v>0.309954831013738</v>
       </c>
       <c r="I125">
-        <v>0.24369579413618347</v>
+        <v>0.6436957941361835</v>
       </c>
       <c r="J125">
-        <v>0.9362492963939066</v>
+        <v>0.7362492963939067</v>
       </c>
       <c r="K125">
-        <v>0.5667931873003021</v>
+        <v>0.06679318730030212</v>
       </c>
       <c r="L125">
-        <v>0.7882236460683186</v>
+        <v>0</v>
       </c>
       <c r="M125">
         <v>0</v>
       </c>
       <c r="N125">
-        <v>0</v>
+        <v>0.32822098849526055</v>
       </c>
       <c r="O125">
-        <v>0.0020120976234117576</v>
+        <v>0.30201209762341175</v>
       </c>
       <c r="P125">
-        <v>0.25594238070815584</v>
+        <v>0.34375126250615007</v>
       </c>
       <c r="Q125">
         <v>0.039852557367835204</v>
@@ -7772,57 +7772,57 @@
         <v>0.3793182831140649</v>
       </c>
       <c r="S125">
-        <v>0.32488677880994415</v>
+        <v>0.23707789701194987</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>robin5</v>
+        <v>plant5</v>
       </c>
       <c r="B126">
-        <v>0.6979776292912365</v>
+        <v>0.007977629291236563</v>
       </c>
       <c r="C126">
-        <v>0.3016185817156771</v>
+        <v>0.08161858171567712</v>
       </c>
       <c r="D126">
-        <v>0.21130454309158703</v>
+        <v>0.07130454309158703</v>
       </c>
       <c r="E126">
-        <v>0.31017670253918045</v>
+        <v>0.9837919288964724</v>
       </c>
       <c r="F126">
         <v>0</v>
       </c>
       <c r="G126">
-        <v>0.6898232974608196</v>
+        <v>0.016208071103527635</v>
       </c>
       <c r="H126">
-        <v>0.5944871898500138</v>
+        <v>0.3444871898500138</v>
       </c>
       <c r="I126">
-        <v>0.2778582814997908</v>
+        <v>0.6778582814997909</v>
       </c>
       <c r="J126">
-        <v>0.9189789293969771</v>
+        <v>0.7189789293969772</v>
       </c>
       <c r="K126">
-        <v>0.4749280174621482</v>
+        <v>0</v>
       </c>
       <c r="L126">
-        <v>0.7971614421194297</v>
+        <v>0</v>
       </c>
       <c r="M126">
         <v>0</v>
       </c>
       <c r="N126">
-        <v>0.029182301870883928</v>
+        <v>0.42918230187088396</v>
       </c>
       <c r="O126">
-        <v>0.023654776802569055</v>
+        <v>0.32365477680256904</v>
       </c>
       <c r="P126">
-        <v>0.2506571483510856</v>
+        <v>0.34648222717500093</v>
       </c>
       <c r="Q126">
         <v>0</v>
@@ -7831,57 +7831,57 @@
         <v>0.4084315722700703</v>
       </c>
       <c r="S126">
-        <v>0.3409112793788441</v>
+        <v>0.24508620055492877</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>robin6</v>
+        <v>plant6</v>
       </c>
       <c r="B127">
-        <v>0.7409404381328206</v>
+        <v>0.050940438132820634</v>
       </c>
       <c r="C127">
-        <v>0.23806268267533248</v>
+        <v>0.018062682675332495</v>
       </c>
       <c r="D127">
-        <v>0.20564376468715498</v>
+        <v>0.06564376468715497</v>
       </c>
       <c r="E127">
-        <v>0.31537568353074863</v>
+        <v>1</v>
       </c>
       <c r="F127">
         <v>0</v>
       </c>
       <c r="G127">
-        <v>0.6846243164692514</v>
+        <v>0</v>
       </c>
       <c r="H127">
-        <v>0.6180799863813949</v>
+        <v>0.368079986381395</v>
       </c>
       <c r="I127">
-        <v>0.21139722789407034</v>
+        <v>0.6113972278940704</v>
       </c>
       <c r="J127">
-        <v>0.9303223000560671</v>
+        <v>0.7303223000560671</v>
       </c>
       <c r="K127">
-        <v>0.5123847901073919</v>
+        <v>0.012384790107391852</v>
       </c>
       <c r="L127">
-        <v>0.8279329983815871</v>
+        <v>0.02793299838158706</v>
       </c>
       <c r="M127">
         <v>0.016168837411500145</v>
       </c>
       <c r="N127">
-        <v>0</v>
+        <v>0.36962816818214356</v>
       </c>
       <c r="O127">
-        <v>0.006467729219911746</v>
+        <v>0.3064677292199117</v>
       </c>
       <c r="P127">
-        <v>0.2197612777108753</v>
+        <v>0.3190393416302056</v>
       </c>
       <c r="Q127">
         <v>0</v>
@@ -7890,57 +7890,57 @@
         <v>0.4107570421962735</v>
       </c>
       <c r="S127">
-        <v>0.36948168009285104</v>
+        <v>0.2702036161735208</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>robin7</v>
+        <v>plant7</v>
       </c>
       <c r="B128">
-        <v>0.754513032517162</v>
+        <v>0.06451303251716198</v>
       </c>
       <c r="C128">
-        <v>0.31923728085944997</v>
+        <v>0.09923728085944998</v>
       </c>
       <c r="D128">
-        <v>0.21794345377489927</v>
+        <v>0.07794345377489927</v>
       </c>
       <c r="E128">
-        <v>0.31338619277831564</v>
+        <v>0.9461438669953625</v>
       </c>
       <c r="F128">
-        <v>0.04283359940683273</v>
+        <v>0.04467660695162124</v>
       </c>
       <c r="G128">
-        <v>0.6437802078148517</v>
+        <v>0.009179526053016324</v>
       </c>
       <c r="H128">
-        <v>0.5835332772983879</v>
+        <v>0.3335332772983879</v>
       </c>
       <c r="I128">
-        <v>0.23603644581283556</v>
+        <v>0.6360364458128356</v>
       </c>
       <c r="J128">
-        <v>0.931248216507419</v>
+        <v>0.731248216507419</v>
       </c>
       <c r="K128">
-        <v>0.4569214838735876</v>
+        <v>0</v>
       </c>
       <c r="L128">
-        <v>0.7739666004987178</v>
+        <v>0</v>
       </c>
       <c r="M128">
         <v>0</v>
       </c>
       <c r="N128">
-        <v>0</v>
+        <v>0.39581652887898083</v>
       </c>
       <c r="O128">
-        <v>0.02117831233679939</v>
+        <v>0.3211783123367994</v>
       </c>
       <c r="P128">
-        <v>0.2814857289153911</v>
+        <v>0.37846864780284867</v>
       </c>
       <c r="Q128">
         <v>0</v>
@@ -7949,175 +7949,175 @@
         <v>0.38705366712997546</v>
       </c>
       <c r="S128">
-        <v>0.33146060395463345</v>
+        <v>0.23447768506717584</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>robin8</v>
+        <v>plant8</v>
       </c>
       <c r="B129">
-        <v>0.7019481184685009</v>
+        <v>0.011948118468500912</v>
       </c>
       <c r="C129">
-        <v>0.2826277401117915</v>
+        <v>0.06262774011179148</v>
       </c>
       <c r="D129">
-        <v>0.19135368527680158</v>
+        <v>0.05135368527680156</v>
       </c>
       <c r="E129">
-        <v>0.32132436581066254</v>
+        <v>0.9914932878035808</v>
       </c>
       <c r="F129">
         <v>0</v>
       </c>
       <c r="G129">
-        <v>0.6786756341893375</v>
+        <v>0.008506712196419118</v>
       </c>
       <c r="H129">
-        <v>0.5792958827671939</v>
+        <v>0.32929588276719385</v>
       </c>
       <c r="I129">
-        <v>0.2787030130845651</v>
+        <v>0.678703013084565</v>
       </c>
       <c r="J129">
-        <v>0.9366302700459918</v>
+        <v>0.7366302700459918</v>
       </c>
       <c r="K129">
-        <v>0.5221038292107486</v>
+        <v>0.022103829210748622</v>
       </c>
       <c r="L129">
-        <v>0.8142958907555181</v>
+        <v>0.014295890755518107</v>
       </c>
       <c r="M129">
         <v>0</v>
       </c>
       <c r="N129">
-        <v>0</v>
+        <v>0.35754779825666727</v>
       </c>
       <c r="O129">
-        <v>0</v>
+        <v>0.29475183873094823</v>
       </c>
       <c r="P129">
-        <v>0.25474844145863557</v>
+        <v>0.34737170191187794</v>
       </c>
       <c r="Q129">
-        <v>0.025537279179148935</v>
+        <v>0.025537279179148942</v>
       </c>
       <c r="R129">
-        <v>0.37772885925658994</v>
+        <v>0.37772885925659005</v>
       </c>
       <c r="S129">
-        <v>0.3419854201056254</v>
+        <v>0.2493621596523832</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>robin9</v>
+        <v>plant9</v>
       </c>
       <c r="B130">
-        <v>0.7294147811987658</v>
+        <v>0.03941478119876583</v>
       </c>
       <c r="C130">
-        <v>0.3594458018059773</v>
+        <v>0.1394458018059773</v>
       </c>
       <c r="D130">
-        <v>0.23156022978327975</v>
+        <v>0.09156022978327974</v>
       </c>
       <c r="E130">
-        <v>0.3000712977196893</v>
+        <v>1</v>
       </c>
       <c r="F130">
         <v>0</v>
       </c>
       <c r="G130">
-        <v>0.6999287022803107</v>
+        <v>0</v>
       </c>
       <c r="H130">
-        <v>0.6020722909126632</v>
+        <v>0.35207229091266323</v>
       </c>
       <c r="I130">
-        <v>0.23999962685668422</v>
+        <v>0.6399996268566842</v>
       </c>
       <c r="J130">
-        <v>0.953688801262197</v>
+        <v>0.7536888012621971</v>
       </c>
       <c r="K130">
-        <v>0.5410608952153618</v>
+        <v>0.041060895215361846</v>
       </c>
       <c r="L130">
-        <v>0.8089084836141274</v>
+        <v>0.00890848361412738</v>
       </c>
       <c r="M130">
         <v>0</v>
       </c>
       <c r="N130">
-        <v>0</v>
+        <v>0.3932226815131829</v>
       </c>
       <c r="O130">
-        <v>0.01531182908082373</v>
+        <v>0.3153118290808237</v>
       </c>
       <c r="P130">
-        <v>0.243464918098799</v>
+        <v>0.3467523096893726</v>
       </c>
       <c r="Q130">
-        <v>0.025024728933692147</v>
+        <v>0.025024728933692154</v>
       </c>
       <c r="R130">
-        <v>0.3895234603650093</v>
+        <v>0.3895234603650094</v>
       </c>
       <c r="S130">
-        <v>0.3419868926024995</v>
+        <v>0.238699501011926</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>robin10</v>
+        <v>plant10</v>
       </c>
       <c r="B131">
-        <v>0.7416701441114767</v>
+        <v>0.05167014411147668</v>
       </c>
       <c r="C131">
-        <v>0.2910018231877719</v>
+        <v>0.07100182318777194</v>
       </c>
       <c r="D131">
-        <v>0.20343557828772119</v>
+        <v>0.06343557828772116</v>
       </c>
       <c r="E131">
-        <v>0.28974670464099017</v>
+        <v>1</v>
       </c>
       <c r="F131">
         <v>0</v>
       </c>
       <c r="G131">
-        <v>0.7102532953590098</v>
+        <v>0</v>
       </c>
       <c r="H131">
-        <v>0.5719723158110578</v>
+        <v>0.3219723158110578</v>
       </c>
       <c r="I131">
-        <v>0.27676329840929315</v>
+        <v>0.6767632984092932</v>
       </c>
       <c r="J131">
-        <v>0.9518680175635791</v>
+        <v>0.7518680175635791</v>
       </c>
       <c r="K131">
-        <v>0.4348131985560417</v>
+        <v>0</v>
       </c>
       <c r="L131">
-        <v>0.7400004091056597</v>
+        <v>0</v>
       </c>
       <c r="M131">
         <v>0</v>
       </c>
       <c r="N131">
-        <v>0.006286880266691665</v>
+        <v>0.4062868802666917</v>
       </c>
       <c r="O131">
-        <v>0</v>
+        <v>0.26099040983753213</v>
       </c>
       <c r="P131">
-        <v>0.23943241510845772</v>
+        <v>0.33117114736677183</v>
       </c>
       <c r="Q131">
         <v>0</v>
@@ -8126,57 +8126,57 @@
         <v>0.3963128529860667</v>
       </c>
       <c r="S131">
-        <v>0.3642547319054756</v>
+        <v>0.27251599964716144</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>robin11</v>
+        <v>plant11</v>
       </c>
       <c r="B132">
-        <v>0.7360857098369055</v>
+        <v>0.04608570983690548</v>
       </c>
       <c r="C132">
-        <v>0.27904155851914103</v>
+        <v>0.05904155851914103</v>
       </c>
       <c r="D132">
-        <v>0.18095663247236435</v>
+        <v>0.040956632472364335</v>
       </c>
       <c r="E132">
-        <v>0.29676515228086303</v>
+        <v>0.9988766236966812</v>
       </c>
       <c r="F132">
-        <v>0.0011515680112714859</v>
+        <v>0.0011233763033188448</v>
       </c>
       <c r="G132">
-        <v>0.7020832797078654</v>
+        <v>0</v>
       </c>
       <c r="H132">
-        <v>0.5501997586212644</v>
+        <v>0.3001997586212643</v>
       </c>
       <c r="I132">
-        <v>0.22460094999914243</v>
+        <v>0.6246009499991424</v>
       </c>
       <c r="J132">
-        <v>0.9278427441005106</v>
+        <v>0.7278427441005106</v>
       </c>
       <c r="K132">
-        <v>0.5294141410803547</v>
+        <v>0.029414141080354658</v>
       </c>
       <c r="L132">
-        <v>0.7749141557368475</v>
+        <v>0</v>
       </c>
       <c r="M132">
         <v>0.005242565657510901</v>
       </c>
       <c r="N132">
-        <v>0</v>
+        <v>0.34131492712974226</v>
       </c>
       <c r="O132">
-        <v>0.003409783407007587</v>
+        <v>0.3034097834070076</v>
       </c>
       <c r="P132">
-        <v>0.2501329806244591</v>
+        <v>0.3475786816508583</v>
       </c>
       <c r="Q132">
         <v>0.00864105353489445</v>
@@ -8185,116 +8185,116 @@
         <v>0.38520771536411175</v>
       </c>
       <c r="S132">
-        <v>0.35601825047653474</v>
+        <v>0.2585725494501355</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>robin12</v>
+        <v>plant12</v>
       </c>
       <c r="B133">
-        <v>0.7183863393786978</v>
+        <v>0.028386339378697778</v>
       </c>
       <c r="C133">
-        <v>0.30321574279072694</v>
+        <v>0.08321574279072697</v>
       </c>
       <c r="D133">
-        <v>0.21947905951218488</v>
+        <v>0.07947905951218487</v>
       </c>
       <c r="E133">
-        <v>0.29956995913117807</v>
+        <v>1</v>
       </c>
       <c r="F133">
         <v>0</v>
       </c>
       <c r="G133">
-        <v>0.7004300408688219</v>
+        <v>0</v>
       </c>
       <c r="H133">
-        <v>0.5880059053721335</v>
+        <v>0.3380059053721335</v>
       </c>
       <c r="I133">
-        <v>0.2403378938288242</v>
+        <v>0.6403378938288242</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0.8027372922166839</v>
       </c>
       <c r="K133">
-        <v>0.49495953594460695</v>
+        <v>0</v>
       </c>
       <c r="L133">
-        <v>0.8045422611697395</v>
+        <v>0.004542261169739475</v>
       </c>
       <c r="M133">
         <v>0.026874832201103552</v>
       </c>
       <c r="N133">
-        <v>0.05459643467276546</v>
+        <v>0.4545964346727655</v>
       </c>
       <c r="O133">
-        <v>0.003710623446183335</v>
+        <v>0.3037106234461833</v>
       </c>
       <c r="P133">
-        <v>0.2716826994370185</v>
+        <v>0.3701934471001131</v>
       </c>
       <c r="Q133">
         <v>0</v>
       </c>
       <c r="R133">
-        <v>0.3889710498560782</v>
+        <v>0.38897104985607833</v>
       </c>
       <c r="S133">
-        <v>0.33934625070690316</v>
+        <v>0.24083550304380874</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>robin13</v>
+        <v>plant13</v>
       </c>
       <c r="B134">
-        <v>0.7561741137337034</v>
+        <v>0.06617411373370337</v>
       </c>
       <c r="C134">
-        <v>0.28917697549594384</v>
+        <v>0.06917697549594387</v>
       </c>
       <c r="D134">
-        <v>0.2148456970274604</v>
+        <v>0.0748456970274604</v>
       </c>
       <c r="E134">
-        <v>0.30469064313330047</v>
+        <v>1</v>
       </c>
       <c r="F134">
         <v>0</v>
       </c>
       <c r="G134">
-        <v>0.6953093568666995</v>
+        <v>0</v>
       </c>
       <c r="H134">
-        <v>0.6455534303649598</v>
+        <v>0.3955534303649598</v>
       </c>
       <c r="I134">
-        <v>0.22885649930724986</v>
+        <v>0.6288564993072498</v>
       </c>
       <c r="J134">
-        <v>0.9820582960155859</v>
+        <v>0.782058296015586</v>
       </c>
       <c r="K134">
-        <v>0.5060550741300702</v>
+        <v>0.006055074130070252</v>
       </c>
       <c r="L134">
-        <v>0.7899417312089145</v>
+        <v>0</v>
       </c>
       <c r="M134">
         <v>0.03868273120671462</v>
       </c>
       <c r="N134">
-        <v>0.0013481141237664314</v>
+        <v>0.4013481141237665</v>
       </c>
       <c r="O134">
-        <v>0</v>
+        <v>0.25679494929136193</v>
       </c>
       <c r="P134">
-        <v>0.24451558402646661</v>
+        <v>0.34063362162913496</v>
       </c>
       <c r="Q134">
         <v>0</v>
@@ -8303,39 +8303,39 @@
         <v>0.40358386016768016</v>
       </c>
       <c r="S134">
-        <v>0.3519005558058533</v>
+        <v>0.2557825182031849</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>robin14</v>
+        <v>plant14</v>
       </c>
       <c r="B135">
-        <v>0.7707429780263184</v>
+        <v>0.08074297802631844</v>
       </c>
       <c r="C135">
-        <v>0.28044691199780963</v>
+        <v>0.06044691199780963</v>
       </c>
       <c r="D135">
-        <v>0.17146247300081258</v>
+        <v>0.03146247300081255</v>
       </c>
       <c r="E135">
-        <v>0.2900976934417629</v>
+        <v>0.9982829189120666</v>
       </c>
       <c r="F135">
         <v>0</v>
       </c>
       <c r="G135">
-        <v>0.7099023065582372</v>
+        <v>0.0017170810879334542</v>
       </c>
       <c r="H135">
-        <v>0.6281000386549759</v>
+        <v>0.3781000386549758</v>
       </c>
       <c r="I135">
-        <v>0.2713951999312969</v>
+        <v>0.6713951999312969</v>
       </c>
       <c r="J135">
-        <v>0.9501814362954496</v>
+        <v>0.7501814362954496</v>
       </c>
       <c r="K135">
         <v>0</v>
@@ -8353,66 +8353,66 @@
         <v>0</v>
       </c>
       <c r="P135">
-        <v>0.24916757967896544</v>
+        <v>0.349161573989976</v>
       </c>
       <c r="Q135">
         <v>0</v>
       </c>
       <c r="R135">
-        <v>0.41504315431129263</v>
+        <v>0.41504315431129274</v>
       </c>
       <c r="S135">
-        <v>0.33578926600974185</v>
+        <v>0.2357952716987314</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>robin15</v>
+        <v>plant15</v>
       </c>
       <c r="B136">
-        <v>0.7431994448418602</v>
+        <v>0.05319944484186018</v>
       </c>
       <c r="C136">
-        <v>0.32312706351609455</v>
+        <v>0.10312706351609459</v>
       </c>
       <c r="D136">
-        <v>0.24302708925173278</v>
+        <v>0.10302708925173275</v>
       </c>
       <c r="E136">
-        <v>0.282602055746795</v>
+        <v>0.9775962789775674</v>
       </c>
       <c r="F136">
         <v>0</v>
       </c>
       <c r="G136">
-        <v>0.717397944253205</v>
+        <v>0.02240372102243271</v>
       </c>
       <c r="H136">
-        <v>0.5689241895757133</v>
+        <v>0.31892418957571333</v>
       </c>
       <c r="I136">
-        <v>0.2447071443281843</v>
+        <v>0.6447071443281843</v>
       </c>
       <c r="J136">
-        <v>0.9462535938580545</v>
+        <v>0.7462535938580546</v>
       </c>
       <c r="K136">
-        <v>0.4628355510200579</v>
+        <v>0</v>
       </c>
       <c r="L136">
-        <v>0.7847566528254523</v>
+        <v>0</v>
       </c>
       <c r="M136">
         <v>0</v>
       </c>
       <c r="N136">
-        <v>0</v>
+        <v>0.37901880860208126</v>
       </c>
       <c r="O136">
-        <v>0.011567768949551322</v>
+        <v>0.3115677689495513</v>
       </c>
       <c r="P136">
-        <v>0.25039693034380855</v>
+        <v>0.3444476057695593</v>
       </c>
       <c r="Q136">
         <v>0</v>
@@ -8421,57 +8421,57 @@
         <v>0.3840113708018169</v>
       </c>
       <c r="S136">
-        <v>0.3655916988543744</v>
+        <v>0.2715410234286237</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>robin16</v>
+        <v>plant16</v>
       </c>
       <c r="B137">
-        <v>0.7574378813356738</v>
+        <v>0.06743788133567376</v>
       </c>
       <c r="C137">
-        <v>0.33432319422435136</v>
+        <v>0.11432319422435136</v>
       </c>
       <c r="D137">
-        <v>0.18655846262832254</v>
+        <v>0.046558462628322514</v>
       </c>
       <c r="E137">
-        <v>0.2808629172662745</v>
+        <v>0.9602154180293013</v>
       </c>
       <c r="F137">
         <v>0</v>
       </c>
       <c r="G137">
-        <v>0.7191370827337256</v>
+        <v>0.039784581970698694</v>
       </c>
       <c r="H137">
-        <v>0.6104315035473301</v>
+        <v>0.3604315035473301</v>
       </c>
       <c r="I137">
-        <v>0.2878136936259121</v>
+        <v>0.6878136936259122</v>
       </c>
       <c r="J137">
-        <v>0.9564302094637956</v>
+        <v>0.7564302094637957</v>
       </c>
       <c r="K137">
-        <v>0.5132033157894149</v>
+        <v>0.013203315789414923</v>
       </c>
       <c r="L137">
-        <v>0.7927599562011399</v>
+        <v>0</v>
       </c>
       <c r="M137">
         <v>0.0026209893302035128</v>
       </c>
       <c r="N137">
-        <v>0.01991498556172795</v>
+        <v>0.41991498556172796</v>
       </c>
       <c r="O137">
-        <v>0</v>
+        <v>0.29272393760540494</v>
       </c>
       <c r="P137">
-        <v>0.25987658533035063</v>
+        <v>0.35903686315628924</v>
       </c>
       <c r="Q137">
         <v>0</v>
@@ -8480,57 +8480,57 @@
         <v>0.40178470099985786</v>
       </c>
       <c r="S137">
-        <v>0.3383387136697915</v>
+        <v>0.2391784358438529</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>robin17</v>
+        <v>plant17</v>
       </c>
       <c r="B138">
-        <v>0.7877441052684442</v>
+        <v>0.09774410526844414</v>
       </c>
       <c r="C138">
-        <v>0.26846842440457086</v>
+        <v>0.04846842440457089</v>
       </c>
       <c r="D138">
-        <v>0.18365137850106908</v>
+        <v>0.043651378501069066</v>
       </c>
       <c r="E138">
-        <v>0.3119852537939683</v>
+        <v>0.9863477807603171</v>
       </c>
       <c r="F138">
-        <v>0.013722154391615022</v>
+        <v>0.013652219239682873</v>
       </c>
       <c r="G138">
-        <v>0.6742925918144166</v>
+        <v>0</v>
       </c>
       <c r="H138">
-        <v>0.590485087780515</v>
+        <v>0.34048508778051495</v>
       </c>
       <c r="I138">
-        <v>0.2648042350745727</v>
+        <v>0.6648042350745728</v>
       </c>
       <c r="J138">
-        <v>0.9745301589813304</v>
+        <v>0.7745301589813305</v>
       </c>
       <c r="K138">
-        <v>0.4833138187047564</v>
+        <v>0</v>
       </c>
       <c r="L138">
-        <v>0.7611041022644203</v>
+        <v>0</v>
       </c>
       <c r="M138">
         <v>0.013236625407129197</v>
       </c>
       <c r="N138">
-        <v>0.023436552291330258</v>
+        <v>0.42343655229133026</v>
       </c>
       <c r="O138">
-        <v>0</v>
+        <v>0.29857502353787796</v>
       </c>
       <c r="P138">
-        <v>0.26053944304828225</v>
+        <v>0.35978498815697463</v>
       </c>
       <c r="Q138">
         <v>0</v>
@@ -8539,57 +8539,57 @@
         <v>0.378820462167211</v>
       </c>
       <c r="S138">
-        <v>0.3606400947845067</v>
+        <v>0.2613945496758143</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>robin18</v>
+        <v>plant18</v>
       </c>
       <c r="B139">
-        <v>0.7252511101015628</v>
+        <v>0.0352511101015629</v>
       </c>
       <c r="C139">
-        <v>0.31554647522534834</v>
+        <v>0.09554647522534833</v>
       </c>
       <c r="D139">
-        <v>0.1687224458296528</v>
+        <v>0.028722445829652762</v>
       </c>
       <c r="E139">
-        <v>0.3062535827729617</v>
+        <v>0.9927711712076218</v>
       </c>
       <c r="F139">
-        <v>0.007379958252925003</v>
+        <v>0.0072288287923783</v>
       </c>
       <c r="G139">
-        <v>0.6863664589741133</v>
+        <v>0</v>
       </c>
       <c r="H139">
-        <v>0.5657851714770877</v>
+        <v>0.31578517147708773</v>
       </c>
       <c r="I139">
-        <v>0.24764155172041152</v>
+        <v>0.6476415517204115</v>
       </c>
       <c r="J139">
-        <v>0.9621980574610919</v>
+        <v>0.7621980574610919</v>
       </c>
       <c r="K139">
-        <v>0.5075262379907182</v>
+        <v>0.0075262379907182035</v>
       </c>
       <c r="L139">
-        <v>0.8103230557336799</v>
+        <v>0.010323055733679906</v>
       </c>
       <c r="M139">
         <v>0</v>
       </c>
       <c r="N139">
-        <v>0</v>
+        <v>0.3931993986888037</v>
       </c>
       <c r="O139">
-        <v>0.0060970735925119125</v>
+        <v>0.3060970735925119</v>
       </c>
       <c r="P139">
-        <v>0.2632015986980933</v>
+        <v>0.3595259514066551</v>
       </c>
       <c r="Q139">
         <v>0.06642137611869364</v>
@@ -8598,160 +8598,160 @@
         <v>0.35908982604724077</v>
       </c>
       <c r="S139">
-        <v>0.3112871991359723</v>
+        <v>0.21496284642741043</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>robin19</v>
+        <v>plant19</v>
       </c>
       <c r="B140">
-        <v>0.7657043803844096</v>
+        <v>0.07570438038440958</v>
       </c>
       <c r="C140">
-        <v>0.33870031076785484</v>
+        <v>0.11870031076785485</v>
       </c>
       <c r="D140">
-        <v>0.19116630439320295</v>
+        <v>0.05116630439320294</v>
       </c>
       <c r="E140">
-        <v>0.3263563348899177</v>
+        <v>0.9786084892914345</v>
       </c>
       <c r="F140">
         <v>0</v>
       </c>
       <c r="G140">
-        <v>0.6736436651100823</v>
+        <v>0.021391510708565396</v>
       </c>
       <c r="H140">
-        <v>0.5880427425496777</v>
+        <v>0.3380427425496777</v>
       </c>
       <c r="I140">
-        <v>0.2503166223906346</v>
+        <v>0.6503166223906347</v>
       </c>
       <c r="J140">
-        <v>0.9123681098728618</v>
+        <v>0.7123681098728618</v>
       </c>
       <c r="K140">
-        <v>0.44512095411097746</v>
+        <v>0</v>
       </c>
       <c r="L140">
-        <v>0.8253400044638013</v>
+        <v>0.025340004463801233</v>
       </c>
       <c r="M140">
         <v>0</v>
       </c>
       <c r="N140">
-        <v>0</v>
+        <v>0.39313109874231594</v>
       </c>
       <c r="O140">
-        <v>0</v>
+        <v>0.2815386789842203</v>
       </c>
       <c r="P140">
-        <v>0.25576024824557847</v>
+        <v>0.3520644646670055</v>
       </c>
       <c r="Q140">
         <v>0</v>
       </c>
       <c r="R140">
-        <v>0.4188447942205898</v>
+        <v>0.4188447942205897</v>
       </c>
       <c r="S140">
-        <v>0.32539495753383185</v>
+        <v>0.22909074111240477</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>robin20</v>
+        <v>plant20</v>
       </c>
       <c r="B141">
-        <v>0.7425002451147283</v>
+        <v>0.052500245114728304</v>
       </c>
       <c r="C141">
-        <v>0.29211928971762385</v>
+        <v>0.07211928971762388</v>
       </c>
       <c r="D141">
-        <v>0.19224661218440925</v>
+        <v>0.05224661218440924</v>
       </c>
       <c r="E141">
-        <v>0.2872231244873949</v>
+        <v>0.9744547957423102</v>
       </c>
       <c r="F141">
         <v>0</v>
       </c>
       <c r="G141">
-        <v>0.712776875512605</v>
+        <v>0.025545204257689826</v>
       </c>
       <c r="H141">
-        <v>0.6064217330085075</v>
+        <v>0.3564217330085075</v>
       </c>
       <c r="I141">
-        <v>0.24747740585720324</v>
+        <v>0.6474774058572033</v>
       </c>
       <c r="J141">
-        <v>0.9677245003767924</v>
+        <v>0.7677245003767924</v>
       </c>
       <c r="K141">
-        <v>0.5138472980758519</v>
+        <v>0.013847298075851923</v>
       </c>
       <c r="L141">
-        <v>0.8065156494647668</v>
+        <v>0.006515649464766776</v>
       </c>
       <c r="M141">
         <v>0.06457341286008016</v>
       </c>
       <c r="N141">
-        <v>0</v>
+        <v>0.3954010063602966</v>
       </c>
       <c r="O141">
-        <v>0.03335740147827341</v>
+        <v>0.3333574014782734</v>
       </c>
       <c r="P141">
-        <v>0.2280870643689652</v>
+        <v>0.3328939273745329</v>
       </c>
       <c r="Q141">
-        <v>0.005524337134908918</v>
+        <v>0.005524337134908919</v>
       </c>
       <c r="R141">
-        <v>0.42530438512293395</v>
+        <v>0.425304385122934</v>
       </c>
       <c r="S141">
-        <v>0.34108421337319184</v>
+        <v>0.23627735036762423</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>canary1</v>
+        <v>robin1</v>
       </c>
       <c r="B142">
-        <v>1</v>
+        <v>0.8033851344202183</v>
       </c>
       <c r="C142">
-        <v>0.8515490227053566</v>
+        <v>0.3015490227053566</v>
       </c>
       <c r="D142">
-        <v>0.06758854554291048</v>
+        <v>0.16758854554291047</v>
       </c>
       <c r="E142">
-        <v>0.19272428708579956</v>
+        <v>0.28978316664866044</v>
       </c>
       <c r="F142">
-        <v>0.013157100366349938</v>
+        <v>0.01315710036634994</v>
       </c>
       <c r="G142">
-        <v>0.7941186125478504</v>
+        <v>0.6970597329849897</v>
       </c>
       <c r="H142">
         <v>0.627080586389086</v>
       </c>
       <c r="I142">
-        <v>0.32522097521712695</v>
+        <v>0.27522097521712696</v>
       </c>
       <c r="J142">
         <v>0.9728143497113122</v>
       </c>
       <c r="K142">
-        <v>0.340532311378658</v>
+        <v>0.440532311378658</v>
       </c>
       <c r="L142">
         <v>0.811671460357758</v>
@@ -8766,51 +8766,51 @@
         <v>0</v>
       </c>
       <c r="P142">
-        <v>0.1563218872569956</v>
+        <v>0.20672293748697199</v>
       </c>
       <c r="Q142">
         <v>0</v>
       </c>
       <c r="R142">
-        <v>0.2472788865787271</v>
+        <v>0.44888308749863265</v>
       </c>
       <c r="S142">
-        <v>0.5963992261642773</v>
+        <v>0.3443939750143954</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>canary2</v>
+        <v>robin2</v>
       </c>
       <c r="B143">
-        <v>0.9664845534423285</v>
+        <v>0.7664845534423286</v>
       </c>
       <c r="C143">
-        <v>0.8511099598919839</v>
+        <v>0.30110995989198386</v>
       </c>
       <c r="D143">
-        <v>0.08199072112998038</v>
+        <v>0.18199072112998038</v>
       </c>
       <c r="E143">
-        <v>0.17159639510479976</v>
+        <v>0.2734041808464381</v>
       </c>
       <c r="F143">
-        <v>0.005124067632232313</v>
+        <v>0.005124067632232314</v>
       </c>
       <c r="G143">
-        <v>0.823279537262968</v>
+        <v>0.7214717515213296</v>
       </c>
       <c r="H143">
         <v>0.6592605362519217</v>
       </c>
       <c r="I143">
-        <v>0.2969032421001083</v>
+        <v>0.24690324210010836</v>
       </c>
       <c r="J143">
         <v>0.9527105422376445</v>
       </c>
       <c r="K143">
-        <v>0.3749162120748862</v>
+        <v>0.47491621207488616</v>
       </c>
       <c r="L143">
         <v>0.8433152951200134</v>
@@ -8825,51 +8825,51 @@
         <v>0</v>
       </c>
       <c r="P143">
-        <v>0.20174623812374173</v>
+        <v>0.24668354061710546</v>
       </c>
       <c r="Q143">
         <v>0</v>
       </c>
       <c r="R143">
-        <v>0.23237180442805444</v>
+        <v>0.41212101440150944</v>
       </c>
       <c r="S143">
-        <v>0.5658819574482039</v>
+        <v>0.3411954449813852</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>canary3</v>
+        <v>robin3</v>
       </c>
       <c r="B144">
-        <v>0.9262567869885534</v>
+        <v>0.7262567869885534</v>
       </c>
       <c r="C144">
-        <v>0.8592153270896435</v>
+        <v>0.3092153270896435</v>
       </c>
       <c r="D144">
-        <v>0.12571364825767387</v>
+        <v>0.22571364825767387</v>
       </c>
       <c r="E144">
-        <v>0.16468773103630988</v>
+        <v>0.2692400515500341</v>
       </c>
       <c r="F144">
-        <v>0.008350423166686351</v>
+        <v>0.008350423166686353</v>
       </c>
       <c r="G144">
-        <v>0.8269618457970037</v>
+        <v>0.7224095252832796</v>
       </c>
       <c r="H144">
         <v>0.5876127799834172</v>
       </c>
       <c r="I144">
-        <v>0.30758921436586684</v>
+        <v>0.25758921436586685</v>
       </c>
       <c r="J144">
         <v>0.9686315819618467</v>
       </c>
       <c r="K144">
-        <v>0.39771726452431283</v>
+        <v>0.4977172645243128</v>
       </c>
       <c r="L144">
         <v>0.7597636053469774</v>
@@ -8884,51 +8884,51 @@
         <v>0</v>
       </c>
       <c r="P144">
-        <v>0.20547441403599886</v>
+        <v>0.2519146688904375</v>
       </c>
       <c r="Q144">
         <v>0.03556601536449846</v>
       </c>
       <c r="R144">
-        <v>0.15920675401933257</v>
+        <v>0.34496777343708734</v>
       </c>
       <c r="S144">
-        <v>0.5997528165801701</v>
+        <v>0.3675515423079767</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>canary4</v>
+        <v>robin4</v>
       </c>
       <c r="B145">
-        <v>0.9711296586891811</v>
+        <v>0.7711296586891812</v>
       </c>
       <c r="C145">
-        <v>0.8364150666459153</v>
+        <v>0.28641506664591526</v>
       </c>
       <c r="D145">
-        <v>0.09691441096880718</v>
+        <v>0.19691441096880719</v>
       </c>
       <c r="E145">
-        <v>0.20264741843719064</v>
+        <v>0.3066182381357841</v>
       </c>
       <c r="F145">
         <v>0</v>
       </c>
       <c r="G145">
-        <v>0.7973525815628093</v>
+        <v>0.693381761864216</v>
       </c>
       <c r="H145">
         <v>0.5809243951409127</v>
       </c>
       <c r="I145">
-        <v>0.3237365768886664</v>
+        <v>0.27373657688866637</v>
       </c>
       <c r="J145">
         <v>0.943605166112314</v>
       </c>
       <c r="K145">
-        <v>0.3953245948302638</v>
+        <v>0.49532459483026375</v>
       </c>
       <c r="L145">
         <v>0.7860501696898401</v>
@@ -8943,51 +8943,51 @@
         <v>0.029666398101609148</v>
       </c>
       <c r="P145">
-        <v>0.2084647990372206</v>
+        <v>0.2593378465965029</v>
       </c>
       <c r="Q145">
         <v>0</v>
       </c>
       <c r="R145">
-        <v>0.16788125919247449</v>
+        <v>0.3713734494296038</v>
       </c>
       <c r="S145">
-        <v>0.6236539417703049</v>
+        <v>0.3692887039738933</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>canary5</v>
+        <v>robin5</v>
       </c>
       <c r="B146">
-        <v>0.9295245447490946</v>
+        <v>0.7295245447490947</v>
       </c>
       <c r="C146">
-        <v>0.8565527654617748</v>
+        <v>0.30655276546177485</v>
       </c>
       <c r="D146">
-        <v>0.1375777084203532</v>
+        <v>0.2375777084203532</v>
       </c>
       <c r="E146">
-        <v>0.1865808815266348</v>
+        <v>0.2902628532286937</v>
       </c>
       <c r="F146">
         <v>0</v>
       </c>
       <c r="G146">
-        <v>0.8134191184733652</v>
+        <v>0.7097371467713063</v>
       </c>
       <c r="H146">
         <v>0.5479382756889678</v>
       </c>
       <c r="I146">
-        <v>0.3671237479237235</v>
+        <v>0.3171237479237235</v>
       </c>
       <c r="J146">
         <v>0.9394092759104381</v>
       </c>
       <c r="K146">
-        <v>0.41238994850806115</v>
+        <v>0.5123899485080612</v>
       </c>
       <c r="L146">
         <v>0.8149381225968233</v>
@@ -9002,51 +9002,51 @@
         <v>0</v>
       </c>
       <c r="P146">
-        <v>0.18619327042586922</v>
+        <v>0.2341679283428371</v>
       </c>
       <c r="Q146">
         <v>0</v>
       </c>
       <c r="R146">
-        <v>0.22506510958421846</v>
+        <v>0.41696374125209007</v>
       </c>
       <c r="S146">
-        <v>0.5887416199899124</v>
+        <v>0.3488683304050729</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>canary6</v>
+        <v>robin6</v>
       </c>
       <c r="B147">
-        <v>0.9282417632478626</v>
+        <v>0.7282417632478626</v>
       </c>
       <c r="C147">
-        <v>0.8577860976549513</v>
+        <v>0.3077860976549513</v>
       </c>
       <c r="D147">
-        <v>0.08871269118018915</v>
+        <v>0.18871269118018916</v>
       </c>
       <c r="E147">
-        <v>0.19250093766521398</v>
+        <v>0.29687126643077294</v>
       </c>
       <c r="F147">
         <v>0</v>
       </c>
       <c r="G147">
-        <v>0.8074990623347861</v>
+        <v>0.703128733569227</v>
       </c>
       <c r="H147">
         <v>0.5687518427149727</v>
       </c>
       <c r="I147">
-        <v>0.31634611556605596</v>
+        <v>0.266346115566056</v>
       </c>
       <c r="J147">
         <v>0.8966979760924823</v>
       </c>
       <c r="K147">
-        <v>0.3783741401663856</v>
+        <v>0.4783741401663856</v>
       </c>
       <c r="L147">
         <v>0.7708901381712457</v>
@@ -9061,51 +9061,51 @@
         <v>0.040366771839566364</v>
       </c>
       <c r="P147">
-        <v>0.2023565672720248</v>
+        <v>0.2535253033842816</v>
       </c>
       <c r="Q147">
         <v>0</v>
       </c>
       <c r="R147">
-        <v>0.20516404908434965</v>
+        <v>0.4098389935333768</v>
       </c>
       <c r="S147">
-        <v>0.5924793836436255</v>
+        <v>0.33663570308234153</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>canary7</v>
+        <v>robin7</v>
       </c>
       <c r="B148">
-        <v>0.9259375214144036</v>
+        <v>0.7259375214144036</v>
       </c>
       <c r="C148">
-        <v>0.8307116322843812</v>
+        <v>0.2807116322843812</v>
       </c>
       <c r="D148">
-        <v>0.10207411664301722</v>
+        <v>0.20207411664301722</v>
       </c>
       <c r="E148">
-        <v>0.20275680672646834</v>
+        <v>0.3051252426848356</v>
       </c>
       <c r="F148">
         <v>0</v>
       </c>
       <c r="G148">
-        <v>0.7972431932735315</v>
+        <v>0.6948747573151645</v>
       </c>
       <c r="H148">
         <v>0.5851134877304065</v>
       </c>
       <c r="I148">
-        <v>0.3103649787047996</v>
+        <v>0.26036497870479963</v>
       </c>
       <c r="J148">
         <v>0.9452543933638332</v>
       </c>
       <c r="K148">
-        <v>0.44550175958298843</v>
+        <v>0.5455017595829884</v>
       </c>
       <c r="L148">
         <v>0.8174311827746947</v>
@@ -9120,51 +9120,51 @@
         <v>0.006320788188731269</v>
       </c>
       <c r="P148">
-        <v>0.20874693543031828</v>
+        <v>0.2570012443201084</v>
       </c>
       <c r="Q148">
         <v>0</v>
       </c>
       <c r="R148">
-        <v>0.21360002216603605</v>
+        <v>0.40661725772519663</v>
       </c>
       <c r="S148">
-        <v>0.5776530424036457</v>
+        <v>0.33638149795469496</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>canary8</v>
+        <v>robin8</v>
       </c>
       <c r="B149">
-        <v>0.9314622611904254</v>
+        <v>0.7314622611904255</v>
       </c>
       <c r="C149">
-        <v>0.8358219923191408</v>
+        <v>0.2858219923191408</v>
       </c>
       <c r="D149">
-        <v>0.10584097758363853</v>
+        <v>0.20584097758363853</v>
       </c>
       <c r="E149">
-        <v>0.18931841228240615</v>
+        <v>0.2843916345126961</v>
       </c>
       <c r="F149">
         <v>0.05205863362405332</v>
       </c>
       <c r="G149">
-        <v>0.7586229540935405</v>
+        <v>0.6635497318632505</v>
       </c>
       <c r="H149">
         <v>0.5977395100043869</v>
       </c>
       <c r="I149">
-        <v>0.31334870204467913</v>
+        <v>0.26334870204467914</v>
       </c>
       <c r="J149">
         <v>0.9478505972069072</v>
       </c>
       <c r="K149">
-        <v>0.4225874094056421</v>
+        <v>0.5225874094056421</v>
       </c>
       <c r="L149">
         <v>0.8070649315361316</v>
@@ -9179,51 +9179,51 @@
         <v>0</v>
       </c>
       <c r="P149">
-        <v>0.17946274828581602</v>
+        <v>0.23231954141190003</v>
       </c>
       <c r="Q149">
         <v>0.019447842545665894</v>
       </c>
       <c r="R149">
-        <v>0.21169191129307732</v>
+        <v>0.4231190837974134</v>
       </c>
       <c r="S149">
-        <v>0.5893974978754407</v>
+        <v>0.32511353224502065</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>canary9</v>
+        <v>robin9</v>
       </c>
       <c r="B150">
-        <v>0.9472737849311491</v>
+        <v>0.7472737849311492</v>
       </c>
       <c r="C150">
-        <v>0.8315175172091553</v>
+        <v>0.28151751720915535</v>
       </c>
       <c r="D150">
-        <v>0.0792973924524055</v>
+        <v>0.1792973924524055</v>
       </c>
       <c r="E150">
-        <v>0.19501916737354372</v>
+        <v>0.2952639161431296</v>
       </c>
       <c r="F150">
-        <v>0.015624195789732976</v>
+        <v>0.015624195789732977</v>
       </c>
       <c r="G150">
-        <v>0.7893566368367233</v>
+        <v>0.6891118880671374</v>
       </c>
       <c r="H150">
         <v>0.6365567052683304</v>
       </c>
       <c r="I150">
-        <v>0.29401336521765387</v>
+        <v>0.2440133652176539</v>
       </c>
       <c r="J150">
         <v>0.9785508013001065</v>
       </c>
       <c r="K150">
-        <v>0.4369567594461184</v>
+        <v>0.5369567594461184</v>
       </c>
       <c r="L150">
         <v>0.8260867375760399</v>
@@ -9238,51 +9238,51 @@
         <v>0.006761871760169865</v>
       </c>
       <c r="P150">
-        <v>0.19496739411883252</v>
+        <v>0.24383579864006058</v>
       </c>
       <c r="Q150">
         <v>0</v>
       </c>
       <c r="R150">
-        <v>0.21424466294999012</v>
+        <v>0.40971828103490254</v>
       </c>
       <c r="S150">
-        <v>0.5907879429311774</v>
+        <v>0.3464459203250368</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>canary10</v>
+        <v>robin10</v>
       </c>
       <c r="B151">
-        <v>0.9652856894006656</v>
+        <v>0.7652856894006657</v>
       </c>
       <c r="C151">
-        <v>0.8363715039581969</v>
+        <v>0.28637150395819694</v>
       </c>
       <c r="D151">
-        <v>0.12166749477816617</v>
+        <v>0.22166749477816616</v>
       </c>
       <c r="E151">
-        <v>0.19545420122298074</v>
+        <v>0.29224179482531554</v>
       </c>
       <c r="F151">
         <v>0</v>
       </c>
       <c r="G151">
-        <v>0.8045457987770193</v>
+        <v>0.7077582051746845</v>
       </c>
       <c r="H151">
         <v>0.6641633385402095</v>
       </c>
       <c r="I151">
-        <v>0.2754097405520519</v>
+        <v>0.22540974055205193</v>
       </c>
       <c r="J151">
         <v>0.9138867452417976</v>
       </c>
       <c r="K151">
-        <v>0.41029185743434243</v>
+        <v>0.5102918574343425</v>
       </c>
       <c r="L151">
         <v>0.798306435034343</v>
@@ -9297,51 +9297,51 @@
         <v>0</v>
       </c>
       <c r="P151">
-        <v>0.21603635149164224</v>
+        <v>0.26502296300121936</v>
       </c>
       <c r="Q151">
         <v>0</v>
       </c>
       <c r="R151">
-        <v>0.18011609777779505</v>
+        <v>0.37606254381610377</v>
       </c>
       <c r="S151">
-        <v>0.6038475507305628</v>
+        <v>0.35891449318267693</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>canary11</v>
+        <v>robin11</v>
       </c>
       <c r="B152">
-        <v>0.9239068708829418</v>
+        <v>0.7239068708829418</v>
       </c>
       <c r="C152">
-        <v>0.8504318656947683</v>
+        <v>0.30043186569476826</v>
       </c>
       <c r="D152">
-        <v>0.07970391743172092</v>
+        <v>0.17970391743172093</v>
       </c>
       <c r="E152">
-        <v>0.1801466683689458</v>
+        <v>0.2775927929527442</v>
       </c>
       <c r="F152">
         <v>0.029741561952974054</v>
       </c>
       <c r="G152">
-        <v>0.7901117696780802</v>
+        <v>0.6926656450942817</v>
       </c>
       <c r="H152">
         <v>0.6043719745192423</v>
       </c>
       <c r="I152">
-        <v>0.28376954599250026</v>
+        <v>0.23376954599250027</v>
       </c>
       <c r="J152">
         <v>0.965115084222243</v>
       </c>
       <c r="K152">
-        <v>0.4323385092851897</v>
+        <v>0.5323385092851897</v>
       </c>
       <c r="L152">
         <v>0.8257326102447219</v>
@@ -9356,51 +9356,51 @@
         <v>0</v>
       </c>
       <c r="P152">
-        <v>0.22316496407877578</v>
+        <v>0.2708188721496085</v>
       </c>
       <c r="Q152">
         <v>0</v>
       </c>
       <c r="R152">
-        <v>0.20636920154356814</v>
+        <v>0.39698483382689903</v>
       </c>
       <c r="S152">
-        <v>0.570465834377656</v>
+        <v>0.33219629402349243</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>canary12</v>
+        <v>robin12</v>
       </c>
       <c r="B153">
-        <v>0.9333289264621789</v>
+        <v>0.733328926462179</v>
       </c>
       <c r="C153">
-        <v>0.8312567040686972</v>
+        <v>0.2812567040686973</v>
       </c>
       <c r="D153">
-        <v>0.14494123559593072</v>
+        <v>0.24494123559593073</v>
       </c>
       <c r="E153">
-        <v>0.1958476408955817</v>
+        <v>0.29758343960437145</v>
       </c>
       <c r="F153">
         <v>0</v>
       </c>
       <c r="G153">
-        <v>0.8041523591044183</v>
+        <v>0.7024165603956286</v>
       </c>
       <c r="H153">
         <v>0.5706922144182787</v>
       </c>
       <c r="I153">
-        <v>0.3265676728198643</v>
+        <v>0.27656767281986433</v>
       </c>
       <c r="J153">
         <v>0.905792953329762</v>
       </c>
       <c r="K153">
-        <v>0.410837225977764</v>
+        <v>0.510837225977764</v>
       </c>
       <c r="L153">
         <v>0.8025511105272446</v>
@@ -9415,30 +9415,30 @@
         <v>0</v>
       </c>
       <c r="P153">
-        <v>0.23597475094107584</v>
+        <v>0.28752098699931944</v>
       </c>
       <c r="Q153">
         <v>0.002733795752208641</v>
       </c>
       <c r="R153">
-        <v>0.1539474029517507</v>
+        <v>0.36013234718472514</v>
       </c>
       <c r="S153">
-        <v>0.6073440503549649</v>
+        <v>0.3496128700637468</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>canary13</v>
+        <v>robin13</v>
       </c>
       <c r="B154">
-        <v>0.9507719183570731</v>
+        <v>0.7507719183570731</v>
       </c>
       <c r="C154">
-        <v>0.8665780251025712</v>
+        <v>0.3165780251025712</v>
       </c>
       <c r="D154">
-        <v>0.1354045103493713</v>
+        <v>0.2354045103493713</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -9453,13 +9453,13 @@
         <v>0.5967320285865406</v>
       </c>
       <c r="I154">
-        <v>0.28279075351200483</v>
+        <v>0.23279075351200484</v>
       </c>
       <c r="J154">
         <v>0.9695675424355132</v>
       </c>
       <c r="K154">
-        <v>0.42176469503674513</v>
+        <v>0.5217646950367452</v>
       </c>
       <c r="L154">
         <v>0.7947550500652814</v>
@@ -9474,51 +9474,51 @@
         <v>0</v>
       </c>
       <c r="P154">
-        <v>0.21828768709837074</v>
+        <v>0.26994310100192764</v>
       </c>
       <c r="Q154">
-        <v>0.003924416236804415</v>
+        <v>0.0039244162368044155</v>
       </c>
       <c r="R154">
-        <v>0.20494204221392212</v>
+        <v>0.4115636978281497</v>
       </c>
       <c r="S154">
-        <v>0.5728458544509026</v>
+        <v>0.31456878493311824</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>canary14</v>
+        <v>robin14</v>
       </c>
       <c r="B155">
-        <v>0.9251376186947322</v>
+        <v>0.7251376186947323</v>
       </c>
       <c r="C155">
-        <v>0.8570935218937896</v>
+        <v>0.30709352189378963</v>
       </c>
       <c r="D155">
-        <v>0.10827224263831497</v>
+        <v>0.20827224263831498</v>
       </c>
       <c r="E155">
-        <v>0.1779376659924795</v>
+        <v>0.2793340296617018</v>
       </c>
       <c r="F155">
         <v>0.0219773511378397</v>
       </c>
       <c r="G155">
-        <v>0.8000849828696809</v>
+        <v>0.6986886192004584</v>
       </c>
       <c r="H155">
         <v>0.6210249951609305</v>
       </c>
       <c r="I155">
-        <v>0.33654114898673887</v>
+        <v>0.2865411489867389</v>
       </c>
       <c r="J155">
         <v>0.8959325930863483</v>
       </c>
       <c r="K155">
-        <v>0.40028120235585135</v>
+        <v>0.5002812023558514</v>
       </c>
       <c r="L155">
         <v>0.8391359378231622</v>
@@ -9533,51 +9533,51 @@
         <v>0</v>
       </c>
       <c r="P155">
-        <v>0.20223939733872498</v>
+        <v>0.24870935931386143</v>
       </c>
       <c r="Q155">
         <v>0.01995598230290621</v>
       </c>
       <c r="R155">
-        <v>0.20306917141089623</v>
+        <v>0.38894901931144216</v>
       </c>
       <c r="S155">
-        <v>0.5747354489474726</v>
+        <v>0.34238563907179026</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>canary15</v>
+        <v>robin15</v>
       </c>
       <c r="B156">
-        <v>0.951946321468506</v>
+        <v>0.751946321468506</v>
       </c>
       <c r="C156">
-        <v>0.8725149960637597</v>
+        <v>0.3225149960637598</v>
       </c>
       <c r="D156">
-        <v>0.11041495625242281</v>
+        <v>0.21041495625242282</v>
       </c>
       <c r="E156">
-        <v>0.1806979590390285</v>
+        <v>0.28279018709463916</v>
       </c>
       <c r="F156">
         <v>0</v>
       </c>
       <c r="G156">
-        <v>0.8193020409609715</v>
+        <v>0.7172098129053609</v>
       </c>
       <c r="H156">
         <v>0.5982692260874913</v>
       </c>
       <c r="I156">
-        <v>0.28612620175186504</v>
+        <v>0.23612620175186505</v>
       </c>
       <c r="J156">
         <v>0.9644673896772937</v>
       </c>
       <c r="K156">
-        <v>0.3913118040116602</v>
+        <v>0.4913118040116602</v>
       </c>
       <c r="L156">
         <v>0.7934240323125564</v>
@@ -9592,51 +9592,51 @@
         <v>0</v>
       </c>
       <c r="P156">
-        <v>0.1774664985983556</v>
+        <v>0.2232687231721852</v>
       </c>
       <c r="Q156">
         <v>0.05087951801446268</v>
       </c>
       <c r="R156">
-        <v>0.19248384679282687</v>
+        <v>0.3756927450881454</v>
       </c>
       <c r="S156">
-        <v>0.5791701365943549</v>
+        <v>0.35015901372520675</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>canary16</v>
+        <v>robin16</v>
       </c>
       <c r="B157">
-        <v>0.9455725532889424</v>
+        <v>0.7455725532889425</v>
       </c>
       <c r="C157">
-        <v>0.8391909104233642</v>
+        <v>0.28919091042336426</v>
       </c>
       <c r="D157">
-        <v>0.13670137593904957</v>
+        <v>0.23670137593904958</v>
       </c>
       <c r="E157">
-        <v>0.17628320116561125</v>
+        <v>0.27812762077338044</v>
       </c>
       <c r="F157">
         <v>0</v>
       </c>
       <c r="G157">
-        <v>0.8237167988343888</v>
+        <v>0.7218723792266196</v>
       </c>
       <c r="H157">
         <v>0.6003211967764541</v>
       </c>
       <c r="I157">
-        <v>0.2909104623455044</v>
+        <v>0.2409104623455044</v>
       </c>
       <c r="J157">
         <v>0.9246857743561977</v>
       </c>
       <c r="K157">
-        <v>0.38635335850457475</v>
+        <v>0.48635335850457473</v>
       </c>
       <c r="L157">
         <v>0.8030172214140837</v>
@@ -9651,51 +9651,51 @@
         <v>0</v>
       </c>
       <c r="P157">
-        <v>0.178631803820699</v>
+        <v>0.22645196127578465</v>
       </c>
       <c r="Q157">
         <v>0.023053712496382547</v>
       </c>
       <c r="R157">
-        <v>0.22814935561231509</v>
+        <v>0.4194299854326578</v>
       </c>
       <c r="S157">
-        <v>0.5701651280706033</v>
+        <v>0.33106434079517494</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>canary17</v>
+        <v>robin17</v>
       </c>
       <c r="B158">
-        <v>0.9670812350525877</v>
+        <v>0.7670812350525877</v>
       </c>
       <c r="C158">
-        <v>0.8382490935878758</v>
+        <v>0.28824909358787576</v>
       </c>
       <c r="D158">
-        <v>0.11215161775700129</v>
+        <v>0.21215161775700128</v>
       </c>
       <c r="E158">
-        <v>0.18788029758544028</v>
+        <v>0.286651596544586</v>
       </c>
       <c r="F158">
         <v>0</v>
       </c>
       <c r="G158">
-        <v>0.8121197024145597</v>
+        <v>0.7133484034554141</v>
       </c>
       <c r="H158">
         <v>0.6228194164554197</v>
       </c>
       <c r="I158">
-        <v>0.34966061469495113</v>
+        <v>0.2996606146949511</v>
       </c>
       <c r="J158">
         <v>0.9785478313596276</v>
       </c>
       <c r="K158">
-        <v>0.3617560199457102</v>
+        <v>0.4617560199457102</v>
       </c>
       <c r="L158">
         <v>0.7620764232627183</v>
@@ -9710,51 +9710,51 @@
         <v>0.0365488967973456</v>
       </c>
       <c r="P158">
-        <v>0.1646930529190161</v>
+        <v>0.21126065666238886</v>
       </c>
       <c r="Q158">
         <v>0.008739727869735857</v>
       </c>
       <c r="R158">
-        <v>0.2031178826196079</v>
+        <v>0.389388297593099</v>
       </c>
       <c r="S158">
-        <v>0.6234493365916401</v>
+        <v>0.39061131787477626</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>canary18</v>
+        <v>robin18</v>
       </c>
       <c r="B159">
-        <v>0.9937417357903309</v>
+        <v>0.7937417357903309</v>
       </c>
       <c r="C159">
-        <v>0.8563148494425453</v>
+        <v>0.30631484944254533</v>
       </c>
       <c r="D159">
-        <v>0.0640379701623765</v>
+        <v>0.1640379701623765</v>
       </c>
       <c r="E159">
-        <v>0.19025156083252598</v>
+        <v>0.2941791201153936</v>
       </c>
       <c r="F159">
         <v>0</v>
       </c>
       <c r="G159">
-        <v>0.8097484391674741</v>
+        <v>0.7058208798846064</v>
       </c>
       <c r="H159">
         <v>0.6459111306922918</v>
       </c>
       <c r="I159">
-        <v>0.3021956578226708</v>
+        <v>0.25219565782267084</v>
       </c>
       <c r="J159">
         <v>0.9327400022470752</v>
       </c>
       <c r="K159">
-        <v>0.37924972885669567</v>
+        <v>0.47924972885669564</v>
       </c>
       <c r="L159">
         <v>0.7906189731885049</v>
@@ -9769,51 +9769,51 @@
         <v>0.021556619929631524</v>
       </c>
       <c r="P159">
-        <v>0.2107867683532485</v>
+        <v>0.2609364117969281</v>
       </c>
       <c r="Q159">
         <v>0</v>
       </c>
       <c r="R159">
-        <v>0.18552651390788444</v>
+        <v>0.38612508768260295</v>
       </c>
       <c r="S159">
-        <v>0.6036867177388671</v>
+        <v>0.3529385005204689</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>canary19</v>
+        <v>robin19</v>
       </c>
       <c r="B160">
-        <v>0.9831275405205393</v>
+        <v>0.7831275405205393</v>
       </c>
       <c r="C160">
-        <v>0.8282797179110204</v>
+        <v>0.27827971791102035</v>
       </c>
       <c r="D160">
-        <v>0.0739271545522695</v>
+        <v>0.1739271545522695</v>
       </c>
       <c r="E160">
-        <v>0.18557429137117656</v>
+        <v>0.2871323946115339</v>
       </c>
       <c r="F160">
         <v>0</v>
       </c>
       <c r="G160">
-        <v>0.8144257086288235</v>
+        <v>0.712867605388466</v>
       </c>
       <c r="H160">
         <v>0.6375197990692716</v>
       </c>
       <c r="I160">
-        <v>0.30700119936339165</v>
+        <v>0.25700119936339166</v>
       </c>
       <c r="J160">
         <v>0.9268270608683282</v>
       </c>
       <c r="K160">
-        <v>0.391409468219693</v>
+        <v>0.491409468219693</v>
       </c>
       <c r="L160">
         <v>0.7690217639189129</v>
@@ -9828,51 +9828,51 @@
         <v>0.031456150632124015</v>
       </c>
       <c r="P160">
-        <v>0.20211214856949283</v>
+        <v>0.2521805935839592</v>
       </c>
       <c r="Q160">
         <v>0</v>
       </c>
       <c r="R160">
-        <v>0.1735950837242161</v>
+        <v>0.37386886378208156</v>
       </c>
       <c r="S160">
-        <v>0.6242927677062912</v>
+        <v>0.37395054263395916</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>canary20</v>
+        <v>robin20</v>
       </c>
       <c r="B161">
-        <v>0.9690654559734188</v>
+        <v>0.7690654559734188</v>
       </c>
       <c r="C161">
-        <v>0.895410924907184</v>
+        <v>0.345410924907184</v>
       </c>
       <c r="D161">
-        <v>0.09972850930548803</v>
+        <v>0.19972850930548802</v>
       </c>
       <c r="E161">
-        <v>0.1874484074820153</v>
+        <v>0.28842859382621294</v>
       </c>
       <c r="F161">
         <v>0</v>
       </c>
       <c r="G161">
-        <v>0.8125515925179847</v>
+        <v>0.7115714061737871</v>
       </c>
       <c r="H161">
         <v>0.5659772329790722</v>
       </c>
       <c r="I161">
-        <v>0.2846204295351649</v>
+        <v>0.2346204295351649</v>
       </c>
       <c r="J161">
         <v>0.9242871849231291</v>
       </c>
       <c r="K161">
-        <v>0.4409780826105717</v>
+        <v>0.5409780826105717</v>
       </c>
       <c r="L161">
         <v>0.7788139157347733</v>
@@ -9887,21 +9887,21 @@
         <v>0.047588865392387616</v>
       </c>
       <c r="P161">
-        <v>0.2126984410728498</v>
+        <v>0.2599096225186655</v>
       </c>
       <c r="Q161">
         <v>0.013532601892230527</v>
       </c>
       <c r="R161">
-        <v>0.22331834706583162</v>
+        <v>0.41216307284909454</v>
       </c>
       <c r="S161">
-        <v>0.5504506099690881</v>
+        <v>0.3143947027400094</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>bird1</v>
+        <v>canary1</v>
       </c>
       <c r="B162">
         <v>0</v>
@@ -9913,25 +9913,25 @@
         <v>0</v>
       </c>
       <c r="E162">
-        <v>0.2624456786348066</v>
+        <v>0.21651039760238847</v>
       </c>
       <c r="F162">
         <v>0.046161090819155544</v>
       </c>
       <c r="G162">
-        <v>0.6913932305460379</v>
+        <v>0.737328511578456</v>
       </c>
       <c r="H162">
         <v>0.6567240783541074</v>
       </c>
       <c r="I162">
-        <v>0.2336458209149695</v>
+        <v>0.25364582091496946</v>
       </c>
       <c r="J162">
         <v>0.9445099513799984</v>
       </c>
       <c r="K162">
-        <v>0.4605046033302041</v>
+        <v>0.4105046033302041</v>
       </c>
       <c r="L162">
         <v>0.7920532912300184</v>
@@ -9946,51 +9946,51 @@
         <v>0.007061496355659497</v>
       </c>
       <c r="P162">
-        <v>0.22087504031136881</v>
+        <v>0.19137602126070793</v>
       </c>
       <c r="Q162">
-        <v>0.021982967582948865</v>
+        <v>0.02221630576994141</v>
       </c>
       <c r="R162">
-        <v>0.29876928801805364</v>
+        <v>0.19579558451834678</v>
       </c>
       <c r="S162">
-        <v>0.4583727040876286</v>
+        <v>0.5906120884510039</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>bird2</v>
+        <v>canary2</v>
       </c>
       <c r="B163">
-        <v>0.08267418035140611</v>
+        <v>0.9126741803514061</v>
       </c>
       <c r="C163">
-        <v>0.0988312224180995</v>
+        <v>0.8488312224180995</v>
       </c>
       <c r="D163">
-        <v>0.08458677898431918</v>
+        <v>0.10458677898431919</v>
       </c>
       <c r="E163">
-        <v>0.24111692061516415</v>
+        <v>0.19397038937507263</v>
       </c>
       <c r="F163">
         <v>0.004226771789817552</v>
       </c>
       <c r="G163">
-        <v>0.7546563075950183</v>
+        <v>0.8018028388351099</v>
       </c>
       <c r="H163">
         <v>0.5670223796863092</v>
       </c>
       <c r="I163">
-        <v>0.26257210956362886</v>
+        <v>0.2825721095636288</v>
       </c>
       <c r="J163">
         <v>0.9297826581309584</v>
       </c>
       <c r="K163">
-        <v>0.4255615598328881</v>
+        <v>0.37556155983288814</v>
       </c>
       <c r="L163">
         <v>0.7830865325117607</v>
@@ -10005,51 +10005,51 @@
         <v>0.014775146899501915</v>
       </c>
       <c r="P163">
-        <v>0.2240799194615491</v>
+        <v>0.1953641342217237</v>
       </c>
       <c r="Q163">
-        <v>0.005812827270677139</v>
+        <v>0.005872958648634024</v>
       </c>
       <c r="R163">
-        <v>0.26684167317130586</v>
+        <v>0.16615603521727046</v>
       </c>
       <c r="S163">
-        <v>0.5032655800964679</v>
+        <v>0.6326068719123719</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>bird3</v>
+        <v>canary3</v>
       </c>
       <c r="B164">
-        <v>0.07997692179239663</v>
+        <v>0.9099769217923965</v>
       </c>
       <c r="C164">
-        <v>0.07054622064922168</v>
+        <v>0.8205462206492217</v>
       </c>
       <c r="D164">
-        <v>0.07842182195056763</v>
+        <v>0.09842182195056763</v>
       </c>
       <c r="E164">
-        <v>0.270074108233843</v>
+        <v>0.2196967522676074</v>
       </c>
       <c r="F164">
         <v>0</v>
       </c>
       <c r="G164">
-        <v>0.729925891766157</v>
+        <v>0.7803032477323927</v>
       </c>
       <c r="H164">
         <v>0.6213023740849997</v>
       </c>
       <c r="I164">
-        <v>0.25045057072338384</v>
+        <v>0.2704505707233838</v>
       </c>
       <c r="J164">
         <v>0.9377639886361322</v>
       </c>
       <c r="K164">
-        <v>0.4507370387307992</v>
+        <v>0.4007370387307992</v>
       </c>
       <c r="L164">
         <v>0.7941257618984735</v>
@@ -10064,51 +10064,51 @@
         <v>0.0003621650645877338</v>
       </c>
       <c r="P164">
-        <v>0.22419322651002527</v>
+        <v>0.19779518576680513</v>
       </c>
       <c r="Q164">
-        <v>0.03426785406764648</v>
+        <v>0.03459374282060283</v>
       </c>
       <c r="R164">
-        <v>0.2633816273987323</v>
+        <v>0.17078597162188672</v>
       </c>
       <c r="S164">
-        <v>0.4781572920235959</v>
+        <v>0.5968250997907053</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>bird4</v>
+        <v>canary4</v>
       </c>
       <c r="B165">
-        <v>0.17114545464628614</v>
+        <v>1</v>
       </c>
       <c r="C165">
-        <v>0.10230999881391746</v>
+        <v>0.8523099988139174</v>
       </c>
       <c r="D165">
-        <v>0.0593625801829132</v>
+        <v>0.0793625801829132</v>
       </c>
       <c r="E165">
-        <v>0.27608981184913334</v>
+        <v>0.2266346112866855</v>
       </c>
       <c r="F165">
         <v>0</v>
       </c>
       <c r="G165">
-        <v>0.7239101881508666</v>
+        <v>0.7733653887133145</v>
       </c>
       <c r="H165">
         <v>0.6308471856315294</v>
       </c>
       <c r="I165">
-        <v>0.27118918529052777</v>
+        <v>0.29118918529052773</v>
       </c>
       <c r="J165">
         <v>0.9402879069779856</v>
       </c>
       <c r="K165">
-        <v>0.41654536234146233</v>
+        <v>0.36654536234146234</v>
       </c>
       <c r="L165">
         <v>0.830309711933934</v>
@@ -10123,39 +10123,39 @@
         <v>0</v>
       </c>
       <c r="P165">
-        <v>0.23024577826300038</v>
+        <v>0.20375850774785076</v>
       </c>
       <c r="Q165">
         <v>0</v>
       </c>
       <c r="R165">
-        <v>0.30608081466775044</v>
+        <v>0.2133774773828746</v>
       </c>
       <c r="S165">
-        <v>0.46367340706924925</v>
+        <v>0.5828640148692745</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>bird5</v>
+        <v>canary5</v>
       </c>
       <c r="B166">
-        <v>0.14821724971034442</v>
+        <v>0.9782172497103444</v>
       </c>
       <c r="C166">
-        <v>0.10016637588766038</v>
+        <v>0.8501663758876603</v>
       </c>
       <c r="D166">
-        <v>0.11124264202521922</v>
+        <v>0.13124264202521924</v>
       </c>
       <c r="E166">
-        <v>0.22100509600179793</v>
+        <v>0.1712757572453874</v>
       </c>
       <c r="F166">
         <v>0.02446859667973102</v>
       </c>
       <c r="G166">
-        <v>0.754526307318471</v>
+        <v>0.8042556460748816</v>
       </c>
       <c r="H166">
         <v>0</v>
@@ -10167,7 +10167,7 @@
         <v>0</v>
       </c>
       <c r="K166">
-        <v>0.43250534686714337</v>
+        <v>0.3825053468671434</v>
       </c>
       <c r="L166">
         <v>0.8005356013183142</v>
@@ -10182,51 +10182,51 @@
         <v>0</v>
       </c>
       <c r="P166">
-        <v>0.21522330006538157</v>
+        <v>0.18832344717922225</v>
       </c>
       <c r="Q166">
         <v>0</v>
       </c>
       <c r="R166">
-        <v>0.25445993433115044</v>
+        <v>0.16032183195877053</v>
       </c>
       <c r="S166">
-        <v>0.5303167656034681</v>
+        <v>0.6513547208620071</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>bird6</v>
+        <v>canary6</v>
       </c>
       <c r="B167">
-        <v>0.12003460836755354</v>
+        <v>0.9500346083675535</v>
       </c>
       <c r="C167">
-        <v>0.12596753136423827</v>
+        <v>0.8759675313642382</v>
       </c>
       <c r="D167">
-        <v>0.026437377120823696</v>
+        <v>0.0464373771208237</v>
       </c>
       <c r="E167">
-        <v>0.25306001448566207</v>
+        <v>0.20240323288386636</v>
       </c>
       <c r="F167">
         <v>0.013814790295486398</v>
       </c>
       <c r="G167">
-        <v>0.7331251952188516</v>
+        <v>0.7837819768206473</v>
       </c>
       <c r="H167">
         <v>0.6276519452815726</v>
       </c>
       <c r="I167">
-        <v>0.27514405351003285</v>
+        <v>0.2951440535100328</v>
       </c>
       <c r="J167">
         <v>0.9971833057794539</v>
       </c>
       <c r="K167">
-        <v>0.4248777060556741</v>
+        <v>0.37487770605567405</v>
       </c>
       <c r="L167">
         <v>0.7660207572415562</v>
@@ -10241,21 +10241,21 @@
         <v>0.0031709983278022896</v>
       </c>
       <c r="P167">
-        <v>0.21111683885768137</v>
+        <v>0.18375432169271116</v>
       </c>
       <c r="Q167">
-        <v>0.03163193032918213</v>
+        <v>0.03194228009522929</v>
       </c>
       <c r="R167">
-        <v>0.315574957961022</v>
+        <v>0.22055833979006947</v>
       </c>
       <c r="S167">
-        <v>0.4416762728521144</v>
+        <v>0.5637450584219901</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>bird7</v>
+        <v>canary7</v>
       </c>
       <c r="B168">
         <v>0</v>
@@ -10267,25 +10267,25 @@
         <v>0</v>
       </c>
       <c r="E168">
-        <v>0.21870261054391002</v>
+        <v>0.16542125077331662</v>
       </c>
       <c r="F168">
         <v>0</v>
       </c>
       <c r="G168">
-        <v>0.78129738945609</v>
+        <v>0.8345787492266834</v>
       </c>
       <c r="H168">
         <v>0.5413839195049093</v>
       </c>
       <c r="I168">
-        <v>0.2816739103954417</v>
+        <v>0.30167391039544167</v>
       </c>
       <c r="J168">
         <v>0.9719211330371578</v>
       </c>
       <c r="K168">
-        <v>0.4060896387306083</v>
+        <v>0.35608963873060834</v>
       </c>
       <c r="L168">
         <v>0.780550970392107</v>
@@ -10300,51 +10300,51 @@
         <v>0</v>
       </c>
       <c r="P168">
-        <v>0.20010302300007637</v>
+        <v>0.17246501427906363</v>
       </c>
       <c r="Q168">
         <v>0</v>
       </c>
       <c r="R168">
-        <v>0.3187268681813187</v>
+        <v>0.22316224082334632</v>
       </c>
       <c r="S168">
-        <v>0.48117010881860495</v>
+        <v>0.6043727448975901</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>bird8</v>
+        <v>canary8</v>
       </c>
       <c r="B169">
-        <v>0.10470470238166482</v>
+        <v>0.9347047023816648</v>
       </c>
       <c r="C169">
-        <v>0.08645768405320708</v>
+        <v>0.8364576840532071</v>
       </c>
       <c r="D169">
-        <v>0.07372824566242187</v>
+        <v>0.09372824566242187</v>
       </c>
       <c r="E169">
-        <v>0.21288227458030734</v>
+        <v>0.1623990305539764</v>
       </c>
       <c r="F169">
         <v>0</v>
       </c>
       <c r="G169">
-        <v>0.7871177254196927</v>
+        <v>0.8376009694460236</v>
       </c>
       <c r="H169">
         <v>0.5458483274419117</v>
       </c>
       <c r="I169">
-        <v>0.2858208109625365</v>
+        <v>0.30582081096253644</v>
       </c>
       <c r="J169">
         <v>0.9375091954507719</v>
       </c>
       <c r="K169">
-        <v>0.46462169419090793</v>
+        <v>0.41462169419090794</v>
       </c>
       <c r="L169">
         <v>0.7660915993478167</v>
@@ -10359,51 +10359,51 @@
         <v>0</v>
       </c>
       <c r="P169">
-        <v>0.2653219842855844</v>
+        <v>0.23741446358142204</v>
       </c>
       <c r="Q169">
-        <v>0.023685057894896142</v>
+        <v>0.02392676505010155</v>
       </c>
       <c r="R169">
-        <v>0.2527909964524994</v>
+        <v>0.1533202596742844</v>
       </c>
       <c r="S169">
-        <v>0.45820196136702</v>
+        <v>0.585338511694192</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>bird9</v>
+        <v>canary9</v>
       </c>
       <c r="B170">
-        <v>0.1488325347834967</v>
+        <v>0.9788325347834966</v>
       </c>
       <c r="C170">
-        <v>0.04511772870825942</v>
+        <v>0.7951177287082594</v>
       </c>
       <c r="D170">
-        <v>0.07866302831541326</v>
+        <v>0.09866302831541326</v>
       </c>
       <c r="E170">
-        <v>0.2818693997306132</v>
+        <v>0.2322222458458087</v>
       </c>
       <c r="F170">
         <v>0.01251817417864373</v>
       </c>
       <c r="G170">
-        <v>0.7056124260907432</v>
+        <v>0.7552595799755477</v>
       </c>
       <c r="H170">
         <v>0.6035763008003275</v>
       </c>
       <c r="I170">
-        <v>0.27712204852731914</v>
+        <v>0.2971220485273191</v>
       </c>
       <c r="J170">
         <v>0.945604077212533</v>
       </c>
       <c r="K170">
-        <v>0.4436782139752127</v>
+        <v>0.3936782139752127</v>
       </c>
       <c r="L170">
         <v>0.7688385482643663</v>
@@ -10418,51 +10418,51 @@
         <v>0</v>
       </c>
       <c r="P170">
-        <v>0.2087576214885781</v>
+        <v>0.17766073763766918</v>
       </c>
       <c r="Q170">
         <v>0</v>
       </c>
       <c r="R170">
-        <v>0.271962071026928</v>
+        <v>0.16358321152571825</v>
       </c>
       <c r="S170">
-        <v>0.519280307484494</v>
+        <v>0.6587560508366126</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>bird10</v>
+        <v>canary10</v>
       </c>
       <c r="B171">
-        <v>0.1367806870814189</v>
+        <v>0.9667806870814188</v>
       </c>
       <c r="C171">
-        <v>0.08723386618495516</v>
+        <v>0.8372338661849551</v>
       </c>
       <c r="D171">
-        <v>0.10219996777925078</v>
+        <v>0.12219996777925078</v>
       </c>
       <c r="E171">
-        <v>0.2253068275136487</v>
+        <v>0.17165074690311705</v>
       </c>
       <c r="F171">
         <v>0.016104339476778567</v>
       </c>
       <c r="G171">
-        <v>0.7585888330095727</v>
+        <v>0.8122449136201044</v>
       </c>
       <c r="H171">
         <v>0.6357663301890631</v>
       </c>
       <c r="I171">
-        <v>0.25684405468328536</v>
+        <v>0.2768440546832853</v>
       </c>
       <c r="J171">
         <v>0.9188240210243799</v>
       </c>
       <c r="K171">
-        <v>0.44253483586625764</v>
+        <v>0.39253483586625765</v>
       </c>
       <c r="L171">
         <v>0.7850841814280323</v>
@@ -10491,37 +10491,37 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>bird11</v>
+        <v>canary11</v>
       </c>
       <c r="B172">
-        <v>0.06351962223911006</v>
+        <v>0.89351962223911</v>
       </c>
       <c r="C172">
-        <v>0.11329227169252899</v>
+        <v>0.863292271692529</v>
       </c>
       <c r="D172">
-        <v>0.03876977448055085</v>
+        <v>0.05876977448055085</v>
       </c>
       <c r="E172">
-        <v>0.26615858707524775</v>
+        <v>0.21957826403537076</v>
       </c>
       <c r="F172">
-        <v>0.027645379218352088</v>
+        <v>0.02764537921835208</v>
       </c>
       <c r="G172">
-        <v>0.7061960337064003</v>
+        <v>0.7527763567462771</v>
       </c>
       <c r="H172">
         <v>0.6283180115511027</v>
       </c>
       <c r="I172">
-        <v>0.3318821309945499</v>
+        <v>0.35188213099454985</v>
       </c>
       <c r="J172">
         <v>0.9379113795058067</v>
       </c>
       <c r="K172">
-        <v>0.4964623511295206</v>
+        <v>0.4464623511295206</v>
       </c>
       <c r="L172">
         <v>0.7652541495443028</v>
@@ -10536,51 +10536,51 @@
         <v>0.005426863999632595</v>
       </c>
       <c r="P172">
-        <v>0.23649149629541236</v>
+        <v>0.2092392679238441</v>
       </c>
       <c r="Q172">
         <v>0</v>
       </c>
       <c r="R172">
-        <v>0.31180245300241155</v>
+        <v>0.216262681112544</v>
       </c>
       <c r="S172">
-        <v>0.4517060507021762</v>
+        <v>0.5744980509636118</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>bird12</v>
+        <v>canary12</v>
       </c>
       <c r="B173">
-        <v>0.12891028051144526</v>
+        <v>0.9589102805114452</v>
       </c>
       <c r="C173">
-        <v>0.1064559288144504</v>
+        <v>0.8564559288144504</v>
       </c>
       <c r="D173">
-        <v>0.14251838641953204</v>
+        <v>0.16251838641953203</v>
       </c>
       <c r="E173">
-        <v>0.24601470655079638</v>
+        <v>0.19642197728781005</v>
       </c>
       <c r="F173">
         <v>0</v>
       </c>
       <c r="G173">
-        <v>0.7539852934492036</v>
+        <v>0.8035780227121899</v>
       </c>
       <c r="H173">
         <v>0.5899669748705226</v>
       </c>
       <c r="I173">
-        <v>0.2667187542800027</v>
+        <v>0.28671875428000265</v>
       </c>
       <c r="J173">
         <v>0.9421494495227924</v>
       </c>
       <c r="K173">
-        <v>0.4775481383265716</v>
+        <v>0.4275481383265716</v>
       </c>
       <c r="L173">
         <v>0.8380323094821754</v>
@@ -10595,51 +10595,51 @@
         <v>0</v>
       </c>
       <c r="P173">
-        <v>0.18556171374325905</v>
+        <v>0.15425167459105465</v>
       </c>
       <c r="Q173">
         <v>0</v>
       </c>
       <c r="R173">
-        <v>0.3235380555961248</v>
+        <v>0.2158894339107449</v>
       </c>
       <c r="S173">
-        <v>0.4909002306606162</v>
+        <v>0.6298588914982004</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>bird13</v>
+        <v>canary13</v>
       </c>
       <c r="B174">
-        <v>0.08836315284593424</v>
+        <v>0.9183631528459342</v>
       </c>
       <c r="C174">
-        <v>0.11407472131456266</v>
+        <v>0.8640747213145626</v>
       </c>
       <c r="D174">
-        <v>0.05547427701241578</v>
+        <v>0.07547427701241578</v>
       </c>
       <c r="E174">
-        <v>0.21905396590965032</v>
+        <v>0.166886493263809</v>
       </c>
       <c r="F174">
         <v>0</v>
       </c>
       <c r="G174">
-        <v>0.7809460340903498</v>
+        <v>0.833113506736191</v>
       </c>
       <c r="H174">
         <v>0.5708561764534741</v>
       </c>
       <c r="I174">
-        <v>0.28046590808163985</v>
+        <v>0.3004659080816398</v>
       </c>
       <c r="J174">
         <v>0.9301655740968563</v>
       </c>
       <c r="K174">
-        <v>0.4415832690009448</v>
+        <v>0.3915832690009448</v>
       </c>
       <c r="L174">
         <v>0.8079284211790244</v>
@@ -10654,51 +10654,51 @@
         <v>0.013274157855074112</v>
       </c>
       <c r="P174">
-        <v>0.2876377050335736</v>
+        <v>0.261464936397071</v>
       </c>
       <c r="Q174">
         <v>0</v>
       </c>
       <c r="R174">
-        <v>0.2702095673400958</v>
+        <v>0.17632256915100766</v>
       </c>
       <c r="S174">
-        <v>0.44215272762633057</v>
+        <v>0.5622124944519212</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>bird14</v>
+        <v>canary14</v>
       </c>
       <c r="B175">
-        <v>0.1003249727892571</v>
+        <v>0.9303249727892571</v>
       </c>
       <c r="C175">
-        <v>0.0932196027389657</v>
+        <v>0.8432196027389657</v>
       </c>
       <c r="D175">
-        <v>0.08850348878827728</v>
+        <v>0.10850348878827729</v>
       </c>
       <c r="E175">
-        <v>0.2385186138987701</v>
+        <v>0.19128716773473908</v>
       </c>
       <c r="F175">
         <v>0.007904694292644452</v>
       </c>
       <c r="G175">
-        <v>0.7535766918085854</v>
+        <v>0.8008081379726165</v>
       </c>
       <c r="H175">
         <v>0.6139145132129612</v>
       </c>
       <c r="I175">
-        <v>0.3459737733455841</v>
+        <v>0.36597377334558406</v>
       </c>
       <c r="J175">
         <v>0.9658177285231406</v>
       </c>
       <c r="K175">
-        <v>0.46263240335774003</v>
+        <v>0.41263240335774</v>
       </c>
       <c r="L175">
         <v>0.7733540127217507</v>
@@ -10713,51 +10713,51 @@
         <v>0</v>
       </c>
       <c r="P175">
-        <v>0.1833785783696525</v>
+        <v>0.15743807042683247</v>
       </c>
       <c r="Q175">
-        <v>0.05309985205257547</v>
+        <v>0.05358889084328917</v>
       </c>
       <c r="R175">
-        <v>0.3057676093437533</v>
+        <v>0.21648570926369196</v>
       </c>
       <c r="S175">
-        <v>0.45775396023401865</v>
+        <v>0.5724873294661864</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>bird15</v>
+        <v>canary15</v>
       </c>
       <c r="B176">
-        <v>0.13183272938058269</v>
+        <v>0.9618327293805826</v>
       </c>
       <c r="C176">
-        <v>0.13249722541444242</v>
+        <v>0.8824972254144424</v>
       </c>
       <c r="D176">
-        <v>0.10119215050113572</v>
+        <v>0.12119215050113574</v>
       </c>
       <c r="E176">
-        <v>0.20784977260324394</v>
+        <v>0.1546695048324409</v>
       </c>
       <c r="F176">
         <v>0</v>
       </c>
       <c r="G176">
-        <v>0.7921502273967561</v>
+        <v>0.8453304951675592</v>
       </c>
       <c r="H176">
         <v>0.5931124573600607</v>
       </c>
       <c r="I176">
-        <v>0.26905014881273187</v>
+        <v>0.28905014881273183</v>
       </c>
       <c r="J176">
         <v>0.9241468393357989</v>
       </c>
       <c r="K176">
-        <v>0.46422547579787427</v>
+        <v>0.4142254757978743</v>
       </c>
       <c r="L176">
         <v>0.7755599640905464</v>
@@ -10772,51 +10772,51 @@
         <v>0.025187595398541065</v>
       </c>
       <c r="P176">
-        <v>0.23079680197681648</v>
+        <v>0.2044291238522984</v>
       </c>
       <c r="Q176">
-        <v>0.006423205146972662</v>
+        <v>0.006484365341343383</v>
       </c>
       <c r="R176">
-        <v>0.278346567254514</v>
+        <v>0.18577935198633228</v>
       </c>
       <c r="S176">
-        <v>0.484433425621697</v>
+        <v>0.603307158820026</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>bird16</v>
+        <v>canary16</v>
       </c>
       <c r="B177">
-        <v>0.16843159836713414</v>
+        <v>0.9984315983671341</v>
       </c>
       <c r="C177">
-        <v>0.1357567018483691</v>
+        <v>0.8857567018483691</v>
       </c>
       <c r="D177">
-        <v>0.11130729766334738</v>
+        <v>0.13130729766334737</v>
       </c>
       <c r="E177">
-        <v>0.25801316751551745</v>
+        <v>0.20786798035939436</v>
       </c>
       <c r="F177">
         <v>0.0052616724807724195</v>
       </c>
       <c r="G177">
-        <v>0.7367251600037101</v>
+        <v>0.7868703471598333</v>
       </c>
       <c r="H177">
         <v>0.6181400742661892</v>
       </c>
       <c r="I177">
-        <v>0.31020661209184675</v>
+        <v>0.33020661209184676</v>
       </c>
       <c r="J177">
         <v>0.9703135542773097</v>
       </c>
       <c r="K177">
-        <v>0.4367830641024557</v>
+        <v>0.3867830641024557</v>
       </c>
       <c r="L177">
         <v>0.800324530071689</v>
@@ -10845,37 +10845,37 @@
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>bird17</v>
+        <v>canary17</v>
       </c>
       <c r="B178">
-        <v>0.10178262927584643</v>
+        <v>0.9317826292758464</v>
       </c>
       <c r="C178">
-        <v>0.10898786667958354</v>
+        <v>0.8589878666795835</v>
       </c>
       <c r="D178">
-        <v>0.09066478341718205</v>
+        <v>0.11066478341718206</v>
       </c>
       <c r="E178">
-        <v>0.2396752390451609</v>
+        <v>0.1869230655151749</v>
       </c>
       <c r="F178">
         <v>0</v>
       </c>
       <c r="G178">
-        <v>0.760324760954839</v>
+        <v>0.8130769344848251</v>
       </c>
       <c r="H178">
         <v>0.567161136290717</v>
       </c>
       <c r="I178">
-        <v>0.2684847795740403</v>
+        <v>0.2884847795740403</v>
       </c>
       <c r="J178">
         <v>0.971528792199867</v>
       </c>
       <c r="K178">
-        <v>0.4892563145187603</v>
+        <v>0.4392563145187603</v>
       </c>
       <c r="L178">
         <v>0.8046498458058374</v>
@@ -10890,51 +10890,51 @@
         <v>0</v>
       </c>
       <c r="P178">
-        <v>0.24395767019604114</v>
+        <v>0.21773921434383728</v>
       </c>
       <c r="Q178">
         <v>0</v>
       </c>
       <c r="R178">
-        <v>0.3058783703499449</v>
+        <v>0.21365739927692307</v>
       </c>
       <c r="S178">
-        <v>0.45016395945401394</v>
+        <v>0.5686033863792397</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>bird18</v>
+        <v>canary18</v>
       </c>
       <c r="B179">
-        <v>0.09122669803109662</v>
+        <v>0.9212266980310966</v>
       </c>
       <c r="C179">
-        <v>0.12869582058267864</v>
+        <v>0.8786958205826786</v>
       </c>
       <c r="D179">
-        <v>0.007415478086089541</v>
+        <v>0.027415478086089545</v>
       </c>
       <c r="E179">
-        <v>0.2808084507989349</v>
+        <v>0.23697279185232217</v>
       </c>
       <c r="F179">
         <v>0.019167356587261236</v>
       </c>
       <c r="G179">
-        <v>0.7000241926138039</v>
+        <v>0.7438598515604167</v>
       </c>
       <c r="H179">
         <v>0.6036973445365394</v>
       </c>
       <c r="I179">
-        <v>0.2632154563583995</v>
+        <v>0.28321545635839945</v>
       </c>
       <c r="J179">
         <v>0.9569990108676407</v>
       </c>
       <c r="K179">
-        <v>0.41575986150104255</v>
+        <v>0.36575986150104256</v>
       </c>
       <c r="L179">
         <v>0.8008385582699848</v>
@@ -10949,51 +10949,51 @@
         <v>0</v>
       </c>
       <c r="P179">
-        <v>0.21154515078937666</v>
+        <v>0.18362091459921875</v>
       </c>
       <c r="Q179">
         <v>0</v>
       </c>
       <c r="R179">
-        <v>0.30780677228302367</v>
+        <v>0.2107468923398234</v>
       </c>
       <c r="S179">
-        <v>0.4806480769275998</v>
+        <v>0.6056321930609578</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>bird19</v>
+        <v>canary19</v>
       </c>
       <c r="B180">
-        <v>0.12473392318466256</v>
+        <v>0.9547339231846625</v>
       </c>
       <c r="C180">
-        <v>0.06960812611029579</v>
+        <v>0.8196081261102958</v>
       </c>
       <c r="D180">
-        <v>0.05858017523969915</v>
+        <v>0.07858017523969915</v>
       </c>
       <c r="E180">
-        <v>0.2853236730421592</v>
+        <v>0.23327422528471908</v>
       </c>
       <c r="F180">
         <v>0</v>
       </c>
       <c r="G180">
-        <v>0.7146763269578407</v>
+        <v>0.7667257747152809</v>
       </c>
       <c r="H180">
         <v>0.6286457086196464</v>
       </c>
       <c r="I180">
-        <v>0.2780653056151852</v>
+        <v>0.2980653056151852</v>
       </c>
       <c r="J180">
         <v>0.9237979657789603</v>
       </c>
       <c r="K180">
-        <v>0.43751037617342003</v>
+        <v>0.38751037617342005</v>
       </c>
       <c r="L180">
         <v>0.7762109580726972</v>
@@ -11008,51 +11008,51 @@
         <v>0</v>
       </c>
       <c r="P180">
-        <v>0.2521496844017992</v>
+        <v>0.22591136682582572</v>
       </c>
       <c r="Q180">
-        <v>0.0138673925643991</v>
+        <v>0.013999807728351066</v>
       </c>
       <c r="R180">
-        <v>0.2926127162554535</v>
+        <v>0.19992007250480306</v>
       </c>
       <c r="S180">
-        <v>0.4413702067783481</v>
+        <v>0.56016875294102</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>bird20</v>
+        <v>canary20</v>
       </c>
       <c r="B181">
-        <v>0.062413673163530664</v>
+        <v>0.8924136731635306</v>
       </c>
       <c r="C181">
-        <v>0.10251782758256675</v>
+        <v>0.8525178275825667</v>
       </c>
       <c r="D181">
-        <v>0.09823474225277379</v>
+        <v>0.11823474225277379</v>
       </c>
       <c r="E181">
-        <v>0.2769962484580049</v>
+        <v>0.22940240262744901</v>
       </c>
       <c r="F181">
         <v>0.0034354491835399074</v>
       </c>
       <c r="G181">
-        <v>0.7195683023584551</v>
+        <v>0.7671621481890112</v>
       </c>
       <c r="H181">
         <v>0.6110053809350039</v>
       </c>
       <c r="I181">
-        <v>0.31089591329355404</v>
+        <v>0.330895913293554</v>
       </c>
       <c r="J181">
         <v>0.9632742240574751</v>
       </c>
       <c r="K181">
-        <v>0.4679131217251586</v>
+        <v>0.4179131217251586</v>
       </c>
       <c r="L181">
         <v>0.7636501031021307</v>
@@ -11067,57 +11067,57 @@
         <v>0</v>
       </c>
       <c r="P181">
-        <v>0.21460652112519937</v>
+        <v>0.18728231356456732</v>
       </c>
       <c r="Q181">
         <v>0</v>
       </c>
       <c r="R181">
-        <v>0.2646639121386307</v>
+        <v>0.1691620213089394</v>
       </c>
       <c r="S181">
-        <v>0.5207295667361699</v>
+        <v>0.6435556651264931</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>sunfish1</v>
+        <v>bird1</v>
       </c>
       <c r="B182">
-        <v>0.4190882184399566</v>
+        <v>0.13908821843995656</v>
       </c>
       <c r="C182">
-        <v>0.6719910716542635</v>
+        <v>0.17199107165426353</v>
       </c>
       <c r="D182">
-        <v>0.7816294189745598</v>
+        <v>0.11162941897455979</v>
       </c>
       <c r="E182">
-        <v>0</v>
+        <v>0.2360674810997062</v>
       </c>
       <c r="F182">
-        <v>1</v>
+        <v>0.005379053092516303</v>
       </c>
       <c r="G182">
-        <v>0</v>
+        <v>0.7585534658077775</v>
       </c>
       <c r="H182">
-        <v>0.8466655425903122</v>
+        <v>0.5966655425903122</v>
       </c>
       <c r="I182">
-        <v>0.18466273788718574</v>
+        <v>0.26466273788718575</v>
       </c>
       <c r="J182">
-        <v>0.09263739336590107</v>
+        <v>0.9926373933659011</v>
       </c>
       <c r="K182">
-        <v>0.014257260120375221</v>
+        <v>0.4642572601203752</v>
       </c>
       <c r="L182">
-        <v>0</v>
+        <v>0.7638243532553353</v>
       </c>
       <c r="M182">
-        <v>0.7087517094513168</v>
+        <v>0.008751709451316855</v>
       </c>
       <c r="N182">
         <v>0.027203619339711178</v>
@@ -11126,57 +11126,57 @@
         <v>0</v>
       </c>
       <c r="P182">
-        <v>0</v>
+        <v>0.21389808186372847</v>
       </c>
       <c r="Q182">
-        <v>1</v>
+        <v>0.009319581963992261</v>
       </c>
       <c r="R182">
-        <v>0</v>
+        <v>0.30221271828942814</v>
       </c>
       <c r="S182">
-        <v>0</v>
+        <v>0.47456961788285107</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>sunfish2</v>
+        <v>bird2</v>
       </c>
       <c r="B183">
-        <v>0.3652686165873016</v>
+        <v>0.08526861658730153</v>
       </c>
       <c r="C183">
-        <v>0.5778585888007557</v>
+        <v>0.07785858880075573</v>
       </c>
       <c r="D183">
-        <v>0.729688011967078</v>
+        <v>0.059688011967078056</v>
       </c>
       <c r="E183">
-        <v>0.024694246144711086</v>
+        <v>0.25751584702587244</v>
       </c>
       <c r="F183">
-        <v>0.9414369404695753</v>
+        <v>0.009758124459310055</v>
       </c>
       <c r="G183">
-        <v>0.03386881338571353</v>
+        <v>0.7327260285148175</v>
       </c>
       <c r="H183">
-        <v>0.8571421192099428</v>
+        <v>0.6071421192099428</v>
       </c>
       <c r="I183">
-        <v>0.17108708480125118</v>
+        <v>0.2510870848012512</v>
       </c>
       <c r="J183">
-        <v>0</v>
+        <v>0.8840718762053624</v>
       </c>
       <c r="K183">
-        <v>0.034449092541571275</v>
+        <v>0.4844490925415713</v>
       </c>
       <c r="L183">
-        <v>0.007968323609717042</v>
+        <v>0.807968323609717</v>
       </c>
       <c r="M183">
-        <v>0.6595950134464563</v>
+        <v>0</v>
       </c>
       <c r="N183">
         <v>0.04540298830570372</v>
@@ -11185,57 +11185,57 @@
         <v>0.002843421010607623</v>
       </c>
       <c r="P183">
-        <v>0</v>
+        <v>0.21852492654547892</v>
       </c>
       <c r="Q183">
-        <v>1</v>
+        <v>0.02933927103133606</v>
       </c>
       <c r="R183">
-        <v>0</v>
+        <v>0.2925473895576237</v>
       </c>
       <c r="S183">
-        <v>0</v>
+        <v>0.4595884128655613</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>sunfish3</v>
+        <v>bird3</v>
       </c>
       <c r="B184">
-        <v>0.38675642450357006</v>
+        <v>0.10675642450357005</v>
       </c>
       <c r="C184">
-        <v>0.6223182784568398</v>
+        <v>0.12231827845683992</v>
       </c>
       <c r="D184">
-        <v>0.7425310484373078</v>
+        <v>0.07253104843730777</v>
       </c>
       <c r="E184">
-        <v>0</v>
+        <v>0.21662535640845593</v>
       </c>
       <c r="F184">
-        <v>0.9867718197585054</v>
+        <v>0</v>
       </c>
       <c r="G184">
-        <v>0.013228180241494625</v>
+        <v>0.7833746435915441</v>
       </c>
       <c r="H184">
-        <v>0.8195174174036388</v>
+        <v>0.5695174174036388</v>
       </c>
       <c r="I184">
-        <v>0.2119517434898344</v>
+        <v>0.2919517434898344</v>
       </c>
       <c r="J184">
-        <v>0.04546157540896323</v>
+        <v>0.9454615754089631</v>
       </c>
       <c r="K184">
-        <v>0.028505514572393892</v>
+        <v>0.4785055145723939</v>
       </c>
       <c r="L184">
-        <v>0.02896351292899505</v>
+        <v>0.8289635129289951</v>
       </c>
       <c r="M184">
-        <v>0.6998405072439983</v>
+        <v>0</v>
       </c>
       <c r="N184">
         <v>0.028066846670050993</v>
@@ -11244,57 +11244,57 @@
         <v>0.0013530337308508935</v>
       </c>
       <c r="P184">
-        <v>0</v>
+        <v>0.21545055769776364</v>
       </c>
       <c r="Q184">
-        <v>0.9563417834595279</v>
+        <v>0</v>
       </c>
       <c r="R184">
-        <v>0.036078797686927656</v>
+        <v>0.3208860652470806</v>
       </c>
       <c r="S184">
-        <v>0.0075794188535445095</v>
+        <v>0.4636633770551558</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>sunfish4</v>
+        <v>bird4</v>
       </c>
       <c r="B185">
-        <v>0.4457740944155159</v>
+        <v>0.16577409441551585</v>
       </c>
       <c r="C185">
-        <v>0.5934188040014993</v>
+        <v>0.09341880400149927</v>
       </c>
       <c r="D185">
-        <v>0.7478652297761323</v>
+        <v>0.07786522977613233</v>
       </c>
       <c r="E185">
-        <v>0.036110182737003886</v>
+        <v>0.28010218866416653</v>
       </c>
       <c r="F185">
-        <v>0.9638898172629962</v>
+        <v>0.0036998881726866364</v>
       </c>
       <c r="G185">
-        <v>0</v>
+        <v>0.7161979231631468</v>
       </c>
       <c r="H185">
-        <v>0.7969959344232881</v>
+        <v>0.5469959344232881</v>
       </c>
       <c r="I185">
-        <v>0.19986091298865452</v>
+        <v>0.2798609129886545</v>
       </c>
       <c r="J185">
-        <v>0.015235104969548961</v>
+        <v>0.915235104969549</v>
       </c>
       <c r="K185">
-        <v>0.03069261540346894</v>
+        <v>0.48069261540346897</v>
       </c>
       <c r="L185">
-        <v>0.005082841913844105</v>
+        <v>0.8050828419138442</v>
       </c>
       <c r="M185">
-        <v>0.7019198803427356</v>
+        <v>0.0019198803427356295</v>
       </c>
       <c r="N185">
         <v>0</v>
@@ -11303,57 +11303,57 @@
         <v>0</v>
       </c>
       <c r="P185">
-        <v>0</v>
+        <v>0.1974287044567389</v>
       </c>
       <c r="Q185">
-        <v>0.9965055662004965</v>
+        <v>0.02602926708785233</v>
       </c>
       <c r="R185">
-        <v>0</v>
+        <v>0.29447941808426453</v>
       </c>
       <c r="S185">
-        <v>0.003494433799503628</v>
+        <v>0.4820626103711442</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>sunfish5</v>
+        <v>bird5</v>
       </c>
       <c r="B186">
-        <v>0.45064693330880917</v>
+        <v>0.17064693330880915</v>
       </c>
       <c r="C186">
-        <v>0.6178312760763259</v>
+        <v>0.117831276076326</v>
       </c>
       <c r="D186">
-        <v>0.7271196244375913</v>
+        <v>0.05711962443759126</v>
       </c>
       <c r="E186">
-        <v>0.008233130087309285</v>
+        <v>0.2560391285826602</v>
       </c>
       <c r="F186">
-        <v>0.9913094347958127</v>
+        <v>0</v>
       </c>
       <c r="G186">
-        <v>0.0004574351168780559</v>
+        <v>0.7439608714173398</v>
       </c>
       <c r="H186">
-        <v>0.8695652831054892</v>
+        <v>0.6195652831054892</v>
       </c>
       <c r="I186">
-        <v>0.24213824748926271</v>
+        <v>0.32213824748926273</v>
       </c>
       <c r="J186">
-        <v>0.06856336352360537</v>
+        <v>0.9685633635236053</v>
       </c>
       <c r="K186">
-        <v>0.04593955023599605</v>
+        <v>0.49593955023599606</v>
       </c>
       <c r="L186">
-        <v>0</v>
+        <v>0.7684656821259839</v>
       </c>
       <c r="M186">
-        <v>0.694424663084772</v>
+        <v>0</v>
       </c>
       <c r="N186">
         <v>0</v>
@@ -11362,57 +11362,57 @@
         <v>0.02925760079164529</v>
       </c>
       <c r="P186">
-        <v>0</v>
+        <v>0.18397593961828354</v>
       </c>
       <c r="Q186">
-        <v>0.9713737477065901</v>
+        <v>0.015990864909636485</v>
       </c>
       <c r="R186">
-        <v>0.022908612394673646</v>
+        <v>0.3198114394119952</v>
       </c>
       <c r="S186">
-        <v>0.005717639898736408</v>
+        <v>0.48022175606008494</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>sunfish6</v>
+        <v>bird6</v>
       </c>
       <c r="B187">
-        <v>0.3983946635964604</v>
+        <v>0.11839466359646039</v>
       </c>
       <c r="C187">
-        <v>0.6060896217024356</v>
+        <v>0.10608962170243569</v>
       </c>
       <c r="D187">
-        <v>0.7257986249875574</v>
+        <v>0.05579862498755746</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>0.2252174740797978</v>
       </c>
       <c r="F187">
-        <v>0.9861479693056974</v>
+        <v>0.004986925767565239</v>
       </c>
       <c r="G187">
-        <v>0.013852030694302528</v>
+        <v>0.769795600152637</v>
       </c>
       <c r="H187">
-        <v>0.8215312720826162</v>
+        <v>0.5715312720826162</v>
       </c>
       <c r="I187">
-        <v>0.17786620728508198</v>
+        <v>0.25786620728508197</v>
       </c>
       <c r="J187">
-        <v>0.035973745951096696</v>
+        <v>0.9359737459510966</v>
       </c>
       <c r="K187">
-        <v>0</v>
+        <v>0.4096986739215863</v>
       </c>
       <c r="L187">
-        <v>0</v>
+        <v>0.7918245830937916</v>
       </c>
       <c r="M187">
-        <v>0.6781939111475036</v>
+        <v>0</v>
       </c>
       <c r="N187">
         <v>0.024049636524531164</v>
@@ -11421,57 +11421,57 @@
         <v>0.008418858767876333</v>
       </c>
       <c r="P187">
-        <v>0.020791224754734158</v>
+        <v>0.24106083953233373</v>
       </c>
       <c r="Q187">
-        <v>0.9750279207521642</v>
+        <v>0.025459242604182534</v>
       </c>
       <c r="R187">
-        <v>0</v>
+        <v>0.26896803417028775</v>
       </c>
       <c r="S187">
-        <v>0.004180854493101679</v>
+        <v>0.4645118836931959</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>sunfish7</v>
+        <v>bird7</v>
       </c>
       <c r="B188">
-        <v>0.44639503959401694</v>
+        <v>0.16639503959401694</v>
       </c>
       <c r="C188">
-        <v>0.6021508693797791</v>
+        <v>0.10215086937977912</v>
       </c>
       <c r="D188">
-        <v>0.7630930967103537</v>
+        <v>0.09309309671035376</v>
       </c>
       <c r="E188">
-        <v>0</v>
+        <v>0.2386334491538141</v>
       </c>
       <c r="F188">
-        <v>1</v>
+        <v>0.015430178523868401</v>
       </c>
       <c r="G188">
-        <v>0</v>
+        <v>0.7459363723223175</v>
       </c>
       <c r="H188">
-        <v>0.8579497738677404</v>
+        <v>0.6079497738677404</v>
       </c>
       <c r="I188">
-        <v>0.1770485025768797</v>
+        <v>0.2570485025768797</v>
       </c>
       <c r="J188">
-        <v>0.07927264733529601</v>
+        <v>0.979272647335296</v>
       </c>
       <c r="K188">
-        <v>0.019813360087596456</v>
+        <v>0.46981336008759644</v>
       </c>
       <c r="L188">
-        <v>0</v>
+        <v>0.788677486954579</v>
       </c>
       <c r="M188">
-        <v>0.6943804770808254</v>
+        <v>0</v>
       </c>
       <c r="N188">
         <v>0.00533806577969586</v>
@@ -11480,57 +11480,57 @@
         <v>0.02716002083776302</v>
       </c>
       <c r="P188">
-        <v>0</v>
+        <v>0.2059084582193373</v>
       </c>
       <c r="Q188">
-        <v>0.9856409340637823</v>
+        <v>0.0006000839536680962</v>
       </c>
       <c r="R188">
-        <v>0</v>
+        <v>0.28327195904308516</v>
       </c>
       <c r="S188">
-        <v>0.014359065936217615</v>
+        <v>0.5102194987839095</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>sunfish8</v>
+        <v>bird8</v>
       </c>
       <c r="B189">
-        <v>0.4064512794111924</v>
+        <v>0.12645127941119239</v>
       </c>
       <c r="C189">
-        <v>0.5782585250793942</v>
+        <v>0.07825852507939424</v>
       </c>
       <c r="D189">
-        <v>0.7579039597971554</v>
+        <v>0.08790395979715541</v>
       </c>
       <c r="E189">
-        <v>0.004017601542509756</v>
+        <v>0.2609173916840281</v>
       </c>
       <c r="F189">
-        <v>0.9959823984574904</v>
+        <v>0.018286500106839812</v>
       </c>
       <c r="G189">
-        <v>0</v>
+        <v>0.7207961082091321</v>
       </c>
       <c r="H189">
-        <v>0.8767162479112298</v>
+        <v>0.6267162479112298</v>
       </c>
       <c r="I189">
-        <v>0.24852074483557107</v>
+        <v>0.3285207448355711</v>
       </c>
       <c r="J189">
-        <v>0.09926084503242846</v>
+        <v>0.9992608450324284</v>
       </c>
       <c r="K189">
-        <v>0.022159811683880003</v>
+        <v>0.47215981168388</v>
       </c>
       <c r="L189">
-        <v>0.02376193343766463</v>
+        <v>0.8237619334376647</v>
       </c>
       <c r="M189">
-        <v>0.6943177496488857</v>
+        <v>0</v>
       </c>
       <c r="N189">
         <v>0.008137116228146135</v>
@@ -11539,57 +11539,57 @@
         <v>0.014990108956538368</v>
       </c>
       <c r="P189">
-        <v>0.05056439133440573</v>
+        <v>0.2666882268313796</v>
       </c>
       <c r="Q189">
-        <v>0.942142562974426</v>
+        <v>0</v>
       </c>
       <c r="R189">
-        <v>0.0072930456911682595</v>
+        <v>0.28968716241346154</v>
       </c>
       <c r="S189">
-        <v>0</v>
+        <v>0.44362461075515885</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>sunfish9</v>
+        <v>bird9</v>
       </c>
       <c r="B190">
-        <v>0.3635650563864305</v>
+        <v>0.08356505638643047</v>
       </c>
       <c r="C190">
-        <v>0.598877813107076</v>
+        <v>0.09887781310707604</v>
       </c>
       <c r="D190">
-        <v>0.7392574470480588</v>
+        <v>0.06925744704805882</v>
       </c>
       <c r="E190">
-        <v>0</v>
+        <v>0.25116938249688403</v>
       </c>
       <c r="F190">
-        <v>1</v>
+        <v>0.0428805224382078</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>0.7059500950649081</v>
       </c>
       <c r="H190">
-        <v>0.8465120647227546</v>
+        <v>0.5965120647227546</v>
       </c>
       <c r="I190">
-        <v>0.15935238908139399</v>
+        <v>0.239352389081394</v>
       </c>
       <c r="J190">
-        <v>0.034564110897707785</v>
+        <v>0.9345641108977077</v>
       </c>
       <c r="K190">
-        <v>0</v>
+        <v>0.40230880026510674</v>
       </c>
       <c r="L190">
-        <v>0</v>
+        <v>0.7879439916845069</v>
       </c>
       <c r="M190">
-        <v>0.7208125968923151</v>
+        <v>0.020812596892315165</v>
       </c>
       <c r="N190">
         <v>0.04214882999395367</v>
@@ -11598,57 +11598,57 @@
         <v>0</v>
       </c>
       <c r="P190">
-        <v>0.02224040657658222</v>
+        <v>0.2479005000872195</v>
       </c>
       <c r="Q190">
-        <v>0.9456840964479181</v>
+        <v>0.004324760720143403</v>
       </c>
       <c r="R190">
-        <v>0</v>
+        <v>0.2452440527840471</v>
       </c>
       <c r="S190">
-        <v>0.03207549697549967</v>
+        <v>0.5025306864085901</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>sunfish10</v>
+        <v>bird10</v>
       </c>
       <c r="B191">
-        <v>0.41541674215706476</v>
+        <v>0.13541674215706476</v>
       </c>
       <c r="C191">
-        <v>0.6304644130888458</v>
+        <v>0.13046441308884582</v>
       </c>
       <c r="D191">
-        <v>0.7553273302860747</v>
+        <v>0.08532733028607464</v>
       </c>
       <c r="E191">
-        <v>0.016530658604850697</v>
+        <v>0.2534244177566705</v>
       </c>
       <c r="F191">
-        <v>0.966408986999889</v>
+        <v>0.018240555545137586</v>
       </c>
       <c r="G191">
-        <v>0.01706035439526048</v>
+        <v>0.728335026698192</v>
       </c>
       <c r="H191">
-        <v>0.8444834790127875</v>
+        <v>0.5944834790127875</v>
       </c>
       <c r="I191">
-        <v>0.19235899725309222</v>
+        <v>0.27235899725309226</v>
       </c>
       <c r="J191">
-        <v>0.07327394996248088</v>
+        <v>0.9732739499624808</v>
       </c>
       <c r="K191">
-        <v>0</v>
+        <v>0.40421805089564505</v>
       </c>
       <c r="L191">
-        <v>0</v>
+        <v>0.7686898889073056</v>
       </c>
       <c r="M191">
-        <v>0.7308853173285104</v>
+        <v>0.030885317328510353</v>
       </c>
       <c r="N191">
         <v>0</v>
@@ -11657,57 +11657,57 @@
         <v>0.012414023818576056</v>
       </c>
       <c r="P191">
-        <v>0</v>
+        <v>0.20469220123286594</v>
       </c>
       <c r="Q191">
-        <v>0.9393581833639351</v>
+        <v>0</v>
       </c>
       <c r="R191">
-        <v>0.054581765917579746</v>
+        <v>0.3364998578687997</v>
       </c>
       <c r="S191">
-        <v>0.006060050718485395</v>
+        <v>0.45880794089833443</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>sunfish11</v>
+        <v>bird11</v>
       </c>
       <c r="B192">
-        <v>0.4017618551405996</v>
+        <v>0.12176185514059955</v>
       </c>
       <c r="C192">
-        <v>0.5957568941144665</v>
+        <v>0.09575689411446651</v>
       </c>
       <c r="D192">
-        <v>0.7255285197946291</v>
+        <v>0.055528519794629035</v>
       </c>
       <c r="E192">
-        <v>0</v>
+        <v>0.21110706956350045</v>
       </c>
       <c r="F192">
-        <v>0.9642510958771645</v>
+        <v>0</v>
       </c>
       <c r="G192">
-        <v>0.03574890412283545</v>
+        <v>0.7888929304364996</v>
       </c>
       <c r="H192">
-        <v>0.8624580206996657</v>
+        <v>0.6124580206996657</v>
       </c>
       <c r="I192">
-        <v>0.2160057768630926</v>
+        <v>0.29600577686309265</v>
       </c>
       <c r="J192">
-        <v>0.09997414530764726</v>
+        <v>0.9999741453076472</v>
       </c>
       <c r="K192">
-        <v>0.0009165644874412565</v>
+        <v>0.4509165644874413</v>
       </c>
       <c r="L192">
-        <v>0.022072080696758225</v>
+        <v>0.8220720806967583</v>
       </c>
       <c r="M192">
-        <v>0.7280770977950206</v>
+        <v>0.028077097795020697</v>
       </c>
       <c r="N192">
         <v>0.02039760923603954</v>
@@ -11716,57 +11716,57 @@
         <v>0</v>
       </c>
       <c r="P192">
-        <v>0</v>
+        <v>0.21642801593104638</v>
       </c>
       <c r="Q192">
-        <v>0.9486483212826805</v>
+        <v>0</v>
       </c>
       <c r="R192">
-        <v>0.05135167871731946</v>
+        <v>0.3573339542193753</v>
       </c>
       <c r="S192">
-        <v>0</v>
+        <v>0.42623802984957826</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>sunfish12</v>
+        <v>bird12</v>
       </c>
       <c r="B193">
-        <v>0.40762003002009756</v>
+        <v>0.1276200300200975</v>
       </c>
       <c r="C193">
-        <v>0.5737175589207073</v>
+        <v>0.07371755892070729</v>
       </c>
       <c r="D193">
-        <v>0.708480731684113</v>
+        <v>0.03848073168411293</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>0.19329710609831266</v>
       </c>
       <c r="F193">
-        <v>0.9783327108005929</v>
+        <v>0</v>
       </c>
       <c r="G193">
-        <v>0.02166728919940696</v>
+        <v>0.8067028939016873</v>
       </c>
       <c r="H193">
-        <v>0.8463510469414709</v>
+        <v>0.5963510469414709</v>
       </c>
       <c r="I193">
-        <v>0.23274218156755735</v>
+        <v>0.3127421815675574</v>
       </c>
       <c r="J193">
-        <v>0.05611966276467932</v>
+        <v>0.9561196627646793</v>
       </c>
       <c r="K193">
-        <v>0</v>
+        <v>0.4396009542148246</v>
       </c>
       <c r="L193">
-        <v>0.020977598202573153</v>
+        <v>0.8209775982025732</v>
       </c>
       <c r="M193">
-        <v>0.7359213146887728</v>
+        <v>0.03592131468877278</v>
       </c>
       <c r="N193">
         <v>0.03288586344309698</v>
@@ -11775,48 +11775,48 @@
         <v>0.010857748709900457</v>
       </c>
       <c r="P193">
-        <v>0</v>
+        <v>0.19683655983429027</v>
       </c>
       <c r="Q193">
-        <v>0.9764874059986102</v>
+        <v>0.0256152537739993</v>
       </c>
       <c r="R193">
-        <v>0.0020156910016054467</v>
+        <v>0.292097623500721</v>
       </c>
       <c r="S193">
-        <v>0.02149690299978444</v>
+        <v>0.48545056289098937</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>sunfish13</v>
+        <v>bird13</v>
       </c>
       <c r="B194">
-        <v>0.36712233032118324</v>
+        <v>0.0871223303211832</v>
       </c>
       <c r="C194">
-        <v>0.621343583446391</v>
+        <v>0.12134358344639094</v>
       </c>
       <c r="D194">
-        <v>0.7709682036977906</v>
+        <v>0.10096820369779066</v>
       </c>
       <c r="E194">
-        <v>0.014573845797290232</v>
+        <v>0.2597633283845217</v>
       </c>
       <c r="F194">
-        <v>0.9854261542027098</v>
+        <v>0.023190330262132172</v>
       </c>
       <c r="G194">
-        <v>0</v>
+        <v>0.7170463413533461</v>
       </c>
       <c r="H194">
-        <v>0.8159591306552112</v>
+        <v>0.5659591306552112</v>
       </c>
       <c r="I194">
-        <v>0.1722308335810056</v>
+        <v>0.2522308335810056</v>
       </c>
       <c r="J194">
-        <v>0.029629878167138676</v>
+        <v>0.9296298781671386</v>
       </c>
       <c r="K194">
         <v>0</v>
@@ -11834,30 +11834,30 @@
         <v>0</v>
       </c>
       <c r="P194">
-        <v>0.005843095795980765</v>
+        <v>0.22793474375521583</v>
       </c>
       <c r="Q194">
-        <v>0.9752911713689293</v>
+        <v>0</v>
       </c>
       <c r="R194">
-        <v>0.0035872539764980216</v>
+        <v>0.2933533428806569</v>
       </c>
       <c r="S194">
-        <v>0.015278478858591862</v>
+        <v>0.47871191336412716</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>sunfish14</v>
+        <v>bird14</v>
       </c>
       <c r="B195">
-        <v>0.39273768996720315</v>
+        <v>0.1127376899672031</v>
       </c>
       <c r="C195">
-        <v>0.5943871947655689</v>
+        <v>0.09438719476556894</v>
       </c>
       <c r="D195">
-        <v>0.7332833284391279</v>
+        <v>0.06328332843912793</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -11869,22 +11869,22 @@
         <v>0</v>
       </c>
       <c r="H195">
-        <v>0.8309254105278779</v>
+        <v>0.5809254105278779</v>
       </c>
       <c r="I195">
-        <v>0.19787543461170437</v>
+        <v>0.2778754346117044</v>
       </c>
       <c r="J195">
-        <v>0.09489108628424692</v>
+        <v>0.9948910862842468</v>
       </c>
       <c r="K195">
-        <v>0</v>
+        <v>0.41202839450596207</v>
       </c>
       <c r="L195">
-        <v>0.007675234465965288</v>
+        <v>0.8076752344659653</v>
       </c>
       <c r="M195">
-        <v>0.7102082754706297</v>
+        <v>0.010208275470629781</v>
       </c>
       <c r="N195">
         <v>0.0022666396783514913</v>
@@ -11893,57 +11893,57 @@
         <v>0</v>
       </c>
       <c r="P195">
-        <v>0.009623784586967889</v>
+        <v>0.23338097287611625</v>
       </c>
       <c r="Q195">
-        <v>0.9762331573841714</v>
+        <v>0</v>
       </c>
       <c r="R195">
-        <v>0.014143058028860756</v>
+        <v>0.3059604973737137</v>
       </c>
       <c r="S195">
-        <v>0</v>
+        <v>0.46065852975017</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>sunfish15</v>
+        <v>bird15</v>
       </c>
       <c r="B196">
-        <v>0.4218091794295013</v>
+        <v>0.14180917942950128</v>
       </c>
       <c r="C196">
-        <v>0.6026516259613215</v>
+        <v>0.1026516259613215</v>
       </c>
       <c r="D196">
-        <v>0.7562536472129068</v>
+        <v>0.08625364721290676</v>
       </c>
       <c r="E196">
-        <v>0</v>
+        <v>0.22975133521058294</v>
       </c>
       <c r="F196">
-        <v>0.964662868728126</v>
+        <v>0.03363126649110885</v>
       </c>
       <c r="G196">
-        <v>0.035337131271874093</v>
+        <v>0.7366173982983082</v>
       </c>
       <c r="H196">
-        <v>0.8175196999437387</v>
+        <v>0.5675196999437387</v>
       </c>
       <c r="I196">
-        <v>0.1239762890861883</v>
+        <v>0.2039762890861883</v>
       </c>
       <c r="J196">
-        <v>0.06256311554039329</v>
+        <v>0.9625631155403932</v>
       </c>
       <c r="K196">
-        <v>0.02045746874683785</v>
+        <v>0.47045746874683786</v>
       </c>
       <c r="L196">
-        <v>0</v>
+        <v>0.7979056157091478</v>
       </c>
       <c r="M196">
-        <v>0.6605691348506967</v>
+        <v>0</v>
       </c>
       <c r="N196">
         <v>0.0013028601857178802</v>
@@ -11952,57 +11952,57 @@
         <v>0</v>
       </c>
       <c r="P196">
-        <v>0</v>
+        <v>0.1977412704737867</v>
       </c>
       <c r="Q196">
-        <v>0.9861377330490642</v>
+        <v>0.0018944769973917562</v>
       </c>
       <c r="R196">
-        <v>0.013862266950935719</v>
+        <v>0.3183199754861398</v>
       </c>
       <c r="S196">
-        <v>0</v>
+        <v>0.4820442770426818</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>sunfish16</v>
+        <v>bird16</v>
       </c>
       <c r="B197">
-        <v>0.40238697398935325</v>
+        <v>0.1223869739893532</v>
       </c>
       <c r="C197">
-        <v>0.5950542684849452</v>
+        <v>0.09505426848494529</v>
       </c>
       <c r="D197">
-        <v>0.7527071090299653</v>
+        <v>0.08270710902996534</v>
       </c>
       <c r="E197">
-        <v>0.033389648840169775</v>
+        <v>0.27358746832041175</v>
       </c>
       <c r="F197">
-        <v>0.9666103511598303</v>
+        <v>0.02110605317009582</v>
       </c>
       <c r="G197">
-        <v>0</v>
+        <v>0.7053064785094924</v>
       </c>
       <c r="H197">
-        <v>0.8129308949625815</v>
+        <v>0.5629308949625815</v>
       </c>
       <c r="I197">
-        <v>0.20973670665925934</v>
+        <v>0.2897367066592593</v>
       </c>
       <c r="J197">
-        <v>0.02950078970182237</v>
+        <v>0.9295007897018224</v>
       </c>
       <c r="K197">
-        <v>0.004080793203177322</v>
+        <v>0.45408079320317735</v>
       </c>
       <c r="L197">
-        <v>0.0029651458042134395</v>
+        <v>0.8029651458042135</v>
       </c>
       <c r="M197">
-        <v>0.7132590518280515</v>
+        <v>0.0132590518280515</v>
       </c>
       <c r="N197">
         <v>0</v>
@@ -12011,57 +12011,57 @@
         <v>0.04119974911891067</v>
       </c>
       <c r="P197">
-        <v>0</v>
+        <v>0.20475891431933035</v>
       </c>
       <c r="Q197">
-        <v>0.9701970205360063</v>
+        <v>0.016704533946847077</v>
       </c>
       <c r="R197">
-        <v>0.029802979463993642</v>
+        <v>0.3230088293981651</v>
       </c>
       <c r="S197">
-        <v>0</v>
+        <v>0.4555277223356574</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>sunfish17</v>
+        <v>bird17</v>
       </c>
       <c r="B198">
-        <v>0.4377705761343909</v>
+        <v>0.15777057613439086</v>
       </c>
       <c r="C198">
-        <v>0.6127694211533239</v>
+        <v>0.11276942115332386</v>
       </c>
       <c r="D198">
-        <v>0.7609720404857852</v>
+        <v>0.09097204048578512</v>
       </c>
       <c r="E198">
-        <v>0.031113508170009112</v>
+        <v>0.2640947340861165</v>
       </c>
       <c r="F198">
-        <v>0.9568096695188465</v>
+        <v>0.023014520698152362</v>
       </c>
       <c r="G198">
-        <v>0.012076822311144361</v>
+        <v>0.7128907452157311</v>
       </c>
       <c r="H198">
-        <v>0.8030819164011135</v>
+        <v>0.5530819164011135</v>
       </c>
       <c r="I198">
-        <v>0.17852327052763234</v>
+        <v>0.25852327052763235</v>
       </c>
       <c r="J198">
-        <v>0.022227648798127154</v>
+        <v>0.9222276487981271</v>
       </c>
       <c r="K198">
-        <v>0.0102335953562507</v>
+        <v>0.4602335953562507</v>
       </c>
       <c r="L198">
-        <v>0</v>
+        <v>0.7782669454150192</v>
       </c>
       <c r="M198">
-        <v>0.6570009608570977</v>
+        <v>0</v>
       </c>
       <c r="N198">
         <v>0</v>
@@ -12070,57 +12070,57 @@
         <v>0.036972100000727946</v>
       </c>
       <c r="P198">
-        <v>0.013157920723920958</v>
+        <v>0.2274972424044421</v>
       </c>
       <c r="Q198">
-        <v>0.9407393408670982</v>
+        <v>0</v>
       </c>
       <c r="R198">
-        <v>0.04610273840898085</v>
+        <v>0.32500910988321924</v>
       </c>
       <c r="S198">
-        <v>0</v>
+        <v>0.4474936477123385</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>sunfish18</v>
+        <v>bird18</v>
       </c>
       <c r="B199">
-        <v>0.391383403857649</v>
+        <v>0.11138340385764901</v>
       </c>
       <c r="C199">
-        <v>0.6373307036142892</v>
+        <v>0.1373307036142892</v>
       </c>
       <c r="D199">
-        <v>0.7237496958456288</v>
+        <v>0.05374969584562875</v>
       </c>
       <c r="E199">
-        <v>0</v>
+        <v>0.2285819662053092</v>
       </c>
       <c r="F199">
-        <v>1</v>
+        <v>0.011131529285723384</v>
       </c>
       <c r="G199">
-        <v>0</v>
+        <v>0.7602865045089674</v>
       </c>
       <c r="H199">
-        <v>0.8621379558400938</v>
+        <v>0.6121379558400938</v>
       </c>
       <c r="I199">
-        <v>0.22556583780245232</v>
+        <v>0.30556583780245233</v>
       </c>
       <c r="J199">
-        <v>0.03549602692343501</v>
+        <v>0.9354960269234349</v>
       </c>
       <c r="K199">
-        <v>0.01335337196311163</v>
+        <v>0.46335337196311166</v>
       </c>
       <c r="L199">
-        <v>0.041255092692410164</v>
+        <v>0.8412550926924102</v>
       </c>
       <c r="M199">
-        <v>0.7341050713098852</v>
+        <v>0.03410507130988524</v>
       </c>
       <c r="N199">
         <v>0.026420490332802082</v>
@@ -12129,57 +12129,57 @@
         <v>0.015964676874071673</v>
       </c>
       <c r="P199">
-        <v>0</v>
+        <v>0.18558721582097748</v>
       </c>
       <c r="Q199">
-        <v>0.945580024995185</v>
+        <v>0.008735118427954621</v>
       </c>
       <c r="R199">
-        <v>0.02288510900409752</v>
+        <v>0.31186419515817704</v>
       </c>
       <c r="S199">
-        <v>0.03153486600071748</v>
+        <v>0.49381347059289077</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>sunfish19</v>
+        <v>bird19</v>
       </c>
       <c r="B200">
-        <v>0.3500032961713413</v>
+        <v>0.07000329617134125</v>
       </c>
       <c r="C200">
-        <v>0.5460826730526552</v>
+        <v>0.04608267305265526</v>
       </c>
       <c r="D200">
-        <v>0.7924351202028888</v>
+        <v>0.12243512020288874</v>
       </c>
       <c r="E200">
-        <v>0.015113333074494214</v>
+        <v>0.2618625550061054</v>
       </c>
       <c r="F200">
-        <v>0.9848866669255057</v>
+        <v>0</v>
       </c>
       <c r="G200">
-        <v>0</v>
+        <v>0.7381374449938946</v>
       </c>
       <c r="H200">
-        <v>0.8142949384233636</v>
+        <v>0.5642949384233636</v>
       </c>
       <c r="I200">
-        <v>0.2097573430666547</v>
+        <v>0.2897573430666547</v>
       </c>
       <c r="J200">
-        <v>0.08175506270031695</v>
+        <v>0.9817550627003169</v>
       </c>
       <c r="K200">
-        <v>0.010700936295955142</v>
+        <v>0.46070093629595515</v>
       </c>
       <c r="L200">
-        <v>0.03160977748283333</v>
+        <v>0.8316097774828334</v>
       </c>
       <c r="M200">
-        <v>0.6798296412841902</v>
+        <v>0</v>
       </c>
       <c r="N200">
         <v>0</v>
@@ -12188,57 +12188,57 @@
         <v>0.033587328507209614</v>
       </c>
       <c r="P200">
-        <v>0.01692804075126001</v>
+        <v>0.232739921973019</v>
       </c>
       <c r="Q200">
-        <v>0.9487988673195076</v>
+        <v>0</v>
       </c>
       <c r="R200">
-        <v>0.024686696099555677</v>
+        <v>0.30605615415695603</v>
       </c>
       <c r="S200">
-        <v>0.009586395829676665</v>
+        <v>0.461203923870025</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>sunfish20</v>
+        <v>bird20</v>
       </c>
       <c r="B201">
-        <v>0.414034941009585</v>
+        <v>0.134034941009585</v>
       </c>
       <c r="C201">
-        <v>0.585156024132967</v>
+        <v>0.08515602413296702</v>
       </c>
       <c r="D201">
-        <v>0.7705722056301101</v>
+        <v>0.1005722056301101</v>
       </c>
       <c r="E201">
-        <v>0.0042808103496006535</v>
+        <v>0.2512068226095044</v>
       </c>
       <c r="F201">
-        <v>0.98787648468107</v>
+        <v>0</v>
       </c>
       <c r="G201">
-        <v>0.007842704969329314</v>
+        <v>0.7487931773904958</v>
       </c>
       <c r="H201">
-        <v>0.8290712814861282</v>
+        <v>0.5790712814861282</v>
       </c>
       <c r="I201">
-        <v>0.18573060046471704</v>
+        <v>0.2657306004647171</v>
       </c>
       <c r="J201">
-        <v>0.04581628994598061</v>
+        <v>0.9458162899459805</v>
       </c>
       <c r="K201">
-        <v>0</v>
+        <v>0.4374866652440988</v>
       </c>
       <c r="L201">
-        <v>0.001108960414789819</v>
+        <v>0.8011089604147899</v>
       </c>
       <c r="M201">
-        <v>0.7293181527373706</v>
+        <v>0.029318152737370547</v>
       </c>
       <c r="N201">
         <v>0.00010198829153853962</v>
@@ -12247,30 +12247,30 @@
         <v>0</v>
       </c>
       <c r="P201">
-        <v>0</v>
+        <v>0.19898142332900248</v>
       </c>
       <c r="Q201">
-        <v>0.9749772038124581</v>
+        <v>0</v>
       </c>
       <c r="R201">
-        <v>0.025022796187541836</v>
+        <v>0.3460153024607519</v>
       </c>
       <c r="S201">
-        <v>0</v>
+        <v>0.4550032742102456</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>salmon1</v>
+        <v>sunfish1</v>
       </c>
       <c r="B202">
-        <v>0.8460161791118722</v>
+        <v>0.3960161791118723</v>
       </c>
       <c r="C202">
-        <v>0.898705882805121</v>
+        <v>0.648705882805121</v>
       </c>
       <c r="D202">
-        <v>0.8970447102120267</v>
+        <v>0.7470447102120267</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -12297,7 +12297,7 @@
         <v>0</v>
       </c>
       <c r="M202">
-        <v>0.8159835109974397</v>
+        <v>0.7159835109974396</v>
       </c>
       <c r="N202">
         <v>0.010889552981851739</v>
@@ -12320,16 +12320,16 @@
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>salmon2</v>
+        <v>sunfish2</v>
       </c>
       <c r="B203">
-        <v>0.8278938479966221</v>
+        <v>0.3778938479966221</v>
       </c>
       <c r="C203">
-        <v>0.8655630826889741</v>
+        <v>0.6155630826889741</v>
       </c>
       <c r="D203">
-        <v>0.9001157705625097</v>
+        <v>0.7501157705625097</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -12356,7 +12356,7 @@
         <v>0</v>
       </c>
       <c r="M203">
-        <v>0.809517414662287</v>
+        <v>0.7095174146622869</v>
       </c>
       <c r="N203">
         <v>0</v>
@@ -12379,16 +12379,16 @@
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>salmon3</v>
+        <v>sunfish3</v>
       </c>
       <c r="B204">
-        <v>0.8593667965431234</v>
+        <v>0.40936679654312347</v>
       </c>
       <c r="C204">
-        <v>0.8352971633705174</v>
+        <v>0.5852971633705174</v>
       </c>
       <c r="D204">
-        <v>0.9095304191958566</v>
+        <v>0.7595304191958566</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -12415,7 +12415,7 @@
         <v>0.014236663023440671</v>
       </c>
       <c r="M204">
-        <v>0.8456001675861414</v>
+        <v>0.7456001675861413</v>
       </c>
       <c r="N204">
         <v>0.023260767677562286</v>
@@ -12438,16 +12438,16 @@
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>salmon4</v>
+        <v>sunfish4</v>
       </c>
       <c r="B205">
-        <v>0.8696238433526314</v>
+        <v>0.4196238433526314</v>
       </c>
       <c r="C205">
-        <v>0.8681601143462361</v>
+        <v>0.6181601143462361</v>
       </c>
       <c r="D205">
-        <v>0.8979455474221252</v>
+        <v>0.7479455474221252</v>
       </c>
       <c r="E205">
         <v>0.010771718749224135</v>
@@ -12474,7 +12474,7 @@
         <v>0</v>
       </c>
       <c r="M205">
-        <v>0.8367336619061577</v>
+        <v>0.7367336619061576</v>
       </c>
       <c r="N205">
         <v>0</v>
@@ -12497,16 +12497,16 @@
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>salmon5</v>
+        <v>sunfish5</v>
       </c>
       <c r="B206">
-        <v>0.8528647694257004</v>
+        <v>0.40286476942570054</v>
       </c>
       <c r="C206">
-        <v>0.8453955920842409</v>
+        <v>0.5953955920842409</v>
       </c>
       <c r="D206">
-        <v>0.9379216934926954</v>
+        <v>0.7879216934926954</v>
       </c>
       <c r="E206">
         <v>0.026325144981750623</v>
@@ -12533,7 +12533,7 @@
         <v>0</v>
       </c>
       <c r="M206">
-        <v>0.820592850735516</v>
+        <v>0.7205928507355159</v>
       </c>
       <c r="N206">
         <v>0.021387016977996432</v>
@@ -12556,16 +12556,16 @@
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>salmon6</v>
+        <v>sunfish6</v>
       </c>
       <c r="B207">
-        <v>0.8718260036167867</v>
+        <v>0.42182600361678685</v>
       </c>
       <c r="C207">
-        <v>0.8062574970238023</v>
+        <v>0.5562574970238023</v>
       </c>
       <c r="D207">
-        <v>0.8806825149743602</v>
+        <v>0.7306825149743602</v>
       </c>
       <c r="E207">
         <v>0.00010023985030543727</v>
@@ -12592,7 +12592,7 @@
         <v>0.003043544140358573</v>
       </c>
       <c r="M207">
-        <v>0.7599259289459218</v>
+        <v>0.6599259289459217</v>
       </c>
       <c r="N207">
         <v>0.005082924044104539</v>
@@ -12615,16 +12615,16 @@
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>salmon7</v>
+        <v>sunfish7</v>
       </c>
       <c r="B208">
-        <v>0.8353626125212538</v>
+        <v>0.38536261252125376</v>
       </c>
       <c r="C208">
-        <v>0.8547271304845582</v>
+        <v>0.6047271304845582</v>
       </c>
       <c r="D208">
-        <v>0.9044032842795888</v>
+        <v>0.7544032842795888</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -12651,7 +12651,7 @@
         <v>0.00158488157212941</v>
       </c>
       <c r="M208">
-        <v>0.8113908718381655</v>
+        <v>0.7113908718381654</v>
       </c>
       <c r="N208">
         <v>0</v>
@@ -12674,16 +12674,16 @@
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>salmon8</v>
+        <v>sunfish8</v>
       </c>
       <c r="B209">
-        <v>0.847226397197263</v>
+        <v>0.39722639719726305</v>
       </c>
       <c r="C209">
-        <v>0.8780987876116468</v>
+        <v>0.6280987876116468</v>
       </c>
       <c r="D209">
-        <v>0.9197770863782891</v>
+        <v>0.7697770863782891</v>
       </c>
       <c r="E209">
         <v>0.05812400324026726</v>
@@ -12710,7 +12710,7 @@
         <v>0.03151597822393936</v>
       </c>
       <c r="M209">
-        <v>0.836106536858134</v>
+        <v>0.7361065368581339</v>
       </c>
       <c r="N209">
         <v>0.006090984325775633</v>
@@ -12733,16 +12733,16 @@
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>salmon9</v>
+        <v>sunfish9</v>
       </c>
       <c r="B210">
-        <v>0.8513681913867619</v>
+        <v>0.4013681913867619</v>
       </c>
       <c r="C210">
-        <v>0.8670358329087381</v>
+        <v>0.6170358329087381</v>
       </c>
       <c r="D210">
-        <v>0.9325617296141578</v>
+        <v>0.7825617296141578</v>
       </c>
       <c r="E210">
         <v>0.004185532277042151</v>
@@ -12769,7 +12769,7 @@
         <v>0.01750913782723242</v>
       </c>
       <c r="M210">
-        <v>0.7812153555031475</v>
+        <v>0.6812153555031474</v>
       </c>
       <c r="N210">
         <v>0</v>
@@ -12792,16 +12792,16 @@
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>salmon10</v>
+        <v>sunfish10</v>
       </c>
       <c r="B211">
-        <v>0.8742123435550039</v>
+        <v>0.4242123435550039</v>
       </c>
       <c r="C211">
-        <v>0.8586737814061932</v>
+        <v>0.6086737814061932</v>
       </c>
       <c r="D211">
-        <v>0.8876695358988239</v>
+        <v>0.7376695358988239</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -12828,7 +12828,7 @@
         <v>0</v>
       </c>
       <c r="M211">
-        <v>0.7522052845533009</v>
+        <v>0.6522052845533008</v>
       </c>
       <c r="N211">
         <v>0</v>
@@ -12851,16 +12851,16 @@
     </row>
     <row r="212">
       <c r="A212" t="str">
-        <v>salmon11</v>
+        <v>sunfish11</v>
       </c>
       <c r="B212">
-        <v>0.8270239507069738</v>
+        <v>0.37702395070697386</v>
       </c>
       <c r="C212">
-        <v>0.8709634138172813</v>
+        <v>0.6209634138172813</v>
       </c>
       <c r="D212">
-        <v>0.9119741527837574</v>
+        <v>0.7619741527837574</v>
       </c>
       <c r="E212">
         <v>0.001053759608612752</v>
@@ -12887,7 +12887,7 @@
         <v>0.03808107853157141</v>
       </c>
       <c r="M212">
-        <v>0.774891370230535</v>
+        <v>0.6748913702305349</v>
       </c>
       <c r="N212">
         <v>0.021210809292670586</v>
@@ -12910,16 +12910,16 @@
     </row>
     <row r="213">
       <c r="A213" t="str">
-        <v>salmon12</v>
+        <v>sunfish12</v>
       </c>
       <c r="B213">
-        <v>0.8053040891620211</v>
+        <v>0.35530408916202116</v>
       </c>
       <c r="C213">
-        <v>0.8536266831678605</v>
+        <v>0.6036266831678605</v>
       </c>
       <c r="D213">
-        <v>0.8625767316122461</v>
+        <v>0.7125767316122461</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -12946,7 +12946,7 @@
         <v>0</v>
       </c>
       <c r="M213">
-        <v>0.7552213457097123</v>
+        <v>0.6552213457097122</v>
       </c>
       <c r="N213">
         <v>0.019597057998520663</v>
@@ -12969,16 +12969,16 @@
     </row>
     <row r="214">
       <c r="A214" t="str">
-        <v>salmon13</v>
+        <v>sunfish13</v>
       </c>
       <c r="B214">
-        <v>0.8364050293506805</v>
+        <v>0.3864050293506806</v>
       </c>
       <c r="C214">
-        <v>0.8479581634399407</v>
+        <v>0.5979581634399407</v>
       </c>
       <c r="D214">
-        <v>0.9038437595511768</v>
+        <v>0.7538437595511768</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -13005,7 +13005,7 @@
         <v>0.01960019076798132</v>
       </c>
       <c r="M214">
-        <v>0.8096588834397295</v>
+        <v>0.7096588834397294</v>
       </c>
       <c r="N214">
         <v>0</v>
@@ -13028,16 +13028,16 @@
     </row>
     <row r="215">
       <c r="A215" t="str">
-        <v>salmon14</v>
+        <v>sunfish14</v>
       </c>
       <c r="B215">
-        <v>0.8531076086225653</v>
+        <v>0.40310760862256534</v>
       </c>
       <c r="C215">
-        <v>0.8778326058219876</v>
+        <v>0.6278326058219876</v>
       </c>
       <c r="D215">
-        <v>0.9434166533222927</v>
+        <v>0.7934166533222927</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -13064,7 +13064,7 @@
         <v>0.020652409939445875</v>
       </c>
       <c r="M215">
-        <v>0.8316926682813481</v>
+        <v>0.731692668281348</v>
       </c>
       <c r="N215">
         <v>0.013552727934612922</v>
@@ -13087,16 +13087,16 @@
     </row>
     <row r="216">
       <c r="A216" t="str">
-        <v>salmon15</v>
+        <v>sunfish15</v>
       </c>
       <c r="B216">
-        <v>0.8979435406243333</v>
+        <v>0.4479435406243334</v>
       </c>
       <c r="C216">
-        <v>0.8497094883009337</v>
+        <v>0.5997094883009337</v>
       </c>
       <c r="D216">
-        <v>0.9013959297115056</v>
+        <v>0.7513959297115056</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -13123,7 +13123,7 @@
         <v>0.015962742583676075</v>
       </c>
       <c r="M216">
-        <v>0.8415315109506244</v>
+        <v>0.7415315109506243</v>
       </c>
       <c r="N216">
         <v>0</v>
@@ -13146,16 +13146,16 @@
     </row>
     <row r="217">
       <c r="A217" t="str">
-        <v>salmon16</v>
+        <v>sunfish16</v>
       </c>
       <c r="B217">
-        <v>0.8902615679836209</v>
+        <v>0.4402615679836209</v>
       </c>
       <c r="C217">
-        <v>0.8020796663626416</v>
+        <v>0.5520796663626416</v>
       </c>
       <c r="D217">
-        <v>0.8786826684778084</v>
+        <v>0.7286826684778084</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -13182,7 +13182,7 @@
         <v>0</v>
       </c>
       <c r="M217">
-        <v>0.81464141671096</v>
+        <v>0.7146414167109599</v>
       </c>
       <c r="N217">
         <v>0.012405554191536683</v>
@@ -13205,16 +13205,16 @@
     </row>
     <row r="218">
       <c r="A218" t="str">
-        <v>salmon17</v>
+        <v>sunfish17</v>
       </c>
       <c r="B218">
-        <v>0.8586608602183899</v>
+        <v>0.40866086021839004</v>
       </c>
       <c r="C218">
-        <v>0.8619615964083994</v>
+        <v>0.6119615964083994</v>
       </c>
       <c r="D218">
-        <v>0.863703385973192</v>
+        <v>0.7137033859731919</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -13241,7 +13241,7 @@
         <v>0</v>
       </c>
       <c r="M218">
-        <v>0.7957139220018072</v>
+        <v>0.6957139220018072</v>
       </c>
       <c r="N218">
         <v>0</v>
@@ -13264,16 +13264,16 @@
     </row>
     <row r="219">
       <c r="A219" t="str">
-        <v>salmon18</v>
+        <v>sunfish18</v>
       </c>
       <c r="B219">
-        <v>0.8271866827355412</v>
+        <v>0.37718668273554123</v>
       </c>
       <c r="C219">
-        <v>0.8736321702160773</v>
+        <v>0.6236321702160773</v>
       </c>
       <c r="D219">
-        <v>0.8897346344473203</v>
+        <v>0.7397346344473202</v>
       </c>
       <c r="E219">
         <v>0.028349200512415084</v>
@@ -13300,7 +13300,7 @@
         <v>0</v>
       </c>
       <c r="M219">
-        <v>0.8179634653806681</v>
+        <v>0.717963465380668</v>
       </c>
       <c r="N219">
         <v>0.019436259493974345</v>
@@ -13323,16 +13323,16 @@
     </row>
     <row r="220">
       <c r="A220" t="str">
-        <v>salmon19</v>
+        <v>sunfish19</v>
       </c>
       <c r="B220">
-        <v>0.8225155881054959</v>
+        <v>0.3725155881054959</v>
       </c>
       <c r="C220">
-        <v>0.870907078262878</v>
+        <v>0.620907078262878</v>
       </c>
       <c r="D220">
-        <v>0.9357750706076369</v>
+        <v>0.7857750706076368</v>
       </c>
       <c r="E220">
         <v>0.028914315257047064</v>
@@ -13359,7 +13359,7 @@
         <v>0</v>
       </c>
       <c r="M220">
-        <v>0.794451310222226</v>
+        <v>0.694451310222226</v>
       </c>
       <c r="N220">
         <v>0.012074929430122505</v>
@@ -13382,16 +13382,16 @@
     </row>
     <row r="221">
       <c r="A221" t="str">
-        <v>salmon20</v>
+        <v>sunfish20</v>
       </c>
       <c r="B221">
-        <v>0.8598968275243287</v>
+        <v>0.4098968275243288</v>
       </c>
       <c r="C221">
-        <v>0.8825936642629488</v>
+        <v>0.6325936642629488</v>
       </c>
       <c r="D221">
-        <v>0.8985948775512389</v>
+        <v>0.7485948775512389</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -13418,7 +13418,7 @@
         <v>0.007798807033449849</v>
       </c>
       <c r="M221">
-        <v>0.8263258879949127</v>
+        <v>0.7263258879949126</v>
       </c>
       <c r="N221">
         <v>0.020586050511900978</v>
@@ -13441,16 +13441,16 @@
     </row>
     <row r="222">
       <c r="A222" t="str">
-        <v>fish1</v>
+        <v>salmon1</v>
       </c>
       <c r="B222">
-        <v>0.11474776221285797</v>
+        <v>0.864747762212858</v>
       </c>
       <c r="C222">
-        <v>0.176887825658454</v>
+        <v>0.876887825658454</v>
       </c>
       <c r="D222">
-        <v>0.24731720558962642</v>
+        <v>0.9473172055896264</v>
       </c>
       <c r="E222">
         <v>0.007989326368517301</v>
@@ -13477,7 +13477,7 @@
         <v>0</v>
       </c>
       <c r="M222">
-        <v>0.7492683070676207</v>
+        <v>0.7992683070676208</v>
       </c>
       <c r="N222">
         <v>0</v>
@@ -13500,16 +13500,16 @@
     </row>
     <row r="223">
       <c r="A223" t="str">
-        <v>fish2</v>
+        <v>salmon2</v>
       </c>
       <c r="B223">
-        <v>0.15959027789027722</v>
+        <v>0.9095902778902771</v>
       </c>
       <c r="C223">
-        <v>0.17061585984788297</v>
+        <v>0.8706158598478829</v>
       </c>
       <c r="D223">
-        <v>0.1907410852486763</v>
+        <v>0.8907410852486763</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -13536,7 +13536,7 @@
         <v>0</v>
       </c>
       <c r="M223">
-        <v>0.7578978711987916</v>
+        <v>0.8078978711987916</v>
       </c>
       <c r="N223">
         <v>0.003322661452649882</v>
@@ -13559,16 +13559,16 @@
     </row>
     <row r="224">
       <c r="A224" t="str">
-        <v>fish3</v>
+        <v>salmon3</v>
       </c>
       <c r="B224">
-        <v>0.07996630541447342</v>
+        <v>0.8299663054144734</v>
       </c>
       <c r="C224">
-        <v>0.15096159115795973</v>
+        <v>0.8509615911579597</v>
       </c>
       <c r="D224">
-        <v>0.19185283575731138</v>
+        <v>0.8918528357573113</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -13595,7 +13595,7 @@
         <v>0</v>
       </c>
       <c r="M224">
-        <v>0.767317659833452</v>
+        <v>0.8173176598334521</v>
       </c>
       <c r="N224">
         <v>0</v>
@@ -13618,16 +13618,16 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>fish4</v>
+        <v>salmon4</v>
       </c>
       <c r="B225">
-        <v>0.07889389229451105</v>
+        <v>0.828893892294511</v>
       </c>
       <c r="C225">
-        <v>0.11647545981879853</v>
+        <v>0.8164754598187985</v>
       </c>
       <c r="D225">
-        <v>0.17367848399037272</v>
+        <v>0.8736784839903727</v>
       </c>
       <c r="E225">
         <v>0.030889833517448808</v>
@@ -13654,7 +13654,7 @@
         <v>0</v>
       </c>
       <c r="M225">
-        <v>0.7936277239711693</v>
+        <v>0.8436277239711694</v>
       </c>
       <c r="N225">
         <v>0.010942835368434073</v>
@@ -13677,16 +13677,16 @@
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>fish5</v>
+        <v>salmon5</v>
       </c>
       <c r="B226">
-        <v>0.06678249549490273</v>
+        <v>0.8167824954949027</v>
       </c>
       <c r="C226">
-        <v>0.15557272142675316</v>
+        <v>0.8555727214267531</v>
       </c>
       <c r="D226">
-        <v>0.1877806196296742</v>
+        <v>0.8877806196296743</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -13713,7 +13713,7 @@
         <v>0</v>
       </c>
       <c r="M226">
-        <v>0.7632374940960742</v>
+        <v>0.8132374940960743</v>
       </c>
       <c r="N226">
         <v>0.0046287594739386085</v>
@@ -13736,16 +13736,16 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>fish6</v>
+        <v>salmon6</v>
       </c>
       <c r="B227">
-        <v>0.0628638081036278</v>
+        <v>0.8128638081036278</v>
       </c>
       <c r="C227">
-        <v>0.133261904271538</v>
+        <v>0.833261904271538</v>
       </c>
       <c r="D227">
-        <v>0.2173259760201914</v>
+        <v>0.9173259760201914</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -13772,7 +13772,7 @@
         <v>0</v>
       </c>
       <c r="M227">
-        <v>0.7889861810038942</v>
+        <v>0.8389861810038942</v>
       </c>
       <c r="N227">
         <v>0</v>
@@ -13795,16 +13795,16 @@
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>fish7</v>
+        <v>salmon7</v>
       </c>
       <c r="B228">
-        <v>0.06652657385786881</v>
+        <v>0.8165265738578688</v>
       </c>
       <c r="C228">
-        <v>0.18084696949690773</v>
+        <v>0.8808469694969077</v>
       </c>
       <c r="D228">
-        <v>0.175507097251807</v>
+        <v>0.875507097251807</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -13831,7 +13831,7 @@
         <v>0.0028531912560967204</v>
       </c>
       <c r="M228">
-        <v>0.7646737943473773</v>
+        <v>0.8146737943473773</v>
       </c>
       <c r="N228">
         <v>0</v>
@@ -13854,16 +13854,16 @@
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>fish8</v>
+        <v>salmon8</v>
       </c>
       <c r="B229">
-        <v>0.10590868423094477</v>
+        <v>0.8559086842309447</v>
       </c>
       <c r="C229">
-        <v>0.14989703525915568</v>
+        <v>0.8498970352591556</v>
       </c>
       <c r="D229">
-        <v>0.17231339715214933</v>
+        <v>0.8723133971521494</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -13913,16 +13913,16 @@
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>fish9</v>
+        <v>salmon9</v>
       </c>
       <c r="B230">
-        <v>0.11063168136015497</v>
+        <v>0.8606316813601549</v>
       </c>
       <c r="C230">
-        <v>0.12045149953079995</v>
+        <v>0.8204514995307999</v>
       </c>
       <c r="D230">
-        <v>0.2214207099484783</v>
+        <v>0.9214207099484782</v>
       </c>
       <c r="E230">
         <v>0.020099907140390887</v>
@@ -13949,7 +13949,7 @@
         <v>0</v>
       </c>
       <c r="M230">
-        <v>0.7596737219603862</v>
+        <v>0.8096737219603862</v>
       </c>
       <c r="N230">
         <v>0.049182461210733726</v>
@@ -13972,16 +13972,16 @@
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>fish10</v>
+        <v>salmon10</v>
       </c>
       <c r="B231">
-        <v>0.13666849023300037</v>
+        <v>0.8866684902330003</v>
       </c>
       <c r="C231">
-        <v>0.14131304090996505</v>
+        <v>0.8413130409099651</v>
       </c>
       <c r="D231">
-        <v>0.19085823708283034</v>
+        <v>0.8908582370828304</v>
       </c>
       <c r="E231">
         <v>0.009062754254410735</v>
@@ -14008,7 +14008,7 @@
         <v>0</v>
       </c>
       <c r="M231">
-        <v>0.7290778009808745</v>
+        <v>0.7790778009808745</v>
       </c>
       <c r="N231">
         <v>0.004949414976945755</v>
@@ -14031,16 +14031,16 @@
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>fish11</v>
+        <v>salmon11</v>
       </c>
       <c r="B232">
-        <v>0.0822332038978943</v>
+        <v>0.8322332038978942</v>
       </c>
       <c r="C232">
-        <v>0.13700936273480957</v>
+        <v>0.8370093627348095</v>
       </c>
       <c r="D232">
-        <v>0.24045001565295038</v>
+        <v>0.9404500156529504</v>
       </c>
       <c r="E232">
         <v>0.0077405775834195195</v>
@@ -14067,7 +14067,7 @@
         <v>0</v>
       </c>
       <c r="M232">
-        <v>0.7638134404807825</v>
+        <v>0.8138134404807825</v>
       </c>
       <c r="N232">
         <v>0</v>
@@ -14090,16 +14090,16 @@
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>fish12</v>
+        <v>salmon12</v>
       </c>
       <c r="B233">
-        <v>0.1172471691228828</v>
+        <v>0.8672471691228828</v>
       </c>
       <c r="C233">
-        <v>0.17064380316434463</v>
+        <v>0.8706438031643446</v>
       </c>
       <c r="D233">
-        <v>0.18540452195322996</v>
+        <v>0.8854045219532299</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -14126,7 +14126,7 @@
         <v>0.00598277175144438</v>
       </c>
       <c r="M233">
-        <v>0.7396425138891468</v>
+        <v>0.7896425138891469</v>
       </c>
       <c r="N233">
         <v>0.0431153019585023</v>
@@ -14149,16 +14149,16 @@
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>fish13</v>
+        <v>salmon13</v>
       </c>
       <c r="B234">
-        <v>0.09498307351454723</v>
+        <v>0.8449830735145472</v>
       </c>
       <c r="C234">
-        <v>0.1441117998751508</v>
+        <v>0.8441117998751508</v>
       </c>
       <c r="D234">
-        <v>0.19108620658822953</v>
+        <v>0.8910862065882296</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -14185,7 +14185,7 @@
         <v>0.0032884337080639732</v>
       </c>
       <c r="M234">
-        <v>0.7515383132197547</v>
+        <v>0.8015383132197548</v>
       </c>
       <c r="N234">
         <v>0.015432411761629608</v>
@@ -14208,16 +14208,16 @@
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>fish14</v>
+        <v>salmon14</v>
       </c>
       <c r="B235">
-        <v>0.09945222018551443</v>
+        <v>0.8494522201855144</v>
       </c>
       <c r="C235">
-        <v>0.10299106203175451</v>
+        <v>0.8029910620317545</v>
       </c>
       <c r="D235">
-        <v>0.17639807950135336</v>
+        <v>0.8763980795013534</v>
       </c>
       <c r="E235">
         <v>0.0032996409956803138</v>
@@ -14244,7 +14244,7 @@
         <v>0.03435794242181354</v>
       </c>
       <c r="M235">
-        <v>0.7428635421838009</v>
+        <v>0.792863542183801</v>
       </c>
       <c r="N235">
         <v>0</v>
@@ -14267,16 +14267,16 @@
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>fish15</v>
+        <v>salmon15</v>
       </c>
       <c r="B236">
-        <v>0.08179547841624145</v>
+        <v>0.8317954784162415</v>
       </c>
       <c r="C236">
-        <v>0.1371811433803615</v>
+        <v>0.8371811433803614</v>
       </c>
       <c r="D236">
-        <v>0.16164954251796199</v>
+        <v>0.861649542517962</v>
       </c>
       <c r="E236">
         <v>0.00694268977236251</v>
@@ -14303,7 +14303,7 @@
         <v>0.04485709290997803</v>
       </c>
       <c r="M236">
-        <v>0.7895281223068737</v>
+        <v>0.8395281223068738</v>
       </c>
       <c r="N236">
         <v>0</v>
@@ -14326,16 +14326,16 @@
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>fish16</v>
+        <v>salmon16</v>
       </c>
       <c r="B237">
-        <v>0.10116375520350993</v>
+        <v>0.8511637552035098</v>
       </c>
       <c r="C237">
-        <v>0.1920099314897319</v>
+        <v>0.8920099314897318</v>
       </c>
       <c r="D237">
-        <v>0.1854280266891402</v>
+        <v>0.8854280266891402</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -14362,7 +14362,7 @@
         <v>0</v>
       </c>
       <c r="M237">
-        <v>0.7384505670677238</v>
+        <v>0.7884505670677239</v>
       </c>
       <c r="N237">
         <v>0.004763541207981419</v>
@@ -14385,16 +14385,16 @@
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>fish17</v>
+        <v>salmon17</v>
       </c>
       <c r="B238">
-        <v>0.08070533455052796</v>
+        <v>0.830705334550528</v>
       </c>
       <c r="C238">
-        <v>0.0896629982238857</v>
+        <v>0.7896629982238856</v>
       </c>
       <c r="D238">
-        <v>0.20813382473100586</v>
+        <v>0.9081338247310059</v>
       </c>
       <c r="E238">
         <v>0.02479266111626354</v>
@@ -14421,7 +14421,7 @@
         <v>0.024671502187134705</v>
       </c>
       <c r="M238">
-        <v>0.7391777058112545</v>
+        <v>0.7891777058112546</v>
       </c>
       <c r="N238">
         <v>0</v>
@@ -14444,16 +14444,16 @@
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>fish18</v>
+        <v>salmon18</v>
       </c>
       <c r="B239">
-        <v>0.1472524767250531</v>
+        <v>0.897252476725053</v>
       </c>
       <c r="C239">
-        <v>0.19301442031496235</v>
+        <v>0.8930144203149624</v>
       </c>
       <c r="D239">
-        <v>0.16627434872550356</v>
+        <v>0.8662743487255036</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -14480,7 +14480,7 @@
         <v>0.016921042782803358</v>
       </c>
       <c r="M239">
-        <v>0.7336257641857603</v>
+        <v>0.7836257641857604</v>
       </c>
       <c r="N239">
         <v>0.023713023446682274</v>
@@ -14503,16 +14503,16 @@
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>fish19</v>
+        <v>salmon19</v>
       </c>
       <c r="B240">
-        <v>0.12353751893875178</v>
+        <v>0.8735375189387518</v>
       </c>
       <c r="C240">
-        <v>0.13949462842128368</v>
+        <v>0.8394946284212836</v>
       </c>
       <c r="D240">
-        <v>0.173438382973509</v>
+        <v>0.8734383829735091</v>
       </c>
       <c r="E240">
         <v>0.038625858064761424</v>
@@ -14539,7 +14539,7 @@
         <v>0</v>
       </c>
       <c r="M240">
-        <v>0.7499059312315686</v>
+        <v>0.7999059312315686</v>
       </c>
       <c r="N240">
         <v>0.009361224556367837</v>
@@ -14562,16 +14562,16 @@
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>fish20</v>
+        <v>salmon20</v>
       </c>
       <c r="B241">
-        <v>0.10660974465380031</v>
+        <v>0.8566097446538002</v>
       </c>
       <c r="C241">
-        <v>0.14522809172357057</v>
+        <v>0.8452280917235706</v>
       </c>
       <c r="D241">
-        <v>0.1992775898160223</v>
+        <v>0.8992775898160223</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -14598,7 +14598,7 @@
         <v>0.04201442473040808</v>
       </c>
       <c r="M241">
-        <v>0.6977515098905605</v>
+        <v>0.7477515098905605</v>
       </c>
       <c r="N241">
         <v>0</v>
@@ -14619,16 +14619,2376 @@
         <v>0</v>
       </c>
     </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>fish1</v>
+      </c>
+      <c r="B242">
+        <v>0.036770845191722246</v>
+      </c>
+      <c r="C242">
+        <v>0.13680539672816355</v>
+      </c>
+      <c r="D242">
+        <v>0.22188351355893207</v>
+      </c>
+      <c r="E242">
+        <v>0.028181704319073235</v>
+      </c>
+      <c r="F242">
+        <v>0.9191384701790313</v>
+      </c>
+      <c r="G242">
+        <v>0.052679825501895546</v>
+      </c>
+      <c r="H242">
+        <v>0.8383536527679055</v>
+      </c>
+      <c r="I242">
+        <v>0.2379795081908765</v>
+      </c>
+      <c r="J242">
+        <v>0.05959835340351258</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242">
+        <v>0</v>
+      </c>
+      <c r="P242">
+        <v>0.003389172393947176</v>
+      </c>
+      <c r="Q242">
+        <v>0.9800025393310011</v>
+      </c>
+      <c r="R242">
+        <v>0.01660828827505176</v>
+      </c>
+      <c r="S242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>fish2</v>
+      </c>
+      <c r="B243">
+        <v>0.11378714854116165</v>
+      </c>
+      <c r="C243">
+        <v>0.17233374625164113</v>
+      </c>
+      <c r="D243">
+        <v>0.17181937307141457</v>
+      </c>
+      <c r="E243">
+        <v>0.009529517999024678</v>
+      </c>
+      <c r="F243">
+        <v>0.9822496242903583</v>
+      </c>
+      <c r="G243">
+        <v>0.0082208577106168</v>
+      </c>
+      <c r="H243">
+        <v>0.8251558943919726</v>
+      </c>
+      <c r="I243">
+        <v>0.18372294787805699</v>
+      </c>
+      <c r="J243">
+        <v>0.040302433220447985</v>
+      </c>
+      <c r="K243">
+        <v>0.006582239344216677</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>0.741075154203835</v>
+      </c>
+      <c r="N243">
+        <v>0.0034922836034976946</v>
+      </c>
+      <c r="O243">
+        <v>0</v>
+      </c>
+      <c r="P243">
+        <v>0</v>
+      </c>
+      <c r="Q243">
+        <v>0.9892382293809323</v>
+      </c>
+      <c r="R243">
+        <v>0</v>
+      </c>
+      <c r="S243">
+        <v>0.010761770619067827</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>fish3</v>
+      </c>
+      <c r="B244">
+        <v>0.10622676089724489</v>
+      </c>
+      <c r="C244">
+        <v>0.17509142966325858</v>
+      </c>
+      <c r="D244">
+        <v>0.24134781432217722</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244">
+        <v>0</v>
+      </c>
+      <c r="H244">
+        <v>0.8566555874599902</v>
+      </c>
+      <c r="I244">
+        <v>0.20967658973727077</v>
+      </c>
+      <c r="J244">
+        <v>0.04743050319039005</v>
+      </c>
+      <c r="K244">
+        <v>0.00948366459186015</v>
+      </c>
+      <c r="L244">
+        <v>0.009998066532592484</v>
+      </c>
+      <c r="M244">
+        <v>0.728812248077394</v>
+      </c>
+      <c r="N244">
+        <v>0</v>
+      </c>
+      <c r="O244">
+        <v>0</v>
+      </c>
+      <c r="P244">
+        <v>0.008160320851985679</v>
+      </c>
+      <c r="Q244">
+        <v>0.9918396791480144</v>
+      </c>
+      <c r="R244">
+        <v>0</v>
+      </c>
+      <c r="S244">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>fish4</v>
+      </c>
+      <c r="B245">
+        <v>0.09968306378950736</v>
+      </c>
+      <c r="C245">
+        <v>0.15909305875697372</v>
+      </c>
+      <c r="D245">
+        <v>0.21274240150462606</v>
+      </c>
+      <c r="E245">
+        <v>0.0162445800218414</v>
+      </c>
+      <c r="F245">
+        <v>0.977179286275958</v>
+      </c>
+      <c r="G245">
+        <v>0.006576133702200627</v>
+      </c>
+      <c r="H245">
+        <v>0.8478744800415958</v>
+      </c>
+      <c r="I245">
+        <v>0.21503501813539597</v>
+      </c>
+      <c r="J245">
+        <v>0.07050642178015819</v>
+      </c>
+      <c r="K245">
+        <v>0</v>
+      </c>
+      <c r="L245">
+        <v>0.038065919931595624</v>
+      </c>
+      <c r="M245">
+        <v>0.7350698508085424</v>
+      </c>
+      <c r="N245">
+        <v>0</v>
+      </c>
+      <c r="O245">
+        <v>0.006052227114287455</v>
+      </c>
+      <c r="P245">
+        <v>0</v>
+      </c>
+      <c r="Q245">
+        <v>1</v>
+      </c>
+      <c r="R245">
+        <v>0</v>
+      </c>
+      <c r="S245">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>fish5</v>
+      </c>
+      <c r="B246">
+        <v>0.06132941706623196</v>
+      </c>
+      <c r="C246">
+        <v>0.13215308557639338</v>
+      </c>
+      <c r="D246">
+        <v>0.20987379706056258</v>
+      </c>
+      <c r="E246">
+        <v>0.04858965815658913</v>
+      </c>
+      <c r="F246">
+        <v>0.951410341843411</v>
+      </c>
+      <c r="G246">
+        <v>0</v>
+      </c>
+      <c r="H246">
+        <v>0.8797825743514402</v>
+      </c>
+      <c r="I246">
+        <v>0.2339588144276853</v>
+      </c>
+      <c r="J246">
+        <v>0.03731431021326783</v>
+      </c>
+      <c r="K246">
+        <v>0.021007611236363757</v>
+      </c>
+      <c r="L246">
+        <v>0</v>
+      </c>
+      <c r="M246">
+        <v>0.7662780569285836</v>
+      </c>
+      <c r="N246">
+        <v>0</v>
+      </c>
+      <c r="O246">
+        <v>0.06033665541215553</v>
+      </c>
+      <c r="P246">
+        <v>0.012064656764857273</v>
+      </c>
+      <c r="Q246">
+        <v>0.977084830755477</v>
+      </c>
+      <c r="R246">
+        <v>0.01085051247966567</v>
+      </c>
+      <c r="S246">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>fish6</v>
+      </c>
+      <c r="B247">
+        <v>0.07857008227243378</v>
+      </c>
+      <c r="C247">
+        <v>0.1508835310192949</v>
+      </c>
+      <c r="D247">
+        <v>0.18983245175911245</v>
+      </c>
+      <c r="E247">
+        <v>0</v>
+      </c>
+      <c r="F247">
+        <v>0.9930390690534365</v>
+      </c>
+      <c r="G247">
+        <v>0.00696093094656356</v>
+      </c>
+      <c r="H247">
+        <v>0.8544904165854923</v>
+      </c>
+      <c r="I247">
+        <v>0.2228127050759378</v>
+      </c>
+      <c r="J247">
+        <v>0.04234756867400546</v>
+      </c>
+      <c r="K247">
+        <v>0</v>
+      </c>
+      <c r="L247">
+        <v>0</v>
+      </c>
+      <c r="M247">
+        <v>0.7544514484667623</v>
+      </c>
+      <c r="N247">
+        <v>0</v>
+      </c>
+      <c r="O247">
+        <v>0.045674099743199505</v>
+      </c>
+      <c r="P247">
+        <v>0.029238643210322286</v>
+      </c>
+      <c r="Q247">
+        <v>0.9707613567896777</v>
+      </c>
+      <c r="R247">
+        <v>0</v>
+      </c>
+      <c r="S247">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>fish7</v>
+      </c>
+      <c r="B248">
+        <v>0.07061874249564491</v>
+      </c>
+      <c r="C248">
+        <v>0.17037675624013904</v>
+      </c>
+      <c r="D248">
+        <v>0.17862917308777299</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+      <c r="F248">
+        <v>0.9959775037339885</v>
+      </c>
+      <c r="G248">
+        <v>0.004022496266011436</v>
+      </c>
+      <c r="H248">
+        <v>0.8610749435301016</v>
+      </c>
+      <c r="I248">
+        <v>0.18005877074907992</v>
+      </c>
+      <c r="J248">
+        <v>0.04146238427424723</v>
+      </c>
+      <c r="K248">
+        <v>0.07021687559920128</v>
+      </c>
+      <c r="L248">
+        <v>0.019514857264471074</v>
+      </c>
+      <c r="M248">
+        <v>0.7554205210480848</v>
+      </c>
+      <c r="N248">
+        <v>0.044773951578548354</v>
+      </c>
+      <c r="O248">
+        <v>0</v>
+      </c>
+      <c r="P248">
+        <v>0</v>
+      </c>
+      <c r="Q248">
+        <v>0.9382940712172944</v>
+      </c>
+      <c r="R248">
+        <v>0.040120300389626086</v>
+      </c>
+      <c r="S248">
+        <v>0.02158562839307946</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>fish8</v>
+      </c>
+      <c r="B249">
+        <v>0.07861442411584854</v>
+      </c>
+      <c r="C249">
+        <v>0.1266497075890381</v>
+      </c>
+      <c r="D249">
+        <v>0.19056448281648306</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+      <c r="F249">
+        <v>0.9657545193687194</v>
+      </c>
+      <c r="G249">
+        <v>0.034245480631280495</v>
+      </c>
+      <c r="H249">
+        <v>0.8544908678472113</v>
+      </c>
+      <c r="I249">
+        <v>0.22793964714692957</v>
+      </c>
+      <c r="J249">
+        <v>0.06768637287975252</v>
+      </c>
+      <c r="K249">
+        <v>0</v>
+      </c>
+      <c r="L249">
+        <v>0.055550737292465215</v>
+      </c>
+      <c r="M249">
+        <v>0.7167253637311528</v>
+      </c>
+      <c r="N249">
+        <v>0.018334687686748976</v>
+      </c>
+      <c r="O249">
+        <v>0</v>
+      </c>
+      <c r="P249">
+        <v>0.02239035619032905</v>
+      </c>
+      <c r="Q249">
+        <v>0.9776096438096711</v>
+      </c>
+      <c r="R249">
+        <v>0</v>
+      </c>
+      <c r="S249">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>fish9</v>
+      </c>
+      <c r="B250">
+        <v>0.13551001610818963</v>
+      </c>
+      <c r="C250">
+        <v>0.1625625047980193</v>
+      </c>
+      <c r="D250">
+        <v>0.23173188998098523</v>
+      </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
+      <c r="F250">
+        <v>1</v>
+      </c>
+      <c r="G250">
+        <v>0</v>
+      </c>
+      <c r="H250">
+        <v>0.8256083909207323</v>
+      </c>
+      <c r="I250">
+        <v>0.23484963210148163</v>
+      </c>
+      <c r="J250">
+        <v>0.05425157222580702</v>
+      </c>
+      <c r="K250">
+        <v>0.03412068238150617</v>
+      </c>
+      <c r="L250">
+        <v>0</v>
+      </c>
+      <c r="M250">
+        <v>0.7510543581037689</v>
+      </c>
+      <c r="N250">
+        <v>0.0072004297886710455</v>
+      </c>
+      <c r="O250">
+        <v>0.0006673888110285976</v>
+      </c>
+      <c r="P250">
+        <v>0</v>
+      </c>
+      <c r="Q250">
+        <v>0</v>
+      </c>
+      <c r="R250">
+        <v>0</v>
+      </c>
+      <c r="S250">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>fish10</v>
+      </c>
+      <c r="B251">
+        <v>0.09623858210531135</v>
+      </c>
+      <c r="C251">
+        <v>0.11848538716813947</v>
+      </c>
+      <c r="D251">
+        <v>0.16486822568318982</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>1</v>
+      </c>
+      <c r="G251">
+        <v>0</v>
+      </c>
+      <c r="H251">
+        <v>0.8593293940688312</v>
+      </c>
+      <c r="I251">
+        <v>0.24737524701952018</v>
+      </c>
+      <c r="J251">
+        <v>0.08110908711025777</v>
+      </c>
+      <c r="K251">
+        <v>0.006780538086814606</v>
+      </c>
+      <c r="L251">
+        <v>0</v>
+      </c>
+      <c r="M251">
+        <v>0.7565374435316784</v>
+      </c>
+      <c r="N251">
+        <v>0.03165747888778941</v>
+      </c>
+      <c r="O251">
+        <v>0.0341573520175406</v>
+      </c>
+      <c r="P251">
+        <v>0</v>
+      </c>
+      <c r="Q251">
+        <v>0.9145216553917842</v>
+      </c>
+      <c r="R251">
+        <v>0.03424578536523136</v>
+      </c>
+      <c r="S251">
+        <v>0.05123255924298435</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>fish11</v>
+      </c>
+      <c r="B252">
+        <v>0.07644435678373196</v>
+      </c>
+      <c r="C252">
+        <v>0.15548489078960032</v>
+      </c>
+      <c r="D252">
+        <v>0.17277336699343113</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>0.9770127084932284</v>
+      </c>
+      <c r="G252">
+        <v>0.02298729150677155</v>
+      </c>
+      <c r="H252">
+        <v>0.8696832710194463</v>
+      </c>
+      <c r="I252">
+        <v>0.22781752190787824</v>
+      </c>
+      <c r="J252">
+        <v>0.059470035872268595</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>0.00465193376092968</v>
+      </c>
+      <c r="M252">
+        <v>0.7401794131551984</v>
+      </c>
+      <c r="N252">
+        <v>0</v>
+      </c>
+      <c r="O252">
+        <v>0.003028638713480595</v>
+      </c>
+      <c r="P252">
+        <v>0.0066253079068961055</v>
+      </c>
+      <c r="Q252">
+        <v>0.9821651954980185</v>
+      </c>
+      <c r="R252">
+        <v>0.011209496595085477</v>
+      </c>
+      <c r="S252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>fish12</v>
+      </c>
+      <c r="B253">
+        <v>0.11753027939303509</v>
+      </c>
+      <c r="C253">
+        <v>0.17484409396515313</v>
+      </c>
+      <c r="D253">
+        <v>0.2507118422751999</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>1</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
+      </c>
+      <c r="H253">
+        <v>0.8319077794260468</v>
+      </c>
+      <c r="I253">
+        <v>0.18445804857118542</v>
+      </c>
+      <c r="J253">
+        <v>0.0844860668473468</v>
+      </c>
+      <c r="K253">
+        <v>0</v>
+      </c>
+      <c r="L253">
+        <v>0.028182661835874475</v>
+      </c>
+      <c r="M253">
+        <v>0.7138638026775923</v>
+      </c>
+      <c r="N253">
+        <v>0</v>
+      </c>
+      <c r="O253">
+        <v>0.02623759214994194</v>
+      </c>
+      <c r="P253">
+        <v>0.03379640031710844</v>
+      </c>
+      <c r="Q253">
+        <v>0.9355246465412863</v>
+      </c>
+      <c r="R253">
+        <v>0</v>
+      </c>
+      <c r="S253">
+        <v>0.0306789531416052</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>fish13</v>
+      </c>
+      <c r="B254">
+        <v>0.06331535046182488</v>
+      </c>
+      <c r="C254">
+        <v>0.1505492681775706</v>
+      </c>
+      <c r="D254">
+        <v>0.21731144261382113</v>
+      </c>
+      <c r="E254">
+        <v>0.04768148102720952</v>
+      </c>
+      <c r="F254">
+        <v>0.9459817297911152</v>
+      </c>
+      <c r="G254">
+        <v>0.0063367891816753135</v>
+      </c>
+      <c r="H254">
+        <v>0.8718954108529523</v>
+      </c>
+      <c r="I254">
+        <v>0.21213279637904037</v>
+      </c>
+      <c r="J254">
+        <v>0.04056105195378272</v>
+      </c>
+      <c r="K254">
+        <v>0.04311442747392336</v>
+      </c>
+      <c r="L254">
+        <v>0</v>
+      </c>
+      <c r="M254">
+        <v>0.79788542145634</v>
+      </c>
+      <c r="N254">
+        <v>0.012861174700731531</v>
+      </c>
+      <c r="O254">
+        <v>0</v>
+      </c>
+      <c r="P254">
+        <v>0.02976924419541864</v>
+      </c>
+      <c r="Q254">
+        <v>0.9702307558045813</v>
+      </c>
+      <c r="R254">
+        <v>0</v>
+      </c>
+      <c r="S254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>fish14</v>
+      </c>
+      <c r="B255">
+        <v>0.11209234522508385</v>
+      </c>
+      <c r="C255">
+        <v>0.12179426924871842</v>
+      </c>
+      <c r="D255">
+        <v>0.15423834318891616</v>
+      </c>
+      <c r="E255">
+        <v>0.012929655510466912</v>
+      </c>
+      <c r="F255">
+        <v>0.9791538836449891</v>
+      </c>
+      <c r="G255">
+        <v>0.007916460844544032</v>
+      </c>
+      <c r="H255">
+        <v>0.8819792990842733</v>
+      </c>
+      <c r="I255">
+        <v>0.19214381553727913</v>
+      </c>
+      <c r="J255">
+        <v>0.03518657096302235</v>
+      </c>
+      <c r="K255">
+        <v>0.014050148211206901</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="M255">
+        <v>0.7288127233368606</v>
+      </c>
+      <c r="N255">
+        <v>0.0627191375086412</v>
+      </c>
+      <c r="O255">
+        <v>0.02205772008986571</v>
+      </c>
+      <c r="P255">
+        <v>0.00537233714665116</v>
+      </c>
+      <c r="Q255">
+        <v>0.9747720920834937</v>
+      </c>
+      <c r="R255">
+        <v>0.019855570769855176</v>
+      </c>
+      <c r="S255">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>fish15</v>
+      </c>
+      <c r="B256">
+        <v>0.10809775908105908</v>
+      </c>
+      <c r="C256">
+        <v>0.14825969866358008</v>
+      </c>
+      <c r="D256">
+        <v>0.192310664265544</v>
+      </c>
+      <c r="E256">
+        <v>0.025738805745837607</v>
+      </c>
+      <c r="F256">
+        <v>0.9742611942541624</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0.856739589815943</v>
+      </c>
+      <c r="I256">
+        <v>0.2211640717832257</v>
+      </c>
+      <c r="J256">
+        <v>0.08241461412766339</v>
+      </c>
+      <c r="K256">
+        <v>0.037321863333646</v>
+      </c>
+      <c r="L256">
+        <v>0</v>
+      </c>
+      <c r="M256">
+        <v>0.7286356999038359</v>
+      </c>
+      <c r="N256">
+        <v>0</v>
+      </c>
+      <c r="O256">
+        <v>0.046877936424036634</v>
+      </c>
+      <c r="P256">
+        <v>0.017299538883767954</v>
+      </c>
+      <c r="Q256">
+        <v>0.9541620964019671</v>
+      </c>
+      <c r="R256">
+        <v>0</v>
+      </c>
+      <c r="S256">
+        <v>0.028538364714264804</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>fish16</v>
+      </c>
+      <c r="B257">
+        <v>0.08565795652911579</v>
+      </c>
+      <c r="C257">
+        <v>0.17254607300901806</v>
+      </c>
+      <c r="D257">
+        <v>0.20924096251891214</v>
+      </c>
+      <c r="E257">
+        <v>0.050180152593383216</v>
+      </c>
+      <c r="F257">
+        <v>0.913463259551566</v>
+      </c>
+      <c r="G257">
+        <v>0.03635658785505077</v>
+      </c>
+      <c r="H257">
+        <v>0.8519882010099432</v>
+      </c>
+      <c r="I257">
+        <v>0.21567048617940235</v>
+      </c>
+      <c r="J257">
+        <v>0.0357900254424557</v>
+      </c>
+      <c r="K257">
+        <v>0</v>
+      </c>
+      <c r="L257">
+        <v>0</v>
+      </c>
+      <c r="M257">
+        <v>0.7499188260011745</v>
+      </c>
+      <c r="N257">
+        <v>0.011344774313036647</v>
+      </c>
+      <c r="O257">
+        <v>0.013237224948609787</v>
+      </c>
+      <c r="P257">
+        <v>0.006392551531840996</v>
+      </c>
+      <c r="Q257">
+        <v>0.9524511930691597</v>
+      </c>
+      <c r="R257">
+        <v>0.030203752594568995</v>
+      </c>
+      <c r="S257">
+        <v>0.01095250280443029</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>fish17</v>
+      </c>
+      <c r="B258">
+        <v>0.07522070104452375</v>
+      </c>
+      <c r="C258">
+        <v>0.1661116111351485</v>
+      </c>
+      <c r="D258">
+        <v>0.23619022573297171</v>
+      </c>
+      <c r="E258">
+        <v>0.0009491194679013009</v>
+      </c>
+      <c r="F258">
+        <v>0.9990508805320987</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>0</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258">
+        <v>0.025287960784282276</v>
+      </c>
+      <c r="L258">
+        <v>0.01834725729567231</v>
+      </c>
+      <c r="M258">
+        <v>0.7597968318557</v>
+      </c>
+      <c r="N258">
+        <v>0</v>
+      </c>
+      <c r="O258">
+        <v>0</v>
+      </c>
+      <c r="P258">
+        <v>0.018613406558939935</v>
+      </c>
+      <c r="Q258">
+        <v>0.98138659344106</v>
+      </c>
+      <c r="R258">
+        <v>0</v>
+      </c>
+      <c r="S258">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>fish18</v>
+      </c>
+      <c r="B259">
+        <v>0.11432470356176669</v>
+      </c>
+      <c r="C259">
+        <v>0.11430157781571496</v>
+      </c>
+      <c r="D259">
+        <v>0.1786766892566553</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>0.9961628921077671</v>
+      </c>
+      <c r="G259">
+        <v>0.0038371078922328893</v>
+      </c>
+      <c r="H259">
+        <v>0.8742750391354589</v>
+      </c>
+      <c r="I259">
+        <v>0.20547101253637723</v>
+      </c>
+      <c r="J259">
+        <v>0.01917340161051</v>
+      </c>
+      <c r="K259">
+        <v>0</v>
+      </c>
+      <c r="L259">
+        <v>0</v>
+      </c>
+      <c r="M259">
+        <v>0.754751962029062</v>
+      </c>
+      <c r="N259">
+        <v>0.011359527800299673</v>
+      </c>
+      <c r="O259">
+        <v>0</v>
+      </c>
+      <c r="P259">
+        <v>0.02033424615388606</v>
+      </c>
+      <c r="Q259">
+        <v>0.9726974639159078</v>
+      </c>
+      <c r="R259">
+        <v>0</v>
+      </c>
+      <c r="S259">
+        <v>0.006968289930206142</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>fish19</v>
+      </c>
+      <c r="B260">
+        <v>0.09500637958428879</v>
+      </c>
+      <c r="C260">
+        <v>0.18673847148188194</v>
+      </c>
+      <c r="D260">
+        <v>0.20033754306659063</v>
+      </c>
+      <c r="E260">
+        <v>0.039898991797668884</v>
+      </c>
+      <c r="F260">
+        <v>0.9601010082023311</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>0.9173968495748511</v>
+      </c>
+      <c r="I260">
+        <v>0.19363034128919537</v>
+      </c>
+      <c r="J260">
+        <v>0.025626067535611478</v>
+      </c>
+      <c r="K260">
+        <v>0</v>
+      </c>
+      <c r="L260">
+        <v>0</v>
+      </c>
+      <c r="M260">
+        <v>0.7674245431691041</v>
+      </c>
+      <c r="N260">
+        <v>0</v>
+      </c>
+      <c r="O260">
+        <v>0.0076977270064456</v>
+      </c>
+      <c r="P260">
+        <v>0</v>
+      </c>
+      <c r="Q260">
+        <v>0.9790541183708441</v>
+      </c>
+      <c r="R260">
+        <v>0</v>
+      </c>
+      <c r="S260">
+        <v>0.020945881629155904</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>fish20</v>
+      </c>
+      <c r="B261">
+        <v>0.09818102509360206</v>
+      </c>
+      <c r="C261">
+        <v>0.16948281998107181</v>
+      </c>
+      <c r="D261">
+        <v>0.2082591161917668</v>
+      </c>
+      <c r="E261">
+        <v>0.01642971393401949</v>
+      </c>
+      <c r="F261">
+        <v>0.9530166895849577</v>
+      </c>
+      <c r="G261">
+        <v>0.03055359648102284</v>
+      </c>
+      <c r="H261">
+        <v>0.835468631901117</v>
+      </c>
+      <c r="I261">
+        <v>0.17748543417714258</v>
+      </c>
+      <c r="J261">
+        <v>0.042751590186688115</v>
+      </c>
+      <c r="K261">
+        <v>0</v>
+      </c>
+      <c r="L261">
+        <v>0</v>
+      </c>
+      <c r="M261">
+        <v>0.7441499508517931</v>
+      </c>
+      <c r="N261">
+        <v>0.003661072930412985</v>
+      </c>
+      <c r="O261">
+        <v>0.021590503324304122</v>
+      </c>
+      <c r="P261">
+        <v>0</v>
+      </c>
+      <c r="Q261">
+        <v>0.9881240733440169</v>
+      </c>
+      <c r="R261">
+        <v>0.011875926655983192</v>
+      </c>
+      <c r="S261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>animal1</v>
+      </c>
+      <c r="B262">
+        <v>0.05812215836116378</v>
+      </c>
+      <c r="C262">
+        <v>0.07453029467578387</v>
+      </c>
+      <c r="D262">
+        <v>0.06816624662154568</v>
+      </c>
+      <c r="E262">
+        <v>0.06245878875809034</v>
+      </c>
+      <c r="F262">
+        <v>0.5111893555522986</v>
+      </c>
+      <c r="G262">
+        <v>0.426351855689611</v>
+      </c>
+      <c r="H262">
+        <v>0.6150801721916836</v>
+      </c>
+      <c r="I262">
+        <v>0.23467753515403617</v>
+      </c>
+      <c r="J262">
+        <v>0.4439590967958822</v>
+      </c>
+      <c r="K262">
+        <v>0.23766045140866587</v>
+      </c>
+      <c r="L262">
+        <v>0.36172837357036197</v>
+      </c>
+      <c r="M262">
+        <v>0.2963775345002899</v>
+      </c>
+      <c r="N262">
+        <v>0.0008956161017942895</v>
+      </c>
+      <c r="O262">
+        <v>0</v>
+      </c>
+      <c r="P262">
+        <v>0.11186267202722519</v>
+      </c>
+      <c r="Q262">
+        <v>0.5437622662407682</v>
+      </c>
+      <c r="R262">
+        <v>0.1461461402392357</v>
+      </c>
+      <c r="S262">
+        <v>0.198228921492771</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>animal2</v>
+      </c>
+      <c r="B263">
+        <v>0.05651171371215555</v>
+      </c>
+      <c r="C263">
+        <v>0.1242930204011321</v>
+      </c>
+      <c r="D263">
+        <v>0.04388948815734161</v>
+      </c>
+      <c r="E263">
+        <v>0.10035011891050234</v>
+      </c>
+      <c r="F263">
+        <v>0.5197778806856126</v>
+      </c>
+      <c r="G263">
+        <v>0.379872000403885</v>
+      </c>
+      <c r="H263">
+        <v>0.6359258574530618</v>
+      </c>
+      <c r="I263">
+        <v>0.20333526720713516</v>
+      </c>
+      <c r="J263">
+        <v>0.4571206442084186</v>
+      </c>
+      <c r="K263">
+        <v>0.1956460759836201</v>
+      </c>
+      <c r="L263">
+        <v>0.3265340344162163</v>
+      </c>
+      <c r="M263">
+        <v>0.2976921160311268</v>
+      </c>
+      <c r="N263">
+        <v>0.022391913937625123</v>
+      </c>
+      <c r="O263">
+        <v>0.0007422851576401407</v>
+      </c>
+      <c r="P263">
+        <v>0.14513041660617554</v>
+      </c>
+      <c r="Q263">
+        <v>0.4659294785584996</v>
+      </c>
+      <c r="R263">
+        <v>0.20705904568516872</v>
+      </c>
+      <c r="S263">
+        <v>0.18188105915015615</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>animal3</v>
+      </c>
+      <c r="B264">
+        <v>0.037167044491483045</v>
+      </c>
+      <c r="C264">
+        <v>0.06698278653560204</v>
+      </c>
+      <c r="D264">
+        <v>0.10946944925433819</v>
+      </c>
+      <c r="E264">
+        <v>0.08335798988559975</v>
+      </c>
+      <c r="F264">
+        <v>0.5205878654615194</v>
+      </c>
+      <c r="G264">
+        <v>0.39605414465288075</v>
+      </c>
+      <c r="H264">
+        <v>0.6772914297879236</v>
+      </c>
+      <c r="I264">
+        <v>0.17451588311797475</v>
+      </c>
+      <c r="J264">
+        <v>0.4218305098472818</v>
+      </c>
+      <c r="K264">
+        <v>0.19331543305405136</v>
+      </c>
+      <c r="L264">
+        <v>0.3457587266751193</v>
+      </c>
+      <c r="M264">
+        <v>0.2902812296780929</v>
+      </c>
+      <c r="N264">
+        <v>0</v>
+      </c>
+      <c r="O264">
+        <v>0</v>
+      </c>
+      <c r="P264">
+        <v>0.14179521178440027</v>
+      </c>
+      <c r="Q264">
+        <v>0.48569115880058855</v>
+      </c>
+      <c r="R264">
+        <v>0.15752497172034266</v>
+      </c>
+      <c r="S264">
+        <v>0.21498865769466857</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>animal4</v>
+      </c>
+      <c r="B265">
+        <v>0.06926091021465369</v>
+      </c>
+      <c r="C265">
+        <v>0.0802896853710276</v>
+      </c>
+      <c r="D265">
+        <v>0.05703794264251581</v>
+      </c>
+      <c r="E265">
+        <v>0.11600754374955335</v>
+      </c>
+      <c r="F265">
+        <v>0.48828868135229697</v>
+      </c>
+      <c r="G265">
+        <v>0.3957037748981497</v>
+      </c>
+      <c r="H265">
+        <v>0.6585846660469673</v>
+      </c>
+      <c r="I265">
+        <v>0.1961380411111752</v>
+      </c>
+      <c r="J265">
+        <v>0.4431871731217019</v>
+      </c>
+      <c r="K265">
+        <v>0.1489005400158886</v>
+      </c>
+      <c r="L265">
+        <v>0.3317032354384962</v>
+      </c>
+      <c r="M265">
+        <v>0.3065093946555005</v>
+      </c>
+      <c r="N265">
+        <v>0.03285837051014341</v>
+      </c>
+      <c r="O265">
+        <v>0.01891941441298404</v>
+      </c>
+      <c r="P265">
+        <v>0.09925860384502179</v>
+      </c>
+      <c r="Q265">
+        <v>0.4872045870668073</v>
+      </c>
+      <c r="R265">
+        <v>0.19731393839777775</v>
+      </c>
+      <c r="S265">
+        <v>0.21622287069039312</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>animal5</v>
+      </c>
+      <c r="B266">
+        <v>0.06362578748164734</v>
+      </c>
+      <c r="C266">
+        <v>0.07678876341274671</v>
+      </c>
+      <c r="D266">
+        <v>0.13994275477337006</v>
+      </c>
+      <c r="E266">
+        <v>0.12153964250441632</v>
+      </c>
+      <c r="F266">
+        <v>0.4770041877276772</v>
+      </c>
+      <c r="G266">
+        <v>0.4014561697679065</v>
+      </c>
+      <c r="H266">
+        <v>0.6331835243833822</v>
+      </c>
+      <c r="I266">
+        <v>0.2299905831740998</v>
+      </c>
+      <c r="J266">
+        <v>0.45198699280591675</v>
+      </c>
+      <c r="K266">
+        <v>0.1882822956685145</v>
+      </c>
+      <c r="L266">
+        <v>0.3555469176046019</v>
+      </c>
+      <c r="M266">
+        <v>0.3063040841040463</v>
+      </c>
+      <c r="N266">
+        <v>0.010666091253384644</v>
+      </c>
+      <c r="O266">
+        <v>0.012524663808263843</v>
+      </c>
+      <c r="P266">
+        <v>0.11643780481319475</v>
+      </c>
+      <c r="Q266">
+        <v>0.5189928239297171</v>
+      </c>
+      <c r="R266">
+        <v>0.19722691533435774</v>
+      </c>
+      <c r="S266">
+        <v>0.16734245592273037</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>animal6</v>
+      </c>
+      <c r="B267">
+        <v>0.03559031974462008</v>
+      </c>
+      <c r="C267">
+        <v>0.07410233654697174</v>
+      </c>
+      <c r="D267">
+        <v>0.09454918865482342</v>
+      </c>
+      <c r="E267">
+        <v>0.08958968579750283</v>
+      </c>
+      <c r="F267">
+        <v>0.5119225880290911</v>
+      </c>
+      <c r="G267">
+        <v>0.39848772617340605</v>
+      </c>
+      <c r="H267">
+        <v>0.6638349862707074</v>
+      </c>
+      <c r="I267">
+        <v>0.2265542537057257</v>
+      </c>
+      <c r="J267">
+        <v>0.4517873124895998</v>
+      </c>
+      <c r="K267">
+        <v>0.18511479368566572</v>
+      </c>
+      <c r="L267">
+        <v>0.32495146078407816</v>
+      </c>
+      <c r="M267">
+        <v>0.30390707928509336</v>
+      </c>
+      <c r="N267">
+        <v>0</v>
+      </c>
+      <c r="O267">
+        <v>0</v>
+      </c>
+      <c r="P267">
+        <v>0</v>
+      </c>
+      <c r="Q267">
+        <v>0</v>
+      </c>
+      <c r="R267">
+        <v>0</v>
+      </c>
+      <c r="S267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>animal7</v>
+      </c>
+      <c r="B268">
+        <v>0.048760789335309085</v>
+      </c>
+      <c r="C268">
+        <v>0.07715597533446712</v>
+      </c>
+      <c r="D268">
+        <v>0.11077732551068284</v>
+      </c>
+      <c r="E268">
+        <v>0.10390861141567881</v>
+      </c>
+      <c r="F268">
+        <v>0.48932819829624097</v>
+      </c>
+      <c r="G268">
+        <v>0.4067631902880802</v>
+      </c>
+      <c r="H268">
+        <v>0.6653547456320493</v>
+      </c>
+      <c r="I268">
+        <v>0.1552462266227861</v>
+      </c>
+      <c r="J268">
+        <v>0.4173498473424744</v>
+      </c>
+      <c r="K268">
+        <v>0.23819433907637122</v>
+      </c>
+      <c r="L268">
+        <v>0.3149576462975489</v>
+      </c>
+      <c r="M268">
+        <v>0.3374525005110738</v>
+      </c>
+      <c r="N268">
+        <v>0.03070303448933815</v>
+      </c>
+      <c r="O268">
+        <v>0</v>
+      </c>
+      <c r="P268">
+        <v>0.08771983777194936</v>
+      </c>
+      <c r="Q268">
+        <v>0.5044328882889092</v>
+      </c>
+      <c r="R268">
+        <v>0.20920189656693167</v>
+      </c>
+      <c r="S268">
+        <v>0.19864537737220975</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>animal8</v>
+      </c>
+      <c r="B269">
+        <v>0.0913468846795975</v>
+      </c>
+      <c r="C269">
+        <v>0.12722255762987508</v>
+      </c>
+      <c r="D269">
+        <v>0.09857951490415166</v>
+      </c>
+      <c r="E269">
+        <v>0.07339935440314502</v>
+      </c>
+      <c r="F269">
+        <v>0.507184976027948</v>
+      </c>
+      <c r="G269">
+        <v>0.41941566956890697</v>
+      </c>
+      <c r="H269">
+        <v>0.6398124473645063</v>
+      </c>
+      <c r="I269">
+        <v>0.2094800678866367</v>
+      </c>
+      <c r="J269">
+        <v>0.42436113935744635</v>
+      </c>
+      <c r="K269">
+        <v>0.20516684089342352</v>
+      </c>
+      <c r="L269">
+        <v>0.3279683373873932</v>
+      </c>
+      <c r="M269">
+        <v>0.33822283251845364</v>
+      </c>
+      <c r="N269">
+        <v>0.03164017556256826</v>
+      </c>
+      <c r="O269">
+        <v>0</v>
+      </c>
+      <c r="P269">
+        <v>0.12136158815971317</v>
+      </c>
+      <c r="Q269">
+        <v>0.5214010623703167</v>
+      </c>
+      <c r="R269">
+        <v>0.1484592151310446</v>
+      </c>
+      <c r="S269">
+        <v>0.2087781343389256</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>animal9</v>
+      </c>
+      <c r="B270">
+        <v>0.07643867294562265</v>
+      </c>
+      <c r="C270">
+        <v>0.059270392214149564</v>
+      </c>
+      <c r="D270">
+        <v>0.09096480793005646</v>
+      </c>
+      <c r="E270">
+        <v>0.14046493824511336</v>
+      </c>
+      <c r="F270">
+        <v>0.45719394863361984</v>
+      </c>
+      <c r="G270">
+        <v>0.4023411131212668</v>
+      </c>
+      <c r="H270">
+        <v>0.6278083520443628</v>
+      </c>
+      <c r="I270">
+        <v>0.2090879306243855</v>
+      </c>
+      <c r="J270">
+        <v>0.44553535135552097</v>
+      </c>
+      <c r="K270">
+        <v>0.18767295977883358</v>
+      </c>
+      <c r="L270">
+        <v>0.35424377090321574</v>
+      </c>
+      <c r="M270">
+        <v>0.3111231413476257</v>
+      </c>
+      <c r="N270">
+        <v>0.0017601899950145739</v>
+      </c>
+      <c r="O270">
+        <v>0</v>
+      </c>
+      <c r="P270">
+        <v>0.10251609778661841</v>
+      </c>
+      <c r="Q270">
+        <v>0.5143732194542601</v>
+      </c>
+      <c r="R270">
+        <v>0.1779084172775987</v>
+      </c>
+      <c r="S270">
+        <v>0.2052022654815229</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>animal10</v>
+      </c>
+      <c r="B271">
+        <v>0.08239177731820035</v>
+      </c>
+      <c r="C271">
+        <v>0.08072057719998708</v>
+      </c>
+      <c r="D271">
+        <v>0.07881108970205039</v>
+      </c>
+      <c r="E271">
+        <v>0.09782177969914448</v>
+      </c>
+      <c r="F271">
+        <v>0.4993145867826958</v>
+      </c>
+      <c r="G271">
+        <v>0.40286363351815957</v>
+      </c>
+      <c r="H271">
+        <v>0.6909416324401119</v>
+      </c>
+      <c r="I271">
+        <v>0.21151351201072155</v>
+      </c>
+      <c r="J271">
+        <v>0.4289897152734596</v>
+      </c>
+      <c r="K271">
+        <v>0.19541556012520386</v>
+      </c>
+      <c r="L271">
+        <v>0.3235942928860653</v>
+      </c>
+      <c r="M271">
+        <v>0.3139643709294475</v>
+      </c>
+      <c r="N271">
+        <v>0</v>
+      </c>
+      <c r="O271">
+        <v>0</v>
+      </c>
+      <c r="P271">
+        <v>0.09860175759657343</v>
+      </c>
+      <c r="Q271">
+        <v>0.5218299414308845</v>
+      </c>
+      <c r="R271">
+        <v>0.17058460097091</v>
+      </c>
+      <c r="S271">
+        <v>0.2089837000016322</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>animal11</v>
+      </c>
+      <c r="B272">
+        <v>0.07631609968285492</v>
+      </c>
+      <c r="C272">
+        <v>0.1121709528652535</v>
+      </c>
+      <c r="D272">
+        <v>0.10459783278348837</v>
+      </c>
+      <c r="E272">
+        <v>0.07427149203210763</v>
+      </c>
+      <c r="F272">
+        <v>0.5211898082325023</v>
+      </c>
+      <c r="G272">
+        <v>0.40453869973539014</v>
+      </c>
+      <c r="H272">
+        <v>0.6431921839613352</v>
+      </c>
+      <c r="I272">
+        <v>0.23638613652942372</v>
+      </c>
+      <c r="J272">
+        <v>0.4263194666610664</v>
+      </c>
+      <c r="K272">
+        <v>0.16925888932463234</v>
+      </c>
+      <c r="L272">
+        <v>0.37710927218384993</v>
+      </c>
+      <c r="M272">
+        <v>0.21556391723874474</v>
+      </c>
+      <c r="N272">
+        <v>0.03908812582653325</v>
+      </c>
+      <c r="O272">
+        <v>0.012072625953861152</v>
+      </c>
+      <c r="P272">
+        <v>0.08106615269163686</v>
+      </c>
+      <c r="Q272">
+        <v>0.5202510565209294</v>
+      </c>
+      <c r="R272">
+        <v>0.19504925378806362</v>
+      </c>
+      <c r="S272">
+        <v>0.2036335369993701</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>animal12</v>
+      </c>
+      <c r="B273">
+        <v>0.10497030377719738</v>
+      </c>
+      <c r="C273">
+        <v>0.06322422506983293</v>
+      </c>
+      <c r="D273">
+        <v>0.10892680732299163</v>
+      </c>
+      <c r="E273">
+        <v>0.12071096965883371</v>
+      </c>
+      <c r="F273">
+        <v>0.5001302534532668</v>
+      </c>
+      <c r="G273">
+        <v>0.37915877688789956</v>
+      </c>
+      <c r="H273">
+        <v>0.6605335989915304</v>
+      </c>
+      <c r="I273">
+        <v>0.21358110931839927</v>
+      </c>
+      <c r="J273">
+        <v>0.47884659071707364</v>
+      </c>
+      <c r="K273">
+        <v>0.19219489476317847</v>
+      </c>
+      <c r="L273">
+        <v>0.3366356506479994</v>
+      </c>
+      <c r="M273">
+        <v>0.3145975750079175</v>
+      </c>
+      <c r="N273">
+        <v>0</v>
+      </c>
+      <c r="O273">
+        <v>0.01086354403424319</v>
+      </c>
+      <c r="P273">
+        <v>0.0965889659647802</v>
+      </c>
+      <c r="Q273">
+        <v>0.5469282292604265</v>
+      </c>
+      <c r="R273">
+        <v>0.13340262435128913</v>
+      </c>
+      <c r="S273">
+        <v>0.22308018042350422</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>animal13</v>
+      </c>
+      <c r="B274">
+        <v>0</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>0.10190370929667295</v>
+      </c>
+      <c r="F274">
+        <v>0.49945126248728383</v>
+      </c>
+      <c r="G274">
+        <v>0.39864502821604314</v>
+      </c>
+      <c r="H274">
+        <v>0.6757855710950114</v>
+      </c>
+      <c r="I274">
+        <v>0.20726421321768446</v>
+      </c>
+      <c r="J274">
+        <v>0.4214495547974698</v>
+      </c>
+      <c r="K274">
+        <v>0.17268136806556586</v>
+      </c>
+      <c r="L274">
+        <v>0.34997778473227875</v>
+      </c>
+      <c r="M274">
+        <v>0.33897180714822617</v>
+      </c>
+      <c r="N274">
+        <v>0.009954243995920124</v>
+      </c>
+      <c r="O274">
+        <v>0</v>
+      </c>
+      <c r="P274">
+        <v>0.1510159522918755</v>
+      </c>
+      <c r="Q274">
+        <v>0.4884832892203944</v>
+      </c>
+      <c r="R274">
+        <v>0.17054667391601822</v>
+      </c>
+      <c r="S274">
+        <v>0.18995408457171203</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>animal14</v>
+      </c>
+      <c r="B275">
+        <v>0.059947437140661586</v>
+      </c>
+      <c r="C275">
+        <v>0.07344477234849073</v>
+      </c>
+      <c r="D275">
+        <v>0.04360152269662283</v>
+      </c>
+      <c r="E275">
+        <v>0.10834840490291023</v>
+      </c>
+      <c r="F275">
+        <v>0.48520160240825255</v>
+      </c>
+      <c r="G275">
+        <v>0.40644999268883714</v>
+      </c>
+      <c r="H275">
+        <v>0.6524956776054781</v>
+      </c>
+      <c r="I275">
+        <v>0.2111344190319943</v>
+      </c>
+      <c r="J275">
+        <v>0.4167121184328063</v>
+      </c>
+      <c r="K275">
+        <v>0.21470022122133298</v>
+      </c>
+      <c r="L275">
+        <v>0.294170924350276</v>
+      </c>
+      <c r="M275">
+        <v>0.31711506974166737</v>
+      </c>
+      <c r="N275">
+        <v>0</v>
+      </c>
+      <c r="O275">
+        <v>0</v>
+      </c>
+      <c r="P275">
+        <v>0.16682405632983355</v>
+      </c>
+      <c r="Q275">
+        <v>0.4488374058418361</v>
+      </c>
+      <c r="R275">
+        <v>0.19015538173087804</v>
+      </c>
+      <c r="S275">
+        <v>0.19418315609745226</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>animal15</v>
+      </c>
+      <c r="B276">
+        <v>0.11737156059687123</v>
+      </c>
+      <c r="C276">
+        <v>0.09603820238373927</v>
+      </c>
+      <c r="D276">
+        <v>0.10319142406503992</v>
+      </c>
+      <c r="E276">
+        <v>0.08513119113487362</v>
+      </c>
+      <c r="F276">
+        <v>0.4938983875546815</v>
+      </c>
+      <c r="G276">
+        <v>0.42097042131044493</v>
+      </c>
+      <c r="H276">
+        <v>0.6085153062534642</v>
+      </c>
+      <c r="I276">
+        <v>0.22110787537954152</v>
+      </c>
+      <c r="J276">
+        <v>0.4469704634896145</v>
+      </c>
+      <c r="K276">
+        <v>0.17874468530658963</v>
+      </c>
+      <c r="L276">
+        <v>0.32701038541150707</v>
+      </c>
+      <c r="M276">
+        <v>0.3161486149509716</v>
+      </c>
+      <c r="N276">
+        <v>0.011639523065960944</v>
+      </c>
+      <c r="O276">
+        <v>0</v>
+      </c>
+      <c r="P276">
+        <v>0.13110476512939223</v>
+      </c>
+      <c r="Q276">
+        <v>0.4945883768978169</v>
+      </c>
+      <c r="R276">
+        <v>0.17323746553250793</v>
+      </c>
+      <c r="S276">
+        <v>0.201069392440283</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>animal16</v>
+      </c>
+      <c r="B277">
+        <v>0.10943891115591795</v>
+      </c>
+      <c r="C277">
+        <v>0.06507242468478532</v>
+      </c>
+      <c r="D277">
+        <v>0.03573251833101115</v>
+      </c>
+      <c r="E277">
+        <v>0.057782267917700046</v>
+      </c>
+      <c r="F277">
+        <v>0.5328202050688949</v>
+      </c>
+      <c r="G277">
+        <v>0.4093975270134049</v>
+      </c>
+      <c r="H277">
+        <v>0.6983675619199374</v>
+      </c>
+      <c r="I277">
+        <v>0.19037626887121079</v>
+      </c>
+      <c r="J277">
+        <v>0.4616444732224342</v>
+      </c>
+      <c r="K277">
+        <v>0.2078513429330032</v>
+      </c>
+      <c r="L277">
+        <v>0.35004672277559273</v>
+      </c>
+      <c r="M277">
+        <v>0.27420833372226905</v>
+      </c>
+      <c r="N277">
+        <v>0</v>
+      </c>
+      <c r="O277">
+        <v>0.01994366625889976</v>
+      </c>
+      <c r="P277">
+        <v>0.09849767774230364</v>
+      </c>
+      <c r="Q277">
+        <v>0.5785311863838108</v>
+      </c>
+      <c r="R277">
+        <v>0.16655454195249633</v>
+      </c>
+      <c r="S277">
+        <v>0.15641659392138918</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>animal17</v>
+      </c>
+      <c r="B278">
+        <v>0.07710550712812897</v>
+      </c>
+      <c r="C278">
+        <v>0.08063338602120541</v>
+      </c>
+      <c r="D278">
+        <v>0.08053139189087068</v>
+      </c>
+      <c r="E278">
+        <v>0.0941824399707418</v>
+      </c>
+      <c r="F278">
+        <v>0.5079888730919091</v>
+      </c>
+      <c r="G278">
+        <v>0.3978286869373492</v>
+      </c>
+      <c r="H278">
+        <v>0.6621018567553366</v>
+      </c>
+      <c r="I278">
+        <v>0.1887093139543262</v>
+      </c>
+      <c r="J278">
+        <v>0.4503869661989795</v>
+      </c>
+      <c r="K278">
+        <v>0.19677639947789954</v>
+      </c>
+      <c r="L278">
+        <v>0.40283484309395773</v>
+      </c>
+      <c r="M278">
+        <v>0.29005697497644145</v>
+      </c>
+      <c r="N278">
+        <v>0.022730843363469685</v>
+      </c>
+      <c r="O278">
+        <v>0.006251150639009765</v>
+      </c>
+      <c r="P278">
+        <v>0.15159445086838044</v>
+      </c>
+      <c r="Q278">
+        <v>0.49707529303656656</v>
+      </c>
+      <c r="R278">
+        <v>0.15090997645030416</v>
+      </c>
+      <c r="S278">
+        <v>0.20042027964474882</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>animal18</v>
+      </c>
+      <c r="B279">
+        <v>0.07229647905448552</v>
+      </c>
+      <c r="C279">
+        <v>0.10336201480161525</v>
+      </c>
+      <c r="D279">
+        <v>0.08694606539794109</v>
+      </c>
+      <c r="E279">
+        <v>0.11077596448406665</v>
+      </c>
+      <c r="F279">
+        <v>0.5004475286850765</v>
+      </c>
+      <c r="G279">
+        <v>0.38877650683085674</v>
+      </c>
+      <c r="H279">
+        <v>0.6639709650830127</v>
+      </c>
+      <c r="I279">
+        <v>0.24958493944818413</v>
+      </c>
+      <c r="J279">
+        <v>0.4391812751674981</v>
+      </c>
+      <c r="K279">
+        <v>0.18497843316656132</v>
+      </c>
+      <c r="L279">
+        <v>0.3725714197329521</v>
+      </c>
+      <c r="M279">
+        <v>0.28608955029720373</v>
+      </c>
+      <c r="N279">
+        <v>0.013501080844839293</v>
+      </c>
+      <c r="O279">
+        <v>0</v>
+      </c>
+      <c r="P279">
+        <v>0.11167749223366942</v>
+      </c>
+      <c r="Q279">
+        <v>0.5049014844082962</v>
+      </c>
+      <c r="R279">
+        <v>0.1576597678868465</v>
+      </c>
+      <c r="S279">
+        <v>0.2257612554711878</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>animal19</v>
+      </c>
+      <c r="B280">
+        <v>0.07871294584101864</v>
+      </c>
+      <c r="C280">
+        <v>0.09147162292342909</v>
+      </c>
+      <c r="D280">
+        <v>0.07294057327010944</v>
+      </c>
+      <c r="E280">
+        <v>0.06053976430173368</v>
+      </c>
+      <c r="F280">
+        <v>0.4938796398235868</v>
+      </c>
+      <c r="G280">
+        <v>0.4455805958746796</v>
+      </c>
+      <c r="H280">
+        <v>0.6707798720459902</v>
+      </c>
+      <c r="I280">
+        <v>0.2020614565450119</v>
+      </c>
+      <c r="J280">
+        <v>0.4502803304737684</v>
+      </c>
+      <c r="K280">
+        <v>0</v>
+      </c>
+      <c r="L280">
+        <v>0</v>
+      </c>
+      <c r="M280">
+        <v>0</v>
+      </c>
+      <c r="N280">
+        <v>0</v>
+      </c>
+      <c r="O280">
+        <v>0</v>
+      </c>
+      <c r="P280">
+        <v>0.1147249747659157</v>
+      </c>
+      <c r="Q280">
+        <v>0.48260700774002896</v>
+      </c>
+      <c r="R280">
+        <v>0.16934670166061663</v>
+      </c>
+      <c r="S280">
+        <v>0.23332131583343882</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>animal20</v>
+      </c>
+      <c r="B281">
+        <v>0.14180740573491257</v>
+      </c>
+      <c r="C281">
+        <v>0.15115579715535082</v>
+      </c>
+      <c r="D281">
+        <v>0.05800882507650554</v>
+      </c>
+      <c r="E281">
+        <v>0.09649275851196089</v>
+      </c>
+      <c r="F281">
+        <v>0.4685094792458294</v>
+      </c>
+      <c r="G281">
+        <v>0.43499776224220965</v>
+      </c>
+      <c r="H281">
+        <v>0.665365121869434</v>
+      </c>
+      <c r="I281">
+        <v>0.25553765766124725</v>
+      </c>
+      <c r="J281">
+        <v>0.464330609774321</v>
+      </c>
+      <c r="K281">
+        <v>0.20624684718317476</v>
+      </c>
+      <c r="L281">
+        <v>0.4161125838951144</v>
+      </c>
+      <c r="M281">
+        <v>0.28266930278105784</v>
+      </c>
+      <c r="N281">
+        <v>0.0025627884572902264</v>
+      </c>
+      <c r="O281">
+        <v>0</v>
+      </c>
+      <c r="P281">
+        <v>0.12233740911380761</v>
+      </c>
+      <c r="Q281">
+        <v>0.5050371943961015</v>
+      </c>
+      <c r="R281">
+        <v>0.18831793594772941</v>
+      </c>
+      <c r="S281">
+        <v>0.1843074605423615</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S241"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S281"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O31"/>
+  <dimension ref="A1:Q32"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -14659,22 +17019,28 @@
         <v>flower</v>
       </c>
       <c r="J1" t="str">
+        <v>plant</v>
+      </c>
+      <c r="K1" t="str">
         <v>robin</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>canary</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>bird</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>sunfish</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>salmon</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>fish</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>animal</v>
       </c>
     </row>
     <row r="2">
@@ -14706,22 +17072,28 @@
         <v>0.15</v>
       </c>
       <c r="J2">
+        <v>0.06</v>
+      </c>
+      <c r="K2">
         <v>0.75</v>
       </c>
-      <c r="K2">
+      <c r="L2">
         <v>0.95</v>
       </c>
-      <c r="L2">
+      <c r="M2">
         <v>0.12</v>
       </c>
-      <c r="M2">
+      <c r="N2">
         <v>0.4</v>
       </c>
-      <c r="N2">
+      <c r="O2">
         <v>0.85</v>
       </c>
-      <c r="O2">
+      <c r="P2">
         <v>0.1</v>
+      </c>
+      <c r="Q2">
+        <v>0.08</v>
       </c>
     </row>
     <row r="3">
@@ -14753,22 +17125,28 @@
         <v>0.15</v>
       </c>
       <c r="J3">
+        <v>0.08</v>
+      </c>
+      <c r="K3">
         <v>0.3</v>
       </c>
-      <c r="K3">
+      <c r="L3">
         <v>0.85</v>
       </c>
-      <c r="L3">
+      <c r="M3">
         <v>0.1</v>
       </c>
-      <c r="M3">
+      <c r="N3">
         <v>0.6</v>
       </c>
-      <c r="N3">
+      <c r="O3">
         <v>0.85</v>
       </c>
-      <c r="O3">
+      <c r="P3">
         <v>0.15</v>
+      </c>
+      <c r="Q3">
+        <v>0.08</v>
       </c>
     </row>
     <row r="4">
@@ -14800,22 +17178,28 @@
         <v>0.1</v>
       </c>
       <c r="J4">
+        <v>0.06</v>
+      </c>
+      <c r="K4">
         <v>0.2</v>
       </c>
-      <c r="K4">
+      <c r="L4">
         <v>0.1</v>
       </c>
-      <c r="L4">
+      <c r="M4">
         <v>0.08</v>
       </c>
-      <c r="M4">
+      <c r="N4">
         <v>0.75</v>
       </c>
-      <c r="N4">
+      <c r="O4">
         <v>0.9</v>
       </c>
-      <c r="O4">
+      <c r="P4">
         <v>0.2</v>
+      </c>
+      <c r="Q4">
+        <v>0.08</v>
       </c>
     </row>
     <row r="5">
@@ -14847,22 +17231,28 @@
         <v>1</v>
       </c>
       <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
         <v>0.3</v>
       </c>
-      <c r="K5">
+      <c r="L5">
         <v>0.2</v>
       </c>
-      <c r="L5">
+      <c r="M5">
         <v>0.25</v>
       </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
       <c r="N5">
         <v>0</v>
       </c>
       <c r="O5">
         <v>0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -14903,13 +17293,19 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N6">
         <v>1</v>
       </c>
       <c r="O6">
         <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -14941,22 +17337,28 @@
         <v>0</v>
       </c>
       <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7">
         <v>0.7</v>
       </c>
-      <c r="K7">
+      <c r="L7">
         <v>0.8</v>
       </c>
-      <c r="L7">
+      <c r="M7">
         <v>0.75</v>
       </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
       <c r="N7">
         <v>0</v>
       </c>
       <c r="O7">
         <v>0</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0.4</v>
       </c>
     </row>
     <row r="8">
@@ -14988,7 +17390,7 @@
         <v>0.55</v>
       </c>
       <c r="J8">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="K8">
         <v>0.6</v>
@@ -14997,13 +17399,19 @@
         <v>0.6</v>
       </c>
       <c r="M8">
-        <v>0.85</v>
+        <v>0.6</v>
       </c>
       <c r="N8">
         <v>0.85</v>
       </c>
       <c r="O8">
         <v>0.85</v>
+      </c>
+      <c r="P8">
+        <v>0.85</v>
+      </c>
+      <c r="Q8">
+        <v>0.65</v>
       </c>
     </row>
     <row r="9">
@@ -15035,21 +17443,27 @@
         <v>0.4</v>
       </c>
       <c r="J9">
+        <v>0.65</v>
+      </c>
+      <c r="K9">
         <v>0.25</v>
       </c>
-      <c r="K9">
+      <c r="L9">
         <v>0.3</v>
       </c>
-      <c r="L9">
+      <c r="M9">
         <v>0.28</v>
-      </c>
-      <c r="M9">
-        <v>0.2</v>
       </c>
       <c r="N9">
         <v>0.2</v>
       </c>
       <c r="O9">
+        <v>0.2</v>
+      </c>
+      <c r="P9">
+        <v>0.2</v>
+      </c>
+      <c r="Q9">
         <v>0.2</v>
       </c>
     </row>
@@ -15082,7 +17496,7 @@
         <v>0.65</v>
       </c>
       <c r="J10">
-        <v>0.95</v>
+        <v>0.75</v>
       </c>
       <c r="K10">
         <v>0.95</v>
@@ -15091,13 +17505,19 @@
         <v>0.95</v>
       </c>
       <c r="M10">
-        <v>0.05</v>
+        <v>0.95</v>
       </c>
       <c r="N10">
         <v>0.05</v>
       </c>
       <c r="O10">
         <v>0.05</v>
+      </c>
+      <c r="P10">
+        <v>0.05</v>
+      </c>
+      <c r="Q10">
+        <v>0.45</v>
       </c>
     </row>
     <row r="11">
@@ -15129,22 +17549,28 @@
         <v>0</v>
       </c>
       <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
         <v>0.5</v>
       </c>
-      <c r="K11">
+      <c r="L11">
         <v>0.4</v>
       </c>
-      <c r="L11">
+      <c r="M11">
         <v>0.45</v>
       </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="O11">
         <v>0</v>
+      </c>
+      <c r="P11">
+        <v>0</v>
+      </c>
+      <c r="Q11">
+        <v>0.2</v>
       </c>
     </row>
     <row r="12">
@@ -15176,7 +17602,7 @@
         <v>0</v>
       </c>
       <c r="J12">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K12">
         <v>0.8</v>
@@ -15185,13 +17611,19 @@
         <v>0.8</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="O12">
         <v>0</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
+        <v>0.35</v>
       </c>
     </row>
     <row r="13">
@@ -15232,13 +17664,19 @@
         <v>0</v>
       </c>
       <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
         <v>0.7</v>
       </c>
-      <c r="N13">
+      <c r="O13">
         <v>0.8</v>
       </c>
-      <c r="O13">
+      <c r="P13">
         <v>0.75</v>
+      </c>
+      <c r="Q13">
+        <v>0.3</v>
       </c>
     </row>
     <row r="14">
@@ -15270,7 +17708,7 @@
         <v>0.5</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -15285,6 +17723,12 @@
         <v>0</v>
       </c>
       <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>0</v>
+      </c>
+      <c r="Q14">
         <v>0</v>
       </c>
     </row>
@@ -15317,7 +17761,7 @@
         <v>0.85</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -15332,6 +17776,12 @@
         <v>0</v>
       </c>
       <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>0</v>
+      </c>
+      <c r="Q15">
         <v>0</v>
       </c>
     </row>
@@ -15364,22 +17814,28 @@
         <v>0.03</v>
       </c>
       <c r="J16">
+        <v>0.35</v>
+      </c>
+      <c r="K16">
         <v>0.25</v>
       </c>
-      <c r="K16">
+      <c r="L16">
         <v>0.2</v>
       </c>
-      <c r="L16">
+      <c r="M16">
         <v>0.23</v>
       </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
       <c r="N16">
         <v>0</v>
       </c>
       <c r="O16">
         <v>0</v>
+      </c>
+      <c r="P16">
+        <v>0</v>
+      </c>
+      <c r="Q16">
+        <v>0.12</v>
       </c>
     </row>
     <row r="17">
@@ -15420,13 +17876,19 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <v>1</v>
       </c>
       <c r="O17">
         <v>1</v>
+      </c>
+      <c r="P17">
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -15461,19 +17923,25 @@
         <v>0.4</v>
       </c>
       <c r="K18">
+        <v>0.4</v>
+      </c>
+      <c r="L18">
         <v>0.2</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.3</v>
       </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
       <c r="N18">
         <v>0</v>
       </c>
       <c r="O18">
         <v>0</v>
+      </c>
+      <c r="P18">
+        <v>0</v>
+      </c>
+      <c r="Q18">
+        <v>0.18</v>
       </c>
     </row>
     <row r="19">
@@ -15505,22 +17973,28 @@
         <v>0.15</v>
       </c>
       <c r="J19">
+        <v>0.25</v>
+      </c>
+      <c r="K19">
         <v>0.35</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>0.6</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.48</v>
       </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
       <c r="N19">
         <v>0</v>
       </c>
       <c r="O19">
         <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0.2</v>
       </c>
     </row>
     <row r="21">
@@ -15580,17 +18054,22 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Generic prototypes (tree, flower, bird, fish) have damped distinguishing-feature values.</v>
+        <v>Kingdom generics (tree, flower, bird, fish) have damped distinguishing-feature values.</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
+        <v>Super-generics (plant, animal) sit above the kingdoms and damp anything that differs between their children.</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
         <v>Simplex pools are clipped to ≥0 then renormalized to sum=1 after noise. Non-simplex are clipped to [0,1].</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O31"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q32"/>
   </ignoredErrors>
 </worksheet>
 </file>